--- a/docs/latest.xlsx
+++ b/docs/latest.xlsx
@@ -524,7 +524,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mobilize:919162:1773599400</t>
+          <t>mobilize:879712:1773514800</t>
         </is>
       </c>
       <c r="D2" t="b">
@@ -532,63 +532,63 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-11T05:39:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>RCV Canvass at West Hollywood Meet and Greet for Ankur Patel</t>
+          <t>Tesla Takedown - Stanford Mall</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>11:30 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Electric Karma | 8222 1/2 W 3rd St | Los Angeles, CA 90048</t>
+          <t>Tesla Showroom • Stanford Shopping Center | 660 Stanford Shopping Center | Palo Alto, CA 94304</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Beverly Center</t>
+          <t>Stanford Shopping Center</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>BEVCENTER</t>
+          <t>STANFORDSC</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.43</v>
+        <v>0.02</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/calrcv/event/919162/</t>
+          <t>https://www.mobilize.us/thewolves/event/879712/</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>CANVASS</t>
+          <t>RALLY</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>919162</t>
+          <t>879712</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1773599400</v>
+        <v>1773514800</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>BEVCENTER:Beverly Center(0.43mi)</t>
+          <t>STANFORDSC:Stanford Shopping Center(0.02mi)</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mobilize:879712:1773514800</t>
+          <t>mobilize:810382:1773763200</t>
         </is>
       </c>
       <c r="D3" t="b">
@@ -609,63 +609,63 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-11T03:29:59</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tesla Takedown - Stanford Mall</t>
+          <t>Good Trouble: John Lewis Bridge Overpass! (Northgate) #TeslaTakedownTuesday</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Tesla Showroom • Stanford Shopping Center | 660 Stanford Shopping Center | Palo Alto, CA 94304</t>
+          <t>John Lewis Memorial Bridge Pedestrian Overpass at Northgate | 401 NE Northgate Way | Seattle, WA 98125</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Stanford Shopping Center</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>STANFORDSC</t>
+          <t>NORTHGATE</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/thewolves/event/879712/</t>
+          <t>https://www.mobilize.us/seattleindivisible/event/810382/</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>879712</t>
+          <t>810382</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1773514800</v>
+        <v>1773763200</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>STANFORDSC:Stanford Shopping Center(0.02mi)</t>
+          <t>NORTHGATE:Northgate Station(0.2mi)</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mobilize:810382:1773763200</t>
+          <t>mobilize:810170:1773496800</t>
         </is>
       </c>
       <c r="D4" t="b">
@@ -686,45 +686,45 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-11T03:29:59</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Good Trouble: John Lewis Bridge Overpass! (Northgate) #TeslaTakedownTuesday</t>
+          <t>Visibility CLT Pop-up Protest - Southpark</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>John Lewis Memorial Bridge Pedestrian Overpass at Northgate | 401 NE Northgate Way | Seattle, WA 98125</t>
+          <t>Southpark (Fairview &amp; Sharon) | Fairview Road &amp; Sharon Road | Charlotte, NC 28210</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>NORTHGATE</t>
+          <t>SOUTHPARK</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/seattleindivisible/event/810382/</t>
+          <t>https://www.mobilize.us/indivisiblecharlottenc/event/810170/</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -734,15 +734,15 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>810382</t>
+          <t>810170</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1773763200</v>
+        <v>1773496800</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>NORTHGATE:Northgate Station(0.2mi)</t>
+          <t>SOUTHPARK:Southpark(0.23mi)</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mobilize:810170:1773496800</t>
+          <t>mobilize:891931:1773597600</t>
         </is>
       </c>
       <c r="D5" t="b">
@@ -763,45 +763,45 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-09T15:27:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Visibility CLT Pop-up Protest - Southpark</t>
+          <t>Making Our Resistance Visible</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Southpark (Fairview &amp; Sharon) | Fairview Road &amp; Sharon Road | Charlotte, NC 28210</t>
+          <t>Corner of Green Grove Road and Asbury Avenue in front of the CVS | Tinton Falls, NJ 07753</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Jersey Shore Premium Outlets</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SOUTHPARK</t>
+          <t>JERSEYSHOREPO</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisiblecharlottenc/event/810170/</t>
+          <t>https://www.mobilize.us/indivisible/event/891931/</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>810170</t>
+          <t>891931</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1773496800</v>
+        <v>1773597600</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>SOUTHPARK:Southpark(0.23mi)</t>
+          <t>JERSEYSHOREPO:Jersey Shore Premium Outlets(0.27mi)</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mobilize:891931:1773597600</t>
+          <t>mobilize:919162:1773599400</t>
         </is>
       </c>
       <c r="D6" t="b">
@@ -840,12 +840,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-03-09T15:27:00</t>
+          <t>2026-03-11T05:39:25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Making Our Resistance Visible</t>
+          <t>RCV Canvass at West Hollywood Meet and Greet for Ankur Patel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -855,48 +855,48 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>11:30 AM</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Corner of Green Grove Road and Asbury Avenue in front of the CVS | Tinton Falls, NJ 07753</t>
+          <t>Electric Karma | 8222 1/2 W 3rd St | Los Angeles, CA 90048</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Jersey Shore Premium Outlets</t>
+          <t>Beverly Center</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>JERSEYSHOREPO</t>
+          <t>BEVCENTER</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.27</v>
+        <v>0.43</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisible/event/891931/</t>
+          <t>https://www.mobilize.us/calrcv/event/919162/</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>VISIBILITY_EVENT</t>
+          <t>CANVASS</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>891931</t>
+          <t>919162</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1773597600</v>
+        <v>1773599400</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>JERSEYSHOREPO:Jersey Shore Premium Outlets(0.27mi)</t>
+          <t>BEVCENTER:Beverly Center(0.43mi)</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:Q59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4874,55 +4874,60 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Last Seen</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Protest Name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Property ID</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Distance to Property (miles)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Event URL</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Event Type</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Event ID</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Timeslot Start (epoch)</t>
         </is>
@@ -4950,53 +4955,58 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>Bridge Brigade over Storrow Drive promoting NO KINGS -March 28</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>4:30 PM</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Appleton Bridge over Storrow Drive to the Esplanade. (Easy access from Red line Charles St station.) | Frances Appleton Brg | Boston, MA 02114</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Copley Place</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>COPLEY</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/bostonindivisible/event/909535/</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>909535</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>1773261000</v>
       </c>
     </row>
@@ -5022,53 +5032,58 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Workshop to Make Art Signs for the Resistance - Boston Indivisible and 50501</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>The Cathedral Church of Saint Paul | 138 Tremont St, Boston | Boston, MA 02111</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Copley Place</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>COPLEY</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.97</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/bostonindivisible/event/909664/</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>WORKSHOP</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>909664</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>1773496800</v>
       </c>
     </row>
@@ -5094,53 +5109,58 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>Brookline Rally for Democracy, March 2026</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Coolidge Corner | Beacon Street &amp; Harvard Street | Brookline, MA 02446</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Copley Place</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>COPLEY</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>2.26</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/speakoutseniors/event/891822/</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>891822</t>
         </is>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>1773507600</v>
       </c>
     </row>
@@ -5166,53 +5186,58 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>Saturday RESIST Standout</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Newton Center | Beacon Street &amp; Centre Street | Newton, MA 02459</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>The Shops at Chestnut Hill</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>CHESTNUTHILL</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1.14</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/newtonindivisible/event/892572/</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>892572</t>
         </is>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>1773504000</v>
       </c>
     </row>
@@ -5238,53 +5263,58 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>(Panera March 14) Virginia Referendum Postcards</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Panera Bread | 120 Highland Ave | Needham, MA 02494</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>The Shops at Chestnut Hill</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>CHESTNUTHILL</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>2.49</v>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/swingbluealliance/event/917921/</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>POSTCARD_WRITING</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>917921</t>
         </is>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>1773511200</v>
       </c>
     </row>
@@ -5310,53 +5340,58 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>Newton Bridge Brigade—Kendrick St Overpass</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>7:30 AM</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Kendrick Street Overpass | Kendrick St, (Bridge over 128/95) | Needham, MA 02494</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>The Shops at Chestnut Hill</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>CHESTNUTHILL</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>2.68</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/newtonindivisible/event/897984/</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>897984</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>1773315000</v>
       </c>
     </row>
@@ -5382,53 +5417,58 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>Needham Resists Visibility Brigade</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>2:45 PM</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Kendrick Street Bridge over 95/128 (park at Cutler Park, 84 Kendrick St) | Kendrick Street | Needham, MA 02494</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>The Shops at Chestnut Hill</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>CHESTNUTHILL</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>2.68</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/needhamresistsvisibilitybrigade/event/870158/</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>870158</t>
         </is>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>1773600300</v>
       </c>
     </row>
@@ -5454,53 +5494,58 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>Highlanders Visibility Brigade—Mass Pike Overpass</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Mass Pike Overpass at Highland St West Newton | Highland St | Newton, MA 02465</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>The Shops at Chestnut Hill</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>CHESTNUTHILL</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>2.71</v>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/newtonindivisible/event/898267/</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>898267</t>
         </is>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>1773230400</v>
       </c>
     </row>
@@ -5526,53 +5571,58 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>NO KINGS Protest Airport Rotary Saturday, March 14th 12-1pm</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Airport Rotary | hyannnis, MA 02601</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Cape Cod Mall</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>CAPECOD</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>0.52</v>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisible/event/899401/</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>899401</t>
         </is>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>1773504000</v>
       </c>
     </row>
@@ -5598,53 +5648,58 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>Exit 4 Nashua Popup Bridge Brigade</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Nashua | Nashua, NH 03062</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Pheasant Lane Mall</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>PHEASANTLANE</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>2.94</v>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/nh-bridge-brigade-for-democracy/event/888328/</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>888328</t>
         </is>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>1773594000</v>
       </c>
     </row>
@@ -5670,53 +5725,58 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>Jersey City KYRs Outreach Walk - South Asian Communities</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>9:30 AM</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Jersey City, NJ 07306</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Newport Centre</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>NEWPORTCTR</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>1.79</v>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/aapinewjersey/event/906414/</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>SOLIDARITY_EVENT</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>906414</t>
         </is>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>1773581400</v>
       </c>
     </row>
@@ -5742,53 +5802,58 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>Making Our Resistance Visible</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Corner of Green Grove Road and Asbury Avenue in front of the CVS | Tinton Falls, NJ 07753</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Jersey Shore Premium Outlets</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>JERSEYSHOREPO</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>0.27</v>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisible/event/891931/</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>891931</t>
         </is>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>1773597600</v>
       </c>
     </row>
@@ -5814,53 +5879,58 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>Toms River "Hold NJ-CD04 Congressman Chris Smith Accountable" - Protect Democracy</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>33 Washington St | Toms River, NJ 08753</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Ocean County Mall</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>OCEANCOUNTY</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>2.05</v>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisible/event/900632/</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>900632</t>
         </is>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>1773763200</v>
       </c>
     </row>
@@ -5886,53 +5956,58 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>Signs of Democracy Arlington</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>2:00 PM</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>2710 S Glebe Rd | Arlington, VA 22206</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Fashion Center at Pentagon City</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>PENTAGONCITY</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>1.59</v>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisible/event/896112/</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>896112</t>
         </is>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>1773511200</v>
       </c>
     </row>
@@ -5958,53 +6033,58 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>WofA Sunday Bridge Brigade</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>2100 21st St N | Arlington, VA 22201</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Fashion Center at Pentagon City</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>PENTAGONCITY</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>2.7</v>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisible/event/908528/</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>908528</t>
         </is>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>1773601200</v>
       </c>
     </row>
@@ -6030,53 +6110,58 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>Freedom Fridays: Trump, the President of War</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Williamsburg James City County Courthouse | 5201 Monticello Ave | Williamsburg, VA 23188</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Williamsburg Premium Outlets</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>WILLIAMSBURGPO</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>1.25</v>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/williamsburgjccindivisible/event/918450/</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>918450</t>
         </is>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>1773417600</v>
       </c>
     </row>
@@ -6102,53 +6187,58 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>Visibility CLT Pop-up Protest - Cotswold</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>4:30 PM</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Randolph &amp; Sharon Amity | Randolph Road &amp; South Sharon Amity Road | Charlotte, NC 28211</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Southpark</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>SOUTHPARK</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>2.46</v>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisiblecharlottenc/event/797821/</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>797821</t>
         </is>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>1773347400</v>
       </c>
     </row>
@@ -6174,53 +6264,58 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>Visibility CLT Pop-up Protest - Southpark</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Southpark (Fairview &amp; Sharon) | Fairview Road &amp; Sharon Road | Charlotte, NC 28210</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Southpark</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>SOUTHPARK</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>0.23</v>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisiblecharlottenc/event/810170/</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>810170</t>
         </is>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>1773496800</v>
       </c>
     </row>
@@ -6246,53 +6341,58 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>Visibility CLT Pop-up Protest - Park Road Park</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Tyvola Road &amp; Park Road | Charlotte, NC 28210</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Southpark</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>SOUTHPARK</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>1.03</v>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisiblecharlottenc/event/816998/</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>816998</t>
         </is>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>1773781200</v>
       </c>
     </row>
@@ -6318,53 +6418,58 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>Visibility CLT Pop-up Protest - Park Road</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>4:30 PM</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Park Road | Park Road &amp; Woodlawn Road | Charlotte, NC 28209</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Southpark</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>SOUTHPARK</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>1.82</v>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisiblecharlottenc/event/797822/</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>797822</t>
         </is>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>1773347400</v>
       </c>
     </row>
@@ -6390,53 +6495,58 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>Files Into Trials</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>3202 SW 1st Ave | Miami, FL 33145</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Brickell City Centre</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>BRICKELL</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>1.71</v>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisible/event/917684/</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>917684</t>
         </is>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>1773500400</v>
       </c>
     </row>
@@ -6462,53 +6572,58 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>3/16 South Dade: Community Town Hall</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>6:30 PM</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>11111 Pinkston Dr | Miami, FL 33176</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>The Falls</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>THEFALLS</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>2.29</v>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/richardforcongress/event/915847/</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>TOWN_HALL</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>915847</t>
         </is>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>1773700200</v>
       </c>
     </row>
@@ -6534,53 +6649,58 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>Saturday Sign Waving at Nora Plazas &amp; Monon Trail 11 to 2 PM</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Nora Plazas | East 86th Street &amp; Monon Trail | Indianapolis, IN 46240</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Fashion Mall at Keystone</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>KEYSTONE</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>1.31</v>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/hoosiersforconstitutionaldemocracy/event/913681/</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>913681</t>
         </is>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>1773500400</v>
       </c>
     </row>
@@ -6606,53 +6726,58 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>No Kings Twin Cities Bridge Brigade -Edina</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Mooty Pickleball Court | 4300 W 66th St | Edina, MN 55435</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Southdale Center</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>SOUTHDALE</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisibletwincities/event/915295/</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>915295</t>
         </is>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>1773500400</v>
       </c>
     </row>
@@ -6678,53 +6803,58 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>Anti-ICE Protest at MN GOP HQ (11:30am-12:30pm</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>7400 Metro Blvd | Edina, MN 55439</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Southdale Center</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>SOUTHDALE</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>1.56</v>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisiblemn03/event/896393/</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>896393</t>
         </is>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>1773333000</v>
       </c>
     </row>
@@ -6750,53 +6880,58 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>Rally for Democracy</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Fulton Neighborhood, Minneapolis | West 50th Street between Upton &amp; Thomas Avenue South, 50th &amp; Upton Avenue South | Minneapolis, MN 55410</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>Southdale Center</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>SOUTHDALE</t>
         </is>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>2</v>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisible/event/857025/</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>857025</t>
         </is>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>1773439200</v>
       </c>
     </row>
@@ -6822,53 +6957,58 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>Rally for Democracy, Stand on Every Corner</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>4:30 PM</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>West 50th Street &amp; Halifax Avenue South | Edina, MN 55424</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>Southdale Center</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>SOUTHDALE</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>2.21</v>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisible/event/827822/</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>827822</t>
         </is>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>1773696600</v>
       </c>
     </row>
@@ -6894,53 +7034,58 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>Line Colorado Blvd! - Solidarity Saturdays @ 8th Ave</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>8th Avenue &amp; Colorado Boulevard | Denver, CO 80206</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>CHERRYCREEK</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>1.06</v>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisible/event/897610/</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>897610</t>
         </is>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>1773511200</v>
       </c>
     </row>
@@ -6966,53 +7111,58 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>Fight Fascism Fridays Vegas</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Federal Courthouse: Bridger and LVB | 333 S Las Vegas Blvd | Las Vegas, NV 89101</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Las Vegas North Premium Outlets</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>VEGASNORTHPO</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>0.93</v>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisiblelasvegas/event/914058/</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>914058</t>
         </is>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>1773439200</v>
       </c>
     </row>
@@ -7038,53 +7188,58 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>Fight Fascism Fridays Vegas</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Federal Courthouse: Bridger and LVB | 333 S Las Vegas Blvd | Las Vegas, NV 89101</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Las Vegas Convention Center</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>VEGASCONVENTION</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>2.38</v>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisiblelasvegas/event/914058/</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>914058</t>
         </is>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>1773439200</v>
       </c>
     </row>
@@ -7110,53 +7265,58 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
           <t>Fight Fascism Fridays Vegas</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>3:00 PM</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Federal Courthouse: Bridger and LVB | 333 S Las Vegas Blvd | Las Vegas, NV 89101</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Encore at Wynn Las Vegas</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>ENCOREWYNNVEGAS</t>
         </is>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>2.78</v>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisiblelasvegas/event/914058/</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>914058</t>
         </is>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>1773439200</v>
       </c>
     </row>
@@ -7173,7 +7333,7 @@
         </is>
       </c>
       <c r="D33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -7182,53 +7342,58 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>RCV Canvass at West Hollywood Meet and Greet for Ankur Patel</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Electric Karma | 8222 1/2 W 3rd St | Los Angeles, CA 90048</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Beverly Center</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>BEVCENTER</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>0.43</v>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/calrcv/event/919162/</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>CANVASS</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>919162</t>
         </is>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>1773599400</v>
       </c>
     </row>
@@ -7254,53 +7419,58 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>Liberty and Justice for ALL, South Bay</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Northeast corner Anza at PCH | 4135 Pacific Coast Hwy | Torrance, CA 90505</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Del Amo Fashion Center</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>DELAMO</t>
         </is>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>1.66</v>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisiblesouthbayla/event/916557/</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>916557</t>
         </is>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>1773513000</v>
       </c>
     </row>
@@ -7326,53 +7496,58 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>Fight Fascism Fridays - Every Friday in Rancho Cucamonga</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>3:30 PM</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Haven Avenue &amp; Foothill Boulevard | Rancho Cucamonga, CA 91730</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Ontario Mills</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>ONTARIOMILLS</t>
         </is>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>2.81</v>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/catladiesforamerica/event/893656/</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>893656</t>
         </is>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>1773441000</v>
       </c>
     </row>
@@ -7398,53 +7573,58 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>Weekly Meade Ave Bridge Bannering Over I-805 | Thursday Afternoons</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Meade Ave Bridge Over I-805 | 4371 Boundary St | San Diego, CA 92116</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Fashion Valley</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>FASHIONVAL</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>2.41</v>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/visibilitybrigadesandiego/event/860202/</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>860202</t>
         </is>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>1773360000</v>
       </c>
     </row>
@@ -7470,53 +7650,58 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>Visibility Brigade - North Park</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Meade Ave bridge over I-805 in North Park | 4371 Boundary St | San Diego, CA 92116</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>Fashion Valley</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>FASHIONVAL</t>
         </is>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>2.41</v>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisible/event/824060/</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>824060</t>
         </is>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>1773360000</v>
       </c>
     </row>
@@ -7542,53 +7727,58 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>Weekly Taylor St Bridge Bannering Over I-8 | Monday Afternoons</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Taylor Street Bridge (Exit 3) | 4490 Taylor St, Taylor Street Park and Ride | San Diego, CA 92108</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>Fashion Valley</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>FASHIONVAL</t>
         </is>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>1.54</v>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/visibilitybrigadesandiego/event/871084/</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>871084</t>
         </is>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>1773702000</v>
       </c>
     </row>
@@ -7614,53 +7804,58 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>Weekly Taylor St Bridge Bannering Over I-8 | Monday Afternoons - Visibility Brigade</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Taylor Street Bridge (Exit 3) | 4490 Taylor St, Taylor Street Park and Ride | San Diego, CA 92108</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Fashion Valley</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>FASHIONVAL</t>
         </is>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>1.54</v>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisible/event/875118/</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>875118</t>
         </is>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>1773702000</v>
       </c>
     </row>
@@ -7686,53 +7881,58 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
           <t>Change Begins With ME Overpass Alliance-Mondays</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Clairemont Drive overpass at I-5 | 2366 Clairemont Dr | San Diego, CA 92109</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>Fashion Valley</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>FASHIONVAL</t>
         </is>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>2.87</v>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/bethechangesd/event/824571/</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>824571</t>
         </is>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>1773702000</v>
       </c>
     </row>
@@ -7758,53 +7958,58 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
           <t>Say No To Ken Calvert Weekly Visibility Sign Waving- Formerly Empty Chair Town Hall!</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Intersection of Monterrey and 111- park at Panera | 73075 CA-111 | Palm Desert, CA 92260</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>The Gardens on El Paseo</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>GARDENSONELPASO</t>
         </is>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>0.52</v>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisible/event/801600/</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>801600</t>
         </is>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>1773590400</v>
       </c>
     </row>
@@ -7830,53 +8035,58 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>Defend Democracy. Demand Accountability.</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>La Paz Road &amp; Marguerite Parkway | Mission Viejo, CA 92692</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>The Shops at Mission Viejo</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>MISSIONVIEJO</t>
         </is>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>2.71</v>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisibleca40/event/823056/</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>823056</t>
         </is>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>1773252000</v>
       </c>
     </row>
@@ -7902,53 +8112,58 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>Ladera Ranch Stands For Human Rights</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Crown Valley &amp; Antonio | 27402 Antonio Pkwy | Ladera Ranch, CA 92694</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>The Shops at Mission Viejo</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>MISSIONVIEJO</t>
         </is>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>2.39</v>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/ocindivisible/event/893284/</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>893284</t>
         </is>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>1773446400</v>
       </c>
     </row>
@@ -7974,53 +8189,58 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
           <t>Overpass Brigade</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>4:30 PM</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>East Grand Avenue overpass near The Village | E Grand Ave &amp; Hwy. 101 | Arroyo Grande, CA 93420</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Pismo Beach Premium Outlets</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>PISMOBEACH</t>
         </is>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>2.7</v>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisible/event/917108/</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>917108</t>
         </is>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>1773444600</v>
       </c>
     </row>
@@ -8046,53 +8266,58 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>Signs of Fascism (Palo Alto)</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>11:30 AM</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Corner of El Camino Real and Embarcadero Road | 50 Embarcadero Rd | Palo Alto, CA 94301</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>Stanford Shopping Center</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>STANFORDSC</t>
         </is>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>0.84</v>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/ipaplus/event/876104/</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>876104</t>
         </is>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>1773426600</v>
       </c>
     </row>
@@ -8118,53 +8343,58 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
           <t>Tesla Takedown - Stanford Mall</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Tesla Showroom • Stanford Shopping Center | 660 Stanford Shopping Center | Palo Alto, CA 94304</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>Stanford Shopping Center</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>STANFORDSC</t>
         </is>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>0.02</v>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/thewolves/event/879712/</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>879712</t>
         </is>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
         <v>1773514800</v>
       </c>
     </row>
@@ -8190,53 +8420,58 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
           <t>Union Busting Billionaires Gotta Go!</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Whole Foods Market | 774 Emerson St | Palo Alto, CA 94301</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Stanford Shopping Center</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>STANFORDSC</t>
         </is>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>0.63</v>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/thewolves/event/875874/</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>875874</t>
         </is>
       </c>
-      <c r="P47" t="n">
+      <c r="Q47" t="n">
         <v>1773705600</v>
       </c>
     </row>
@@ -8262,53 +8497,58 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
           <t>Menlo Park Speaks Out</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>10:30 AM</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Fremont Park | University Drive &amp; Santa Cruz Avenue | Menlo Park, CA 94025</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>Stanford Shopping Center</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>STANFORDSC</t>
         </is>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/menloparkspeaksout/event/791569/</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>791569</t>
         </is>
       </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
         <v>1773595800</v>
       </c>
     </row>
@@ -8334,53 +8574,58 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
           <t>Bannering 101 (Palo Alto)</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Adobe Creek Bike and Pedestrian Bridge | Palo Alto, CA 94303</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>Stanford Shopping Center</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>STANFORDSC</t>
         </is>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>3</v>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/ipaplus/event/836661/</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>836661</t>
         </is>
       </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
         <v>1773248400</v>
       </c>
     </row>
@@ -8406,53 +8651,58 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
           <t>Weekly Napa Rally to Resist the Trump/Musk/GOP Regime!</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Soscol Avenue &amp; 3rd Street | Napa, CA 94559</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>Napa Premium Outlets</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>NAPAPO</t>
         </is>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>1.14</v>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisible/event/774947/</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>774947</t>
         </is>
       </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
         <v>1773446400</v>
       </c>
     </row>
@@ -8478,53 +8728,58 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
           <t>Justice for Renée Good / Alex Pretti - ICE out of Home Depot Protest</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Bicentennial Way &amp; Mendocino Avenue | Santa Rosa, CA 95403</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>Santa Rosa Plaza</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>SANTAROSA</t>
         </is>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>2.2</v>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisiblesonomacounty/event/838660/</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>838660</t>
         </is>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>1773597600</v>
       </c>
     </row>
@@ -8550,53 +8805,58 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
           <t>VISIBILITY BRIGADE - Santa Rosa - 101 Ped Bridge @ Hwy 12</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>3:30 PM</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>Santa Rosa Pedestrian Overpass, over Hwy 101 and just south of Hwy 12. Access to the "sky bridge" using your mobile map app. | 808 S. Davis St., 935 S. A. St. | Santa Rosa, CA 95407</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>Santa Rosa Plaza</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>SANTAROSA</t>
         </is>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisiblesonomacounty/event/795435/</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>795435</t>
         </is>
       </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
         <v>1773268200</v>
       </c>
     </row>
@@ -8622,53 +8882,58 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
           <t>Tell Target: ICE OUT NOW - Justice for Renee Good &amp; Alex Pretti</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>Target - Santa Rosa South (public sidewalks) | 1980 Santa Rosa Ave, (Meet at the Kawana Springs Rd. driveway entrance to Target Shopping center (traffic signal) | Santa Rosa, CA 95404</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>Santa Rosa Plaza</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>SANTAROSA</t>
         </is>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>1.55</v>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/indivisiblesonomacounty/event/848553/</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>848553</t>
         </is>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="n">
         <v>1773511200</v>
       </c>
     </row>
@@ -8694,53 +8959,58 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>CRUSH ICE! NO SECRET POLICE! WEEKLY THURSDAYS!! (Honolulu)</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>Intersection of Atkinson Drive &amp; Ala Moana Boulevard | Atkinson Drive &amp; Ala Moana Boulevard | Honolulu, HI 96814</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>International Market Place</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>INTLMARKET</t>
         </is>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>1.25</v>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/protecthawaii/event/826166/</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>826166</t>
         </is>
       </c>
-      <c r="P54" t="n">
+      <c r="Q54" t="n">
         <v>1773370800</v>
       </c>
     </row>
@@ -8766,53 +9036,58 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>Good Trouble: John Lewis Bridge Overpass! (Northgate) #TeslaTakedownTuesday</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>John Lewis Memorial Bridge Pedestrian Overpass at Northgate | 401 NE Northgate Way | Seattle, WA 98125</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>Northgate Station</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>NORTHGATE</t>
         </is>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>0.2</v>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/seattleindivisible/event/810382/</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>810382</t>
         </is>
       </c>
-      <c r="P55" t="n">
+      <c r="Q55" t="n">
         <v>1773763200</v>
       </c>
     </row>
@@ -8838,53 +9113,58 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
           <t>Tesla Takedown Tuesday: Woodland Park Overpass!</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>4:00 PM</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>Woodland Park N Pedestrian Bridge | 5192 Aurora Ave N | Seattle, WA 98103</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>Northgate Station</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>NORTHGATE</t>
         </is>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
         <v>2.81</v>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/seattleindivisible/event/807188/</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>807188</t>
         </is>
       </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
         <v>1773788400</v>
       </c>
     </row>
@@ -8910,53 +9190,58 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>Refuse Fascism Fridays-Marysville (Other locations, see Details)</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>5:00 PM</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>Fourth Street &amp; State Avenue | Marysville, WA 98270</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>Seattle Premium Outlets</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>SEATTLEPO</t>
         </is>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>2.88</v>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/snohomishcountyindivisible/event/899741/</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>899741</t>
         </is>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>1773446400</v>
       </c>
     </row>
@@ -8982,53 +9267,58 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
           <t>NO WAR. NO KINGS: Tacoma</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>10:00 AM</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>Union Station - Federal Courthouse | 1717 Pacific Ave | Tacoma, WA 98402</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>Tacoma Mall</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>TACOMAMALL</t>
         </is>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>2.59</v>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/seattleindivisible/event/795854/</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>795854</t>
         </is>
       </c>
-      <c r="P58" t="n">
+      <c r="Q58" t="n">
         <v>1773507600</v>
       </c>
     </row>
@@ -9054,58 +9344,63 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
+          <t>2026-03-11T06:33:53</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
           <t>Knock doors with Team Sydney for Assembly!</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>12:00 PM</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>Location provided upon RSVP | Throughout North Anchorage! | Anchorage, AK 99501</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>Anchorage 5th Avenue Mall</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>ANC5Ave</t>
         </is>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
         <v>0.73</v>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/sydneyscoutforassembly/event/918417/</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>CANVASS</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>918417</t>
         </is>
       </c>
-      <c r="P59" t="n">
+      <c r="Q59" t="n">
         <v>1773604800</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:P59">
+  <conditionalFormatting sqref="A2:Q59">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$D2=TRUE</formula>
     </cfRule>

--- a/docs/latest.xlsx
+++ b/docs/latest.xlsx
@@ -13,9 +13,9 @@
     <sheet name="NoKings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Protests'!$A$1:$L$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AllMatches'!$A$1:$M$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NoKings'!$A$1:$L$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Protests'!$A$1:$L$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AllMatches'!$A$1:$M$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NoKings'!$A$1:$L$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7"/>
@@ -696,7 +696,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fashion Valley</t>
+          <t>Stanford Shopping Center</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -706,7 +706,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Stanford Shopping Center</t>
+          <t>Fashion Valley</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -716,7 +716,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Southdale Center</t>
+          <t>Southpark</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -726,7 +726,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Southpark</t>
+          <t>Southdale Center</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -756,7 +756,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fashion Center at Pentagon City</t>
+          <t>The Shops at Mission Viejo</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -766,7 +766,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>The Shops at Mission Viejo</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -776,7 +776,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Fashion Center at Pentagon City</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -796,7 +796,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Anchorage 5th Avenue Mall</t>
+          <t>Brickell City Centre</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -816,7 +816,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brickell City Centre</t>
+          <t>Beverly Center</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -826,7 +826,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Anchorage 5th Avenue Mall</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -836,7 +836,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Beverly Center</t>
+          <t>Napa Premium Outlets</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -846,7 +846,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Newport Centre</t>
+          <t>Las Vegas North Premium Outlets</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -856,7 +856,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Napa Premium Outlets</t>
+          <t>Jersey Shore Premium Outlets</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -866,7 +866,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Las Vegas North Premium Outlets</t>
+          <t>International Market Place</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -876,7 +876,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jersey Shore Premium Outlets</t>
+          <t>Folsom Outlet Marketplace</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -886,7 +886,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>International Market Place</t>
+          <t>Fashion Mall at Keystone</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -896,7 +896,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Folsom Outlet Marketplace</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -906,7 +906,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Fashion Mall at Keystone</t>
+          <t>Newport Centre</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -916,7 +916,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ocean County Mall</t>
+          <t>Pheasant Lane Mall</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -926,7 +926,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Seattle Premium Outlets</t>
+          <t>Pismo Beach Premium Outlets</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -936,7 +936,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Pismo Beach Premium Outlets</t>
+          <t>Ocean County Mall</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -956,7 +956,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pheasant Lane Mall</t>
+          <t>The Falls</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -966,7 +966,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>The Falls</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -976,7 +976,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>The Gardens on El Paseo</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -986,145 +986,145 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>The Gardens on El Paseo</t>
+          <t>Williamsburg Premium Outlets</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Williamsburg Premium Outlets</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42"/>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>By Organization</t>
+        </is>
+      </c>
+    </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>By Organization</t>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Event Count</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Organization</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>NoKings</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>By Distance</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Distance Band</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Event Count</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>NoKings</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>By Distance</t>
-        </is>
-      </c>
-    </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Distance Band</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>&lt; 1 mile</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>1–2 miles</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 2 miles</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>By Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>Event Count</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>&lt; 1 mile</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>1–2 miles</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 2 miles</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>By Property</t>
-        </is>
-      </c>
-    </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Property</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>Event Count</t>
-        </is>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Beverly Center</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Beverly Center</t>
+          <t>Fashion Center at Pentagon City</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Fashion Center at Pentagon City</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -1150,7 +1150,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Stanford Shopping Center</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1160,11 +1160,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Stanford Shopping Center</t>
+          <t>Santa Rosa Plaza</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -1180,7 +1180,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Santa Rosa Plaza</t>
+          <t>Town Center at Boca Raton</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1190,17 +1190,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Town Center at Boca Raton</t>
+          <t>Southdale Center</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Southdale Center</t>
+          <t>Pismo Beach Premium Outlets</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1210,7 +1210,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Pismo Beach Premium Outlets</t>
+          <t>Battlefield Mall</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1220,17 +1220,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Battlefield Mall</t>
+          <t>Del Amo Fashion Center</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Broadway Square</t>
+          <t>Cielo Vista Mall</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1250,7 +1250,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cielo Vista Mall</t>
+          <t>Broadway Square</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1270,7 +1270,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Simon Tower</t>
+          <t>Sunvalley Shopping Center</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1290,7 +1290,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sunvalley Shopping Center</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1300,7 +1300,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ontario Mills</t>
+          <t>Orland Square</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1310,7 +1310,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Woodfield Mall</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1320,7 +1320,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Simon Tower</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1330,7 +1330,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Woodfield Mall</t>
+          <t>Tyrone Square</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -1340,7 +1340,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Tyrone Square</t>
+          <t>Folsom Outlet Marketplace</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1350,7 +1350,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Orland Square</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -1360,7 +1360,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Newport Centre</t>
+          <t>Northshore Mall</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -1370,7 +1370,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Northshore Mall</t>
+          <t>Ontario Mills</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1380,7 +1380,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Del Amo Fashion Center</t>
+          <t>Coral Square</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1400,7 +1400,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Folsom Outlet Marketplace</t>
+          <t>Napa Premium Outlets</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1410,7 +1410,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Napa Premium Outlets</t>
+          <t>Newport Centre</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1420,11 +1420,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Coral Square</t>
+          <t>Anchorage 5th Avenue Mall</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -1470,7 +1470,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Calhoun Outlet Marketplace</t>
+          <t>Burlington Mall</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -1480,7 +1480,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Anchorage 5th Avenue Mall</t>
+          <t>Brickell City Centre</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -1490,7 +1490,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Brickell City Centre</t>
+          <t>Calhoun Outlet Marketplace</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -1500,7 +1500,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Burlington Mall</t>
+          <t>Gilroy Premium Outlets</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -1510,7 +1510,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>King of Prussia</t>
+          <t>La Plaza Mall</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -1520,7 +1520,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Gurnee Mills</t>
+          <t>King of Prussia</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -1530,7 +1530,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Greenwood Park Mall</t>
+          <t>Gurnee Mills</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -1540,7 +1540,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Great Mall</t>
+          <t>Greenwood Park Mall</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -1560,7 +1560,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Ellenton Premium Outlets</t>
+          <t>Dover Mall</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -1590,7 +1590,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Petaluma Village Premium Outlets</t>
+          <t>Pheasant Lane Mall</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -1600,7 +1600,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Palm Beach Gardens</t>
+          <t>Petaluma Village Premium Outlets</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -1610,7 +1610,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Ocean County Mall</t>
+          <t>Palm Beach Gardens</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -1620,7 +1620,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>La Plaza Mall</t>
+          <t>Ocean County Mall</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -1630,7 +1630,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Liberty Tree Mall</t>
+          <t>Mall at Rockingham Park</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -1640,7 +1640,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Mall at Rockingham Park</t>
+          <t>Liberty Tree Mall</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -1650,7 +1650,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Midland Park Mall</t>
+          <t>Miller Hill Mall</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -1660,7 +1660,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Miller Hill Mall</t>
+          <t>Midland Park Mall</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -1680,7 +1680,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Dover Mall</t>
+          <t>Ellenton Premium Outlets</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -1690,7 +1690,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Gilroy Premium Outlets</t>
+          <t>Great Mall</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -1710,7 +1710,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Pheasant Lane Mall</t>
+          <t>South Shore Plaza</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -1720,7 +1720,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Roosevelt Field</t>
+          <t>Potomac Mills</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -1730,7 +1730,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Potomac Mills</t>
+          <t>Prien Lake Mall</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -1740,7 +1740,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Prien Lake Mall</t>
+          <t>Roosevelt Field</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -1750,7 +1750,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>The Gardens on El Paseo</t>
+          <t>The Mall at University Town Center</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -1760,7 +1760,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Tampa Premium Outlets</t>
+          <t>The Gardens on El Paseo</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -1770,7 +1770,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>South Shore Plaza</t>
+          <t>Tampa Premium Outlets</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -1780,7 +1780,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>The Mall at University Town Center</t>
+          <t>The Shops at Riverside</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -1800,7 +1800,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>The Shops at Riverside</t>
+          <t>Tucson Premium Outlets</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -1810,7 +1810,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Tucson Premium Outlets</t>
+          <t>Twin Cities Premium Outlets</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -1830,7 +1830,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Twin Cities Premium Outlets</t>
+          <t>University Park Village</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -1840,7 +1840,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>University Park Village</t>
+          <t>Vacaville Premium Outlets</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -1850,7 +1850,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Walt Whitman Shops</t>
+          <t>White Oaks Mall</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -1860,7 +1860,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Vacaville Premium Outlets</t>
+          <t>Walt Whitman Shops</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1948,7 +1948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:L58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5054,7 +5054,7 @@
     <row r="56">
       <c r="A56" s="43" t="inlineStr">
         <is>
-          <t>mobilize:899741:1773446400</t>
+          <t>mobilize:910556:1773880200</t>
         </is>
       </c>
       <c r="B56" s="44" t="b">
@@ -5065,52 +5065,52 @@
       </c>
       <c r="D56" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E56" s="45" t="inlineStr">
         <is>
-          <t>Refuse Fascism Fridays-Marysville (Other locations, see Details)</t>
+          <t>Drinks and Democracy hosted by the Folsom Area Democratic Club</t>
         </is>
       </c>
       <c r="F56" s="45" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G56" s="45" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>5:30 PM</t>
         </is>
       </c>
       <c r="H56" s="44" t="inlineStr">
         <is>
-          <t>Fourth Street &amp; State Avenue | Marysville, WA 98270</t>
+          <t>Frends in Folsom | 6608 Folsom-Auburn Rd | Folsom, CA 95630</t>
         </is>
       </c>
       <c r="I56" s="45" t="inlineStr">
         <is>
-          <t>Seattle Premium Outlets</t>
+          <t>Folsom Outlet Marketplace</t>
         </is>
       </c>
       <c r="J56" s="45" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K56" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/snohomishcountyindivisible/event/899741/</t>
+          <t>https://www.mobilize.us/cadems/event/910556/</t>
         </is>
       </c>
       <c r="L56" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>MEET_GREET</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="43" t="inlineStr">
         <is>
-          <t>mobilize:910556:1773880200</t>
+          <t>mobilize:888328:1773594000</t>
         </is>
       </c>
       <c r="B57" s="44" t="b">
@@ -5121,163 +5121,107 @@
       </c>
       <c r="D57" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-09T15:27:00</t>
         </is>
       </c>
       <c r="E57" s="45" t="inlineStr">
         <is>
-          <t>Drinks and Democracy hosted by the Folsom Area Democratic Club</t>
+          <t>Exit 4 Nashua Popup Bridge Brigade</t>
         </is>
       </c>
       <c r="F57" s="45" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G57" s="45" t="inlineStr">
         <is>
-          <t>5:30 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="H57" s="44" t="inlineStr">
         <is>
-          <t>Frends in Folsom | 6608 Folsom-Auburn Rd | Folsom, CA 95630</t>
+          <t>Nashua | Nashua, NH 03062</t>
         </is>
       </c>
       <c r="I57" s="45" t="inlineStr">
         <is>
-          <t>Folsom Outlet Marketplace</t>
+          <t>Pheasant Lane Mall</t>
         </is>
       </c>
       <c r="J57" s="45" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K57" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/cadems/event/910556/</t>
+          <t>https://www.mobilize.us/nh-bridge-brigade-for-democracy/event/888328/</t>
         </is>
       </c>
       <c r="L57" s="47" t="inlineStr">
         <is>
-          <t>MEET_GREET</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="43" t="inlineStr">
-        <is>
-          <t>mobilize:888328:1773594000</t>
-        </is>
-      </c>
-      <c r="B58" s="44" t="b">
-        <v>0</v>
-      </c>
-      <c r="C58" s="44" t="b">
-        <v>0</v>
-      </c>
-      <c r="D58" s="44" t="inlineStr">
-        <is>
-          <t>2026-03-09T15:27:00</t>
-        </is>
-      </c>
-      <c r="E58" s="45" t="inlineStr">
-        <is>
-          <t>Exit 4 Nashua Popup Bridge Brigade</t>
-        </is>
-      </c>
-      <c r="F58" s="45" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="G58" s="45" t="inlineStr">
-        <is>
-          <t>1:00 PM</t>
-        </is>
-      </c>
-      <c r="H58" s="44" t="inlineStr">
-        <is>
-          <t>Nashua | Nashua, NH 03062</t>
-        </is>
-      </c>
-      <c r="I58" s="45" t="inlineStr">
-        <is>
-          <t>Pheasant Lane Mall</t>
-        </is>
-      </c>
-      <c r="J58" s="45" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K58" s="46" t="inlineStr">
-        <is>
-          <t>https://www.mobilize.us/nh-bridge-brigade-for-democracy/event/888328/</t>
-        </is>
-      </c>
-      <c r="L58" s="47" t="inlineStr">
+      <c r="A58" s="48" t="inlineStr">
+        <is>
+          <t>mobilize:836661:1773442800</t>
+        </is>
+      </c>
+      <c r="B58" s="49" t="b">
+        <v>0</v>
+      </c>
+      <c r="C58" s="49" t="b">
+        <v>0</v>
+      </c>
+      <c r="D58" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-11T19:33:16</t>
+        </is>
+      </c>
+      <c r="E58" s="50" t="inlineStr">
+        <is>
+          <t>Bannering 101 (Palo Alto)</t>
+        </is>
+      </c>
+      <c r="F58" s="50" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G58" s="50" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="H58" s="49" t="inlineStr">
+        <is>
+          <t>Adobe Creek Bike and Pedestrian Bridge | Palo Alto, CA 94303</t>
+        </is>
+      </c>
+      <c r="I58" s="50" t="inlineStr">
+        <is>
+          <t>Stanford Shopping Center</t>
+        </is>
+      </c>
+      <c r="J58" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="K58" s="51" t="inlineStr">
+        <is>
+          <t>https://www.mobilize.us/ipaplus/event/836661/</t>
+        </is>
+      </c>
+      <c r="L58" s="52" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="48" t="inlineStr">
-        <is>
-          <t>mobilize:836661:1773442800</t>
-        </is>
-      </c>
-      <c r="B59" s="49" t="b">
-        <v>0</v>
-      </c>
-      <c r="C59" s="49" t="b">
-        <v>0</v>
-      </c>
-      <c r="D59" s="49" t="inlineStr">
-        <is>
-          <t>2026-03-11T19:33:16</t>
-        </is>
-      </c>
-      <c r="E59" s="50" t="inlineStr">
-        <is>
-          <t>Bannering 101 (Palo Alto)</t>
-        </is>
-      </c>
-      <c r="F59" s="50" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G59" s="50" t="inlineStr">
-        <is>
-          <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="H59" s="49" t="inlineStr">
-        <is>
-          <t>Adobe Creek Bike and Pedestrian Bridge | Palo Alto, CA 94303</t>
-        </is>
-      </c>
-      <c r="I59" s="50" t="inlineStr">
-        <is>
-          <t>Stanford Shopping Center</t>
-        </is>
-      </c>
-      <c r="J59" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="K59" s="51" t="inlineStr">
-        <is>
-          <t>https://www.mobilize.us/ipaplus/event/836661/</t>
-        </is>
-      </c>
-      <c r="L59" s="52" t="inlineStr">
-        <is>
-          <t>VISIBILITY_EVENT</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L59"/>
-  <conditionalFormatting sqref="A2:L59">
+  <autoFilter ref="A1:L58"/>
+  <conditionalFormatting sqref="A2:L58">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$B2=TRUE</formula>
     </cfRule>
@@ -5340,7 +5284,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5352,7 +5295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5456,7 +5399,7 @@
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F2" s="10" t="inlineStr">
@@ -5517,7 +5460,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F3" s="15" t="inlineStr">
@@ -5578,7 +5521,7 @@
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F4" s="15" t="inlineStr">
@@ -5639,7 +5582,7 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr">
@@ -5700,7 +5643,7 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F6" s="15" t="inlineStr">
@@ -5761,7 +5704,7 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F7" s="15" t="inlineStr">
@@ -5822,7 +5765,7 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
@@ -5883,7 +5826,7 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
@@ -5944,7 +5887,7 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -6005,7 +5948,7 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
@@ -6066,7 +6009,7 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
@@ -6127,7 +6070,7 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
@@ -6188,7 +6131,7 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
@@ -6249,7 +6192,7 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
@@ -6310,7 +6253,7 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
@@ -6371,7 +6314,7 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -6432,7 +6375,7 @@
       </c>
       <c r="E18" s="24" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F18" s="25" t="inlineStr">
@@ -6493,7 +6436,7 @@
       </c>
       <c r="E19" s="29" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F19" s="30" t="inlineStr">
@@ -6554,7 +6497,7 @@
       </c>
       <c r="E20" s="29" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F20" s="30" t="inlineStr">
@@ -6615,7 +6558,7 @@
       </c>
       <c r="E21" s="29" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F21" s="30" t="inlineStr">
@@ -6676,7 +6619,7 @@
       </c>
       <c r="E22" s="29" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F22" s="30" t="inlineStr">
@@ -6737,7 +6680,7 @@
       </c>
       <c r="E23" s="29" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F23" s="30" t="inlineStr">
@@ -6798,7 +6741,7 @@
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F24" s="30" t="inlineStr">
@@ -6859,7 +6802,7 @@
       </c>
       <c r="E25" s="29" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F25" s="30" t="inlineStr">
@@ -6920,7 +6863,7 @@
       </c>
       <c r="E26" s="29" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F26" s="30" t="inlineStr">
@@ -6981,7 +6924,7 @@
       </c>
       <c r="E27" s="29" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F27" s="30" t="inlineStr">
@@ -7042,7 +6985,7 @@
       </c>
       <c r="E28" s="29" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F28" s="30" t="inlineStr">
@@ -7103,7 +7046,7 @@
       </c>
       <c r="E29" s="29" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F29" s="30" t="inlineStr">
@@ -7164,7 +7107,7 @@
       </c>
       <c r="E30" s="29" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F30" s="30" t="inlineStr">
@@ -7225,7 +7168,7 @@
       </c>
       <c r="E31" s="29" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F31" s="30" t="inlineStr">
@@ -7286,7 +7229,7 @@
       </c>
       <c r="E32" s="29" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F32" s="30" t="inlineStr">
@@ -7347,7 +7290,7 @@
       </c>
       <c r="E33" s="34" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F33" s="35" t="inlineStr">
@@ -7408,7 +7351,7 @@
       </c>
       <c r="E34" s="39" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F34" s="40" t="inlineStr">
@@ -7469,7 +7412,7 @@
       </c>
       <c r="E35" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F35" s="45" t="inlineStr">
@@ -7530,7 +7473,7 @@
       </c>
       <c r="E36" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F36" s="45" t="inlineStr">
@@ -7591,7 +7534,7 @@
       </c>
       <c r="E37" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F37" s="45" t="inlineStr">
@@ -7652,7 +7595,7 @@
       </c>
       <c r="E38" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F38" s="45" t="inlineStr">
@@ -7713,7 +7656,7 @@
       </c>
       <c r="E39" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F39" s="45" t="inlineStr">
@@ -7774,7 +7717,7 @@
       </c>
       <c r="E40" s="54" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F40" s="55" t="inlineStr">
@@ -7835,7 +7778,7 @@
       </c>
       <c r="E41" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F41" s="45" t="inlineStr">
@@ -7880,7 +7823,7 @@
     <row r="42">
       <c r="A42" s="43" t="inlineStr">
         <is>
-          <t>mobilize:860202:1773360000</t>
+          <t>mobilize:824060:1773360000</t>
         </is>
       </c>
       <c r="B42" s="44" t="b">
@@ -7896,12 +7839,12 @@
       </c>
       <c r="E42" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F42" s="45" t="inlineStr">
         <is>
-          <t>Weekly Meade Ave Bridge Bannering Over I-805 | Thursday Afternoons</t>
+          <t>Visibility Brigade - North Park</t>
         </is>
       </c>
       <c r="G42" s="45" t="inlineStr">
@@ -7916,7 +7859,7 @@
       </c>
       <c r="I42" s="44" t="inlineStr">
         <is>
-          <t>Meade Ave Bridge Over I-805 | 4371 Boundary St | San Diego, CA 92116</t>
+          <t>Meade Ave bridge over I-805 in North Park | 4371 Boundary St | San Diego, CA 92116</t>
         </is>
       </c>
       <c r="J42" s="45" t="inlineStr">
@@ -7929,7 +7872,7 @@
       </c>
       <c r="L42" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/visibilitybrigadesandiego/event/860202/</t>
+          <t>https://www.mobilize.us/indivisible/event/824060/</t>
         </is>
       </c>
       <c r="M42" s="47" t="inlineStr">
@@ -7941,7 +7884,7 @@
     <row r="43">
       <c r="A43" s="43" t="inlineStr">
         <is>
-          <t>mobilize:824060:1773360000</t>
+          <t>mobilize:860202:1773360000</t>
         </is>
       </c>
       <c r="B43" s="44" t="b">
@@ -7957,12 +7900,12 @@
       </c>
       <c r="E43" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F43" s="45" t="inlineStr">
         <is>
-          <t>Visibility Brigade - North Park</t>
+          <t>Weekly Meade Ave Bridge Bannering Over I-805 | Thursday Afternoons</t>
         </is>
       </c>
       <c r="G43" s="45" t="inlineStr">
@@ -7977,7 +7920,7 @@
       </c>
       <c r="I43" s="44" t="inlineStr">
         <is>
-          <t>Meade Ave bridge over I-805 in North Park | 4371 Boundary St | San Diego, CA 92116</t>
+          <t>Meade Ave Bridge Over I-805 | 4371 Boundary St | San Diego, CA 92116</t>
         </is>
       </c>
       <c r="J43" s="45" t="inlineStr">
@@ -7990,7 +7933,7 @@
       </c>
       <c r="L43" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisible/event/824060/</t>
+          <t>https://www.mobilize.us/visibilitybrigadesandiego/event/860202/</t>
         </is>
       </c>
       <c r="M43" s="47" t="inlineStr">
@@ -8018,7 +7961,7 @@
       </c>
       <c r="E44" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F44" s="45" t="inlineStr">
@@ -8079,7 +8022,7 @@
       </c>
       <c r="E45" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F45" s="45" t="inlineStr">
@@ -8140,7 +8083,7 @@
       </c>
       <c r="E46" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F46" s="45" t="inlineStr">
@@ -8201,7 +8144,7 @@
       </c>
       <c r="E47" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F47" s="45" t="inlineStr">
@@ -8262,7 +8205,7 @@
       </c>
       <c r="E48" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F48" s="45" t="inlineStr">
@@ -8323,7 +8266,7 @@
       </c>
       <c r="E49" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F49" s="45" t="inlineStr">
@@ -8384,7 +8327,7 @@
       </c>
       <c r="E50" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F50" s="45" t="inlineStr">
@@ -8445,7 +8388,7 @@
       </c>
       <c r="E51" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F51" s="45" t="inlineStr">
@@ -8506,7 +8449,7 @@
       </c>
       <c r="E52" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F52" s="45" t="inlineStr">
@@ -8567,7 +8510,7 @@
       </c>
       <c r="E53" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F53" s="45" t="inlineStr">
@@ -8628,7 +8571,7 @@
       </c>
       <c r="E54" s="54" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F54" s="55" t="inlineStr">
@@ -8689,7 +8632,7 @@
       </c>
       <c r="E55" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F55" s="45" t="inlineStr">
@@ -8750,7 +8693,7 @@
       </c>
       <c r="E56" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F56" s="45" t="inlineStr">
@@ -8811,7 +8754,7 @@
       </c>
       <c r="E57" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F57" s="45" t="inlineStr">
@@ -8856,7 +8799,7 @@
     <row r="58">
       <c r="A58" s="43" t="inlineStr">
         <is>
-          <t>mobilize:899741:1773446400</t>
+          <t>mobilize:910556:1773880200</t>
         </is>
       </c>
       <c r="B58" s="44" t="b">
@@ -8867,57 +8810,57 @@
       </c>
       <c r="D58" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E58" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F58" s="45" t="inlineStr">
         <is>
-          <t>Refuse Fascism Fridays-Marysville (Other locations, see Details)</t>
+          <t>Drinks and Democracy hosted by the Folsom Area Democratic Club</t>
         </is>
       </c>
       <c r="G58" s="45" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H58" s="45" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>5:30 PM</t>
         </is>
       </c>
       <c r="I58" s="44" t="inlineStr">
         <is>
-          <t>Fourth Street &amp; State Avenue | Marysville, WA 98270</t>
+          <t>Frends in Folsom | 6608 Folsom-Auburn Rd | Folsom, CA 95630</t>
         </is>
       </c>
       <c r="J58" s="45" t="inlineStr">
         <is>
-          <t>Seattle Premium Outlets</t>
+          <t>Folsom Outlet Marketplace</t>
         </is>
       </c>
       <c r="K58" s="45" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="L58" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/snohomishcountyindivisible/event/899741/</t>
+          <t>https://www.mobilize.us/cadems/event/910556/</t>
         </is>
       </c>
       <c r="M58" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>MEET_GREET</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="43" t="inlineStr">
         <is>
-          <t>mobilize:910556:1773880200</t>
+          <t>mobilize:888328:1773594000</t>
         </is>
       </c>
       <c r="B59" s="44" t="b">
@@ -8928,178 +8871,117 @@
       </c>
       <c r="D59" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-09T15:27:00</t>
         </is>
       </c>
       <c r="E59" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T07:22:12</t>
+          <t>2026-03-12T08:22:04</t>
         </is>
       </c>
       <c r="F59" s="45" t="inlineStr">
         <is>
-          <t>Drinks and Democracy hosted by the Folsom Area Democratic Club</t>
+          <t>Exit 4 Nashua Popup Bridge Brigade</t>
         </is>
       </c>
       <c r="G59" s="45" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="H59" s="45" t="inlineStr">
         <is>
-          <t>5:30 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="I59" s="44" t="inlineStr">
         <is>
-          <t>Frends in Folsom | 6608 Folsom-Auburn Rd | Folsom, CA 95630</t>
+          <t>Nashua | Nashua, NH 03062</t>
         </is>
       </c>
       <c r="J59" s="45" t="inlineStr">
         <is>
-          <t>Folsom Outlet Marketplace</t>
+          <t>Pheasant Lane Mall</t>
         </is>
       </c>
       <c r="K59" s="45" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="L59" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/cadems/event/910556/</t>
+          <t>https://www.mobilize.us/nh-bridge-brigade-for-democracy/event/888328/</t>
         </is>
       </c>
       <c r="M59" s="47" t="inlineStr">
         <is>
-          <t>MEET_GREET</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="43" t="inlineStr">
-        <is>
-          <t>mobilize:888328:1773594000</t>
-        </is>
-      </c>
-      <c r="B60" s="44" t="b">
-        <v>0</v>
-      </c>
-      <c r="C60" s="44" t="b">
-        <v>0</v>
-      </c>
-      <c r="D60" s="44" t="inlineStr">
-        <is>
-          <t>2026-03-09T15:27:00</t>
-        </is>
-      </c>
-      <c r="E60" s="44" t="inlineStr">
-        <is>
-          <t>2026-03-12T07:22:12</t>
-        </is>
-      </c>
-      <c r="F60" s="45" t="inlineStr">
-        <is>
-          <t>Exit 4 Nashua Popup Bridge Brigade</t>
-        </is>
-      </c>
-      <c r="G60" s="45" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="H60" s="45" t="inlineStr">
-        <is>
-          <t>1:00 PM</t>
-        </is>
-      </c>
-      <c r="I60" s="44" t="inlineStr">
-        <is>
-          <t>Nashua | Nashua, NH 03062</t>
-        </is>
-      </c>
-      <c r="J60" s="45" t="inlineStr">
-        <is>
-          <t>Pheasant Lane Mall</t>
-        </is>
-      </c>
-      <c r="K60" s="45" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="L60" s="46" t="inlineStr">
-        <is>
-          <t>https://www.mobilize.us/nh-bridge-brigade-for-democracy/event/888328/</t>
-        </is>
-      </c>
-      <c r="M60" s="47" t="inlineStr">
+      <c r="A60" s="48" t="inlineStr">
+        <is>
+          <t>mobilize:836661:1773442800</t>
+        </is>
+      </c>
+      <c r="B60" s="49" t="b">
+        <v>0</v>
+      </c>
+      <c r="C60" s="49" t="b">
+        <v>0</v>
+      </c>
+      <c r="D60" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-11T19:33:16</t>
+        </is>
+      </c>
+      <c r="E60" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-12T08:22:04</t>
+        </is>
+      </c>
+      <c r="F60" s="50" t="inlineStr">
+        <is>
+          <t>Bannering 101 (Palo Alto)</t>
+        </is>
+      </c>
+      <c r="G60" s="50" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="H60" s="50" t="inlineStr">
+        <is>
+          <t>4:00 PM</t>
+        </is>
+      </c>
+      <c r="I60" s="49" t="inlineStr">
+        <is>
+          <t>Adobe Creek Bike and Pedestrian Bridge | Palo Alto, CA 94303</t>
+        </is>
+      </c>
+      <c r="J60" s="50" t="inlineStr">
+        <is>
+          <t>Stanford Shopping Center</t>
+        </is>
+      </c>
+      <c r="K60" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="L60" s="51" t="inlineStr">
+        <is>
+          <t>https://www.mobilize.us/ipaplus/event/836661/</t>
+        </is>
+      </c>
+      <c r="M60" s="52" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="48" t="inlineStr">
-        <is>
-          <t>mobilize:836661:1773442800</t>
-        </is>
-      </c>
-      <c r="B61" s="49" t="b">
-        <v>0</v>
-      </c>
-      <c r="C61" s="49" t="b">
-        <v>0</v>
-      </c>
-      <c r="D61" s="49" t="inlineStr">
-        <is>
-          <t>2026-03-11T19:33:16</t>
-        </is>
-      </c>
-      <c r="E61" s="49" t="inlineStr">
-        <is>
-          <t>2026-03-12T07:22:12</t>
-        </is>
-      </c>
-      <c r="F61" s="50" t="inlineStr">
-        <is>
-          <t>Bannering 101 (Palo Alto)</t>
-        </is>
-      </c>
-      <c r="G61" s="50" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="H61" s="50" t="inlineStr">
-        <is>
-          <t>4:00 PM</t>
-        </is>
-      </c>
-      <c r="I61" s="49" t="inlineStr">
-        <is>
-          <t>Adobe Creek Bike and Pedestrian Bridge | Palo Alto, CA 94303</t>
-        </is>
-      </c>
-      <c r="J61" s="50" t="inlineStr">
-        <is>
-          <t>Stanford Shopping Center</t>
-        </is>
-      </c>
-      <c r="K61" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="L61" s="51" t="inlineStr">
-        <is>
-          <t>https://www.mobilize.us/ipaplus/event/836661/</t>
-        </is>
-      </c>
-      <c r="M61" s="52" t="inlineStr">
-        <is>
-          <t>VISIBILITY_EVENT</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M61"/>
-  <conditionalFormatting sqref="A2:M61">
+  <autoFilter ref="A1:M60"/>
+  <conditionalFormatting sqref="A2:M60">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$B2=TRUE</formula>
     </cfRule>
@@ -9164,7 +9046,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9176,7 +9057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L143"/>
+  <dimension ref="A1:L144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -11106,7 +10987,7 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>mobilize:911213:1774731600</t>
+          <t>mobilize:902035:1774731600</t>
         </is>
       </c>
       <c r="B35" s="14" t="b">
@@ -11117,7 +10998,7 @@
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E35" s="15" t="inlineStr">
@@ -11137,7 +11018,7 @@
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>El Camino Real from Embarcadero to California Avenue | Embarcadero Road &amp; El Camino Real | Palo Alto, CA 94306</t>
+          <t>El Camino Real &amp; Embarcadero Road | Palo Alto, CA 94306</t>
         </is>
       </c>
       <c r="I35" s="15" t="inlineStr">
@@ -11150,7 +11031,7 @@
       </c>
       <c r="K35" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/ipaplus/event/911213/</t>
+          <t>https://www.mobilize.us/nokings/event/902035/</t>
         </is>
       </c>
       <c r="L35" s="17" t="inlineStr">
@@ -11162,7 +11043,7 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>mobilize:902035:1774731600</t>
+          <t>mobilize:911213:1774731600</t>
         </is>
       </c>
       <c r="B36" s="14" t="b">
@@ -11173,7 +11054,7 @@
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
@@ -11193,7 +11074,7 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>El Camino Real &amp; Embarcadero Road | Palo Alto, CA 94306</t>
+          <t>El Camino Real from Embarcadero to California Avenue | Embarcadero Road &amp; El Camino Real | Palo Alto, CA 94306</t>
         </is>
       </c>
       <c r="I36" s="15" t="inlineStr">
@@ -11206,7 +11087,7 @@
       </c>
       <c r="K36" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/902035/</t>
+          <t>https://www.mobilize.us/ipaplus/event/911213/</t>
         </is>
       </c>
       <c r="L36" s="17" t="inlineStr">
@@ -11554,7 +11435,7 @@
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>mobilize:901078:1774735200</t>
+          <t>mobilize:905855:1774720800</t>
         </is>
       </c>
       <c r="B43" s="14" t="b">
@@ -11570,7 +11451,7 @@
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>NO KINGS Santa Rosa, CA - SRJC March to Old Courthouse Square</t>
+          <t>NO Kings Richfield-66th St Sidewalk Rally</t>
         </is>
       </c>
       <c r="F43" s="15" t="inlineStr">
@@ -11580,17 +11461,17 @@
       </c>
       <c r="G43" s="15" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>SRJC | Mendocino Ave &amp; Carr Street | Santa Rosa, CA 95401</t>
+          <t>Penn Avenue South &amp; West 66th Street, West 66th Street and Lyndale Ave | Richfield, MN 55423</t>
         </is>
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
-          <t>Santa Rosa Plaza</t>
+          <t>Southdale Center</t>
         </is>
       </c>
       <c r="J43" s="15" t="n">
@@ -11598,7 +11479,7 @@
       </c>
       <c r="K43" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/901078/</t>
+          <t>https://www.mobilize.us/nokings/event/905855/</t>
         </is>
       </c>
       <c r="L43" s="17" t="inlineStr">
@@ -11666,7 +11547,7 @@
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>mobilize:905855:1774720800</t>
+          <t>mobilize:901078:1774735200</t>
         </is>
       </c>
       <c r="B45" s="14" t="b">
@@ -11682,7 +11563,7 @@
       </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>NO Kings Richfield-66th St Sidewalk Rally</t>
+          <t>NO KINGS Santa Rosa, CA - SRJC March to Old Courthouse Square</t>
         </is>
       </c>
       <c r="F45" s="15" t="inlineStr">
@@ -11692,17 +11573,17 @@
       </c>
       <c r="G45" s="15" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>Penn Avenue South &amp; West 66th Street, West 66th Street and Lyndale Ave | Richfield, MN 55423</t>
+          <t>SRJC | Mendocino Ave &amp; Carr Street | Santa Rosa, CA 95401</t>
         </is>
       </c>
       <c r="I45" s="15" t="inlineStr">
         <is>
-          <t>Southdale Center</t>
+          <t>Santa Rosa Plaza</t>
         </is>
       </c>
       <c r="J45" s="15" t="n">
@@ -11710,7 +11591,7 @@
       </c>
       <c r="K45" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/905855/</t>
+          <t>https://www.mobilize.us/nokings/event/901078/</t>
         </is>
       </c>
       <c r="L45" s="17" t="inlineStr">
@@ -12170,7 +12051,7 @@
     <row r="54">
       <c r="A54" s="28" t="inlineStr">
         <is>
-          <t>mobilize:903157:1774717200</t>
+          <t>mobilize:904754:1774720800</t>
         </is>
       </c>
       <c r="B54" s="29" t="b">
@@ -12186,7 +12067,7 @@
       </c>
       <c r="E54" s="30" t="inlineStr">
         <is>
-          <t>NO KINGS EL PASO</t>
+          <t>NO KINGS - A JOYFUL DEMONSTRATION - MILPITAS CA</t>
         </is>
       </c>
       <c r="F54" s="30" t="inlineStr">
@@ -12201,12 +12082,12 @@
       </c>
       <c r="H54" s="29" t="inlineStr">
         <is>
-          <t>Edgemere Linear Park | Edgemere Boulevard &amp; Airway Boulevard | El Paso, TX 79925</t>
+          <t>North Milpitas Boulevard &amp; Calaveras Boulevard | Milpitas, CA 95035</t>
         </is>
       </c>
       <c r="I54" s="30" t="inlineStr">
         <is>
-          <t>Cielo Vista Mall</t>
+          <t>Great Mall</t>
         </is>
       </c>
       <c r="J54" s="30" t="n">
@@ -12214,19 +12095,19 @@
       </c>
       <c r="K54" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/903157/</t>
+          <t>https://www.mobilize.us/nokings/event/904754/</t>
         </is>
       </c>
       <c r="L54" s="32" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="28" t="inlineStr">
         <is>
-          <t>mobilize:904754:1774720800</t>
+          <t>mobilize:903157:1774717200</t>
         </is>
       </c>
       <c r="B55" s="29" t="b">
@@ -12242,7 +12123,7 @@
       </c>
       <c r="E55" s="30" t="inlineStr">
         <is>
-          <t>NO KINGS - A JOYFUL DEMONSTRATION - MILPITAS CA</t>
+          <t>NO KINGS EL PASO</t>
         </is>
       </c>
       <c r="F55" s="30" t="inlineStr">
@@ -12257,12 +12138,12 @@
       </c>
       <c r="H55" s="29" t="inlineStr">
         <is>
-          <t>North Milpitas Boulevard &amp; Calaveras Boulevard | Milpitas, CA 95035</t>
+          <t>Edgemere Linear Park | Edgemere Boulevard &amp; Airway Boulevard | El Paso, TX 79925</t>
         </is>
       </c>
       <c r="I55" s="30" t="inlineStr">
         <is>
-          <t>Great Mall</t>
+          <t>Cielo Vista Mall</t>
         </is>
       </c>
       <c r="J55" s="30" t="n">
@@ -12270,12 +12151,12 @@
       </c>
       <c r="K55" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/904754/</t>
+          <t>https://www.mobilize.us/nokings/event/903157/</t>
         </is>
       </c>
       <c r="L55" s="32" t="inlineStr">
         <is>
-          <t>VISIBILITY_EVENT</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
@@ -13234,7 +13115,7 @@
     <row r="73">
       <c r="A73" s="28" t="inlineStr">
         <is>
-          <t>mobilize:909439:1774717200</t>
+          <t>mobilize:919598:1774717200</t>
         </is>
       </c>
       <c r="B73" s="29" t="b">
@@ -13250,7 +13131,7 @@
       </c>
       <c r="E73" s="30" t="inlineStr">
         <is>
-          <t>No Kings  Grover Beach, CA</t>
+          <t>No Kings III Grover Beach</t>
         </is>
       </c>
       <c r="F73" s="30" t="inlineStr">
@@ -13265,7 +13146,7 @@
       </c>
       <c r="H73" s="29" t="inlineStr">
         <is>
-          <t>GROVER BEACH, CA | North Oak Park Boulevard &amp; West Grand Avenue | Grover Beach, CA 93433</t>
+          <t>Grover Beach | East Grand Avenue &amp; North Oak Park Boulevard | Grover Beach, CA 93433</t>
         </is>
       </c>
       <c r="I73" s="30" t="inlineStr">
@@ -13278,19 +13159,19 @@
       </c>
       <c r="K73" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisiblenipomo/event/909439/</t>
+          <t>https://www.mobilize.us/indivisiblenipomo/event/919598/</t>
         </is>
       </c>
       <c r="L73" s="32" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>COMMUNITY</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="28" t="inlineStr">
         <is>
-          <t>mobilize:919479:1774717200</t>
+          <t>mobilize:909439:1774717200</t>
         </is>
       </c>
       <c r="B74" s="29" t="b">
@@ -13306,7 +13187,7 @@
       </c>
       <c r="E74" s="30" t="inlineStr">
         <is>
-          <t>No Kings Grover Beach, CA</t>
+          <t>No Kings  Grover Beach, CA</t>
         </is>
       </c>
       <c r="F74" s="30" t="inlineStr">
@@ -13321,7 +13202,7 @@
       </c>
       <c r="H74" s="29" t="inlineStr">
         <is>
-          <t>Grover Beach | North Oak Park Boulevard &amp; West Grand Avenue | Grover Beach, CA 93433</t>
+          <t>GROVER BEACH, CA | North Oak Park Boulevard &amp; West Grand Avenue | Grover Beach, CA 93433</t>
         </is>
       </c>
       <c r="I74" s="30" t="inlineStr">
@@ -13334,7 +13215,7 @@
       </c>
       <c r="K74" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisiblenipomo/event/919479/</t>
+          <t>https://www.mobilize.us/indivisiblenipomo/event/909439/</t>
         </is>
       </c>
       <c r="L74" s="32" t="inlineStr">
@@ -13346,7 +13227,7 @@
     <row r="75">
       <c r="A75" s="28" t="inlineStr">
         <is>
-          <t>mobilize:919598:1774717200</t>
+          <t>mobilize:919479:1774717200</t>
         </is>
       </c>
       <c r="B75" s="29" t="b">
@@ -13362,7 +13243,7 @@
       </c>
       <c r="E75" s="30" t="inlineStr">
         <is>
-          <t>No Kings III Grover Beach</t>
+          <t>No Kings Grover Beach, CA</t>
         </is>
       </c>
       <c r="F75" s="30" t="inlineStr">
@@ -13377,7 +13258,7 @@
       </c>
       <c r="H75" s="29" t="inlineStr">
         <is>
-          <t>Grover Beach | East Grand Avenue &amp; North Oak Park Boulevard | Grover Beach, CA 93433</t>
+          <t>Grover Beach | North Oak Park Boulevard &amp; West Grand Avenue | Grover Beach, CA 93433</t>
         </is>
       </c>
       <c r="I75" s="30" t="inlineStr">
@@ -13390,19 +13271,19 @@
       </c>
       <c r="K75" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisiblenipomo/event/919598/</t>
+          <t>https://www.mobilize.us/indivisiblenipomo/event/919479/</t>
         </is>
       </c>
       <c r="L75" s="32" t="inlineStr">
         <is>
-          <t>COMMUNITY</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="28" t="inlineStr">
         <is>
-          <t>mobilize:905436:1774720800</t>
+          <t>mobilize:918067:1774656000</t>
         </is>
       </c>
       <c r="B76" s="29" t="b">
@@ -13413,52 +13294,52 @@
       </c>
       <c r="D76" s="29" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E76" s="30" t="inlineStr">
         <is>
-          <t>NO KINGS with Signs of Democracy Arlington</t>
+          <t>NO KINGS Sign Making Party</t>
         </is>
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G76" s="30" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="H76" s="29" t="inlineStr">
         <is>
-          <t>2710 S Glebe Rd | Arlington, VA 22206</t>
+          <t>China Towne Ceramics | 4007 Yucan Dr | Springfield, IL 62711</t>
         </is>
       </c>
       <c r="I76" s="30" t="inlineStr">
         <is>
-          <t>Fashion Center at Pentagon City</t>
+          <t>White Oaks Mall</t>
         </is>
       </c>
       <c r="J76" s="30" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="K76" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/905436/</t>
+          <t>https://www.mobilize.us/indivisible/event/918067/</t>
         </is>
       </c>
       <c r="L76" s="32" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>COMMUNITY</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="28" t="inlineStr">
         <is>
-          <t>mobilize:900717:1774710000</t>
+          <t>mobilize:905436:1774720800</t>
         </is>
       </c>
       <c r="B77" s="29" t="b">
@@ -13474,7 +13355,7 @@
       </c>
       <c r="E77" s="30" t="inlineStr">
         <is>
-          <t>NO KINGS MIAMI - CALLE OCHO!!!</t>
+          <t>NO KINGS with Signs of Democracy Arlington</t>
         </is>
       </c>
       <c r="F77" s="30" t="inlineStr">
@@ -13484,25 +13365,25 @@
       </c>
       <c r="G77" s="30" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="H77" s="29" t="inlineStr">
         <is>
-          <t>Outside Maximo Gomez Park (Parque del Dominó) | 801-817 SW 15th Ave | Miami, FL 33135</t>
+          <t>2710 S Glebe Rd | Arlington, VA 22206</t>
         </is>
       </c>
       <c r="I77" s="30" t="inlineStr">
         <is>
-          <t>Brickell City Centre</t>
+          <t>Fashion Center at Pentagon City</t>
         </is>
       </c>
       <c r="J77" s="30" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="K77" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/900717/</t>
+          <t>https://www.mobilize.us/nokings/event/905436/</t>
         </is>
       </c>
       <c r="L77" s="32" t="inlineStr">
@@ -13514,7 +13395,7 @@
     <row r="78">
       <c r="A78" s="28" t="inlineStr">
         <is>
-          <t>mobilize:908884:1774713600</t>
+          <t>mobilize:900717:1774710000</t>
         </is>
       </c>
       <c r="B78" s="29" t="b">
@@ -13530,7 +13411,7 @@
       </c>
       <c r="E78" s="30" t="inlineStr">
         <is>
-          <t>NO KINGS Springfield Missouri</t>
+          <t>NO KINGS MIAMI - CALLE OCHO!!!</t>
         </is>
       </c>
       <c r="F78" s="30" t="inlineStr">
@@ -13545,12 +13426,12 @@
       </c>
       <c r="H78" s="29" t="inlineStr">
         <is>
-          <t>S Campbell Ave | Springfield, MO 65807</t>
+          <t>Outside Maximo Gomez Park (Parque del Dominó) | 801-817 SW 15th Ave | Miami, FL 33135</t>
         </is>
       </c>
       <c r="I78" s="30" t="inlineStr">
         <is>
-          <t>Battlefield Mall</t>
+          <t>Brickell City Centre</t>
         </is>
       </c>
       <c r="J78" s="30" t="n">
@@ -13558,7 +13439,7 @@
       </c>
       <c r="K78" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/908884/</t>
+          <t>https://www.mobilize.us/nokings/event/900717/</t>
         </is>
       </c>
       <c r="L78" s="32" t="inlineStr">
@@ -13570,7 +13451,7 @@
     <row r="79">
       <c r="A79" s="28" t="inlineStr">
         <is>
-          <t>mobilize:919145:1774717200</t>
+          <t>mobilize:908884:1774713600</t>
         </is>
       </c>
       <c r="B79" s="29" t="b">
@@ -13581,12 +13462,12 @@
       </c>
       <c r="D79" s="29" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E79" s="30" t="inlineStr">
         <is>
-          <t>No Kings Hands Across Arlington Rally - Arlington Dems Meetup</t>
+          <t>NO KINGS Springfield Missouri</t>
         </is>
       </c>
       <c r="F79" s="30" t="inlineStr">
@@ -13596,37 +13477,37 @@
       </c>
       <c r="G79" s="30" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="H79" s="29" t="inlineStr">
         <is>
-          <t>South Glebe Road &amp; Columbia Pike | Arlington, VA 22204</t>
+          <t>S Campbell Ave | Springfield, MO 65807</t>
         </is>
       </c>
       <c r="I79" s="30" t="inlineStr">
         <is>
-          <t>Fashion Center at Pentagon City</t>
+          <t>Battlefield Mall</t>
         </is>
       </c>
       <c r="J79" s="30" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="K79" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/arlingtondems/event/919145/</t>
+          <t>https://www.mobilize.us/nokings/event/908884/</t>
         </is>
       </c>
       <c r="L79" s="32" t="inlineStr">
         <is>
-          <t>COMMUNITY</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="28" t="inlineStr">
         <is>
-          <t>mobilize:901076:1774713600</t>
+          <t>mobilize:919145:1774717200</t>
         </is>
       </c>
       <c r="B80" s="29" t="b">
@@ -13642,7 +13523,7 @@
       </c>
       <c r="E80" s="30" t="inlineStr">
         <is>
-          <t>NO KINGS March from Torrance High School to City Hall</t>
+          <t>No Kings Hands Across Arlington Rally - Arlington Dems Meetup</t>
         </is>
       </c>
       <c r="F80" s="30" t="inlineStr">
@@ -13652,37 +13533,37 @@
       </c>
       <c r="G80" s="30" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="H80" s="29" t="inlineStr">
         <is>
-          <t>El Prado Park (Directly across from Torrance High) | 1563-1599 Arlington Ave | Torrance, CA 90501</t>
+          <t>South Glebe Road &amp; Columbia Pike | Arlington, VA 22204</t>
         </is>
       </c>
       <c r="I80" s="30" t="inlineStr">
         <is>
-          <t>Del Amo Fashion Center</t>
+          <t>Fashion Center at Pentagon City</t>
         </is>
       </c>
       <c r="J80" s="30" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="K80" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisiblesouthbayla/event/901076/</t>
+          <t>https://www.mobilize.us/arlingtondems/event/919145/</t>
         </is>
       </c>
       <c r="L80" s="32" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>COMMUNITY</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="28" t="inlineStr">
         <is>
-          <t>mobilize:909010:1774706400</t>
+          <t>mobilize:901076:1774713600</t>
         </is>
       </c>
       <c r="B81" s="29" t="b">
@@ -13693,12 +13574,12 @@
       </c>
       <c r="D81" s="29" t="inlineStr">
         <is>
-          <t>2026-03-11T03:29:59</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E81" s="30" t="inlineStr">
         <is>
-          <t>NO KINGS Calhoun</t>
+          <t>NO KINGS March from Torrance High School to City Hall</t>
         </is>
       </c>
       <c r="F81" s="30" t="inlineStr">
@@ -13708,25 +13589,25 @@
       </c>
       <c r="G81" s="30" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="H81" s="29" t="inlineStr">
         <is>
-          <t>Gordon County Courthouse | S Wall St | Calhoun, GA 30701</t>
+          <t>El Prado Park (Directly across from Torrance High) | 1563-1599 Arlington Ave | Torrance, CA 90501</t>
         </is>
       </c>
       <c r="I81" s="30" t="inlineStr">
         <is>
-          <t>Calhoun Outlet Marketplace</t>
+          <t>Del Amo Fashion Center</t>
         </is>
       </c>
       <c r="J81" s="30" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="K81" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/909010/</t>
+          <t>https://www.mobilize.us/indivisiblesouthbayla/event/901076/</t>
         </is>
       </c>
       <c r="L81" s="32" t="inlineStr">
@@ -13738,7 +13619,7 @@
     <row r="82">
       <c r="A82" s="28" t="inlineStr">
         <is>
-          <t>mobilize:900871:1774724400</t>
+          <t>mobilize:909010:1774706400</t>
         </is>
       </c>
       <c r="B82" s="29" t="b">
@@ -13749,12 +13630,12 @@
       </c>
       <c r="D82" s="29" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-11T03:29:59</t>
         </is>
       </c>
       <c r="E82" s="30" t="inlineStr">
         <is>
-          <t>NO KINGS Petaluma, CA</t>
+          <t>NO KINGS Calhoun</t>
         </is>
       </c>
       <c r="F82" s="30" t="inlineStr">
@@ -13764,37 +13645,37 @@
       </c>
       <c r="G82" s="30" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="H82" s="29" t="inlineStr">
         <is>
-          <t>Walnut Park | D St. and Petaluma Blvd S. | Petaluma, CA 94952</t>
+          <t>Gordon County Courthouse | S Wall St | Calhoun, GA 30701</t>
         </is>
       </c>
       <c r="I82" s="30" t="inlineStr">
         <is>
-          <t>Petaluma Village Premium Outlets</t>
+          <t>Calhoun Outlet Marketplace</t>
         </is>
       </c>
       <c r="J82" s="30" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="K82" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/900871/</t>
+          <t>https://www.mobilize.us/nokings/event/909010/</t>
         </is>
       </c>
       <c r="L82" s="32" t="inlineStr">
         <is>
-          <t>VISIBILITY_EVENT</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="28" t="inlineStr">
         <is>
-          <t>mobilize:907481:1774717200</t>
+          <t>mobilize:900871:1774724400</t>
         </is>
       </c>
       <c r="B83" s="29" t="b">
@@ -13810,7 +13691,7 @@
       </c>
       <c r="E83" s="30" t="inlineStr">
         <is>
-          <t>NO KINGS Greenwood</t>
+          <t>NO KINGS Petaluma, CA</t>
         </is>
       </c>
       <c r="F83" s="30" t="inlineStr">
@@ -13820,37 +13701,37 @@
       </c>
       <c r="G83" s="30" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="H83" s="29" t="inlineStr">
         <is>
-          <t>Greenwood Fieldhouse | 411 S Madison Ave | Greenwood, IN 46142</t>
+          <t>Walnut Park | D St. and Petaluma Blvd S. | Petaluma, CA 94952</t>
         </is>
       </c>
       <c r="I83" s="30" t="inlineStr">
         <is>
-          <t>Greenwood Park Mall</t>
+          <t>Petaluma Village Premium Outlets</t>
         </is>
       </c>
       <c r="J83" s="30" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="K83" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/907481/</t>
+          <t>https://www.mobilize.us/nokings/event/900871/</t>
         </is>
       </c>
       <c r="L83" s="32" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="28" t="inlineStr">
         <is>
-          <t>mobilize:902030:1774710000</t>
+          <t>mobilize:907481:1774717200</t>
         </is>
       </c>
       <c r="B84" s="29" t="b">
@@ -13866,7 +13747,7 @@
       </c>
       <c r="E84" s="30" t="inlineStr">
         <is>
-          <t>NO KINGS Tyngsboro Indivisible</t>
+          <t>NO KINGS Greenwood</t>
         </is>
       </c>
       <c r="F84" s="30" t="inlineStr">
@@ -13876,25 +13757,25 @@
       </c>
       <c r="G84" s="30" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="H84" s="29" t="inlineStr">
         <is>
-          <t>Tyngsboro Town Center across from the Bridge | 216 Middlesex Rd | Tyngsborough, MA 01879</t>
+          <t>Greenwood Fieldhouse | 411 S Madison Ave | Greenwood, IN 46142</t>
         </is>
       </c>
       <c r="I84" s="30" t="inlineStr">
         <is>
-          <t>Pheasant Lane Mall</t>
+          <t>Greenwood Park Mall</t>
         </is>
       </c>
       <c r="J84" s="30" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="K84" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/902030/</t>
+          <t>https://www.mobilize.us/nokings/event/907481/</t>
         </is>
       </c>
       <c r="L84" s="32" t="inlineStr">
@@ -13906,7 +13787,7 @@
     <row r="85">
       <c r="A85" s="28" t="inlineStr">
         <is>
-          <t>mobilize:914267:1774704600</t>
+          <t>mobilize:902030:1774710000</t>
         </is>
       </c>
       <c r="B85" s="29" t="b">
@@ -13922,7 +13803,7 @@
       </c>
       <c r="E85" s="30" t="inlineStr">
         <is>
-          <t>NO KINGS Jersey City &amp; Hoboken March &amp; Rally</t>
+          <t>NO KINGS Tyngsboro Indivisible</t>
         </is>
       </c>
       <c r="F85" s="30" t="inlineStr">
@@ -13932,25 +13813,25 @@
       </c>
       <c r="G85" s="30" t="inlineStr">
         <is>
-          <t>9:30 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="H85" s="29" t="inlineStr">
         <is>
-          <t>Newport Green Park | 14th Street | Jersey City, NJ 07030</t>
+          <t>Tyngsboro Town Center across from the Bridge | 216 Middlesex Rd | Tyngsborough, MA 01879</t>
         </is>
       </c>
       <c r="I85" s="30" t="inlineStr">
         <is>
-          <t>Newport Centre</t>
+          <t>Pheasant Lane Mall</t>
         </is>
       </c>
       <c r="J85" s="30" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="K85" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/914267/</t>
+          <t>https://www.mobilize.us/nokings/event/902030/</t>
         </is>
       </c>
       <c r="L85" s="32" t="inlineStr">
@@ -13962,7 +13843,7 @@
     <row r="86">
       <c r="A86" s="28" t="inlineStr">
         <is>
-          <t>mobilize:916537:1774706400</t>
+          <t>mobilize:914267:1774704600</t>
         </is>
       </c>
       <c r="B86" s="29" t="b">
@@ -13973,12 +13854,12 @@
       </c>
       <c r="D86" s="29" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E86" s="30" t="inlineStr">
         <is>
-          <t>NO KINGS: Greenburgh, NY</t>
+          <t>NO KINGS Jersey City &amp; Hoboken March &amp; Rally</t>
         </is>
       </c>
       <c r="F86" s="30" t="inlineStr">
@@ -13988,25 +13869,25 @@
       </c>
       <c r="G86" s="30" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>9:30 AM</t>
         </is>
       </c>
       <c r="H86" s="29" t="inlineStr">
         <is>
-          <t>Town of Greenburgh Town Hall | 177 Hillside Ave | White Plains, NY 10607</t>
+          <t>Newport Green Park | 14th Street | Jersey City, NJ 07030</t>
         </is>
       </c>
       <c r="I86" s="30" t="inlineStr">
         <is>
-          <t>The Westchester</t>
+          <t>Newport Centre</t>
         </is>
       </c>
       <c r="J86" s="30" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="K86" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/916537/</t>
+          <t>https://www.mobilize.us/nokings/event/914267/</t>
         </is>
       </c>
       <c r="L86" s="32" t="inlineStr">
@@ -14018,7 +13899,7 @@
     <row r="87">
       <c r="A87" s="28" t="inlineStr">
         <is>
-          <t>mobilize:901796:1774717200</t>
+          <t>mobilize:916537:1774706400</t>
         </is>
       </c>
       <c r="B87" s="29" t="b">
@@ -14029,12 +13910,12 @@
       </c>
       <c r="D87" s="29" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E87" s="30" t="inlineStr">
         <is>
-          <t>No Kings- WOFA HANDS ACROSS ARLINGTON</t>
+          <t>NO KINGS: Greenburgh, NY</t>
         </is>
       </c>
       <c r="F87" s="30" t="inlineStr">
@@ -14044,17 +13925,17 @@
       </c>
       <c r="G87" s="30" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="H87" s="29" t="inlineStr">
         <is>
-          <t>125 S Old Glebe Rd | Arlington, VA 22204</t>
+          <t>Town of Greenburgh Town Hall | 177 Hillside Ave | White Plains, NY 10607</t>
         </is>
       </c>
       <c r="I87" s="30" t="inlineStr">
         <is>
-          <t>Fashion Center at Pentagon City</t>
+          <t>The Westchester</t>
         </is>
       </c>
       <c r="J87" s="30" t="n">
@@ -14062,234 +13943,234 @@
       </c>
       <c r="K87" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/901796/</t>
+          <t>https://www.mobilize.us/nokings/event/916537/</t>
         </is>
       </c>
       <c r="L87" s="32" t="inlineStr">
         <is>
-          <t>VISIBILITY_EVENT</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="28" t="inlineStr">
         <is>
+          <t>mobilize:901796:1774717200</t>
+        </is>
+      </c>
+      <c r="B88" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="C88" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D88" s="29" t="inlineStr">
+        <is>
+          <t>2026-03-08T07:16:44</t>
+        </is>
+      </c>
+      <c r="E88" s="30" t="inlineStr">
+        <is>
+          <t>No Kings- WOFA HANDS ACROSS ARLINGTON</t>
+        </is>
+      </c>
+      <c r="F88" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G88" s="30" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="H88" s="29" t="inlineStr">
+        <is>
+          <t>125 S Old Glebe Rd | Arlington, VA 22204</t>
+        </is>
+      </c>
+      <c r="I88" s="30" t="inlineStr">
+        <is>
+          <t>Fashion Center at Pentagon City</t>
+        </is>
+      </c>
+      <c r="J88" s="30" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="K88" s="31" t="inlineStr">
+        <is>
+          <t>https://www.mobilize.us/nokings/event/901796/</t>
+        </is>
+      </c>
+      <c r="L88" s="32" t="inlineStr">
+        <is>
+          <t>VISIBILITY_EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="28" t="inlineStr">
+        <is>
           <t>mobilize:906951:1774717200</t>
         </is>
       </c>
-      <c r="B88" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="C88" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="D88" s="29" t="inlineStr">
+      <c r="B89" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="C89" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D89" s="29" t="inlineStr">
         <is>
           <t>2026-03-08T07:16:44</t>
         </is>
       </c>
-      <c r="E88" s="30" t="inlineStr">
+      <c r="E89" s="30" t="inlineStr">
         <is>
           <t>NO KINGS TEANECK</t>
         </is>
       </c>
-      <c r="F88" s="30" t="inlineStr">
+      <c r="F89" s="30" t="inlineStr">
         <is>
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="G88" s="30" t="inlineStr">
+      <c r="G89" s="30" t="inlineStr">
         <is>
           <t>1:00 PM</t>
         </is>
       </c>
-      <c r="H88" s="29" t="inlineStr">
+      <c r="H89" s="29" t="inlineStr">
         <is>
           <t>Teaneck | Teaneck Municipal Green(intersection of Teaneck Road and Cedar Lane) | Teaneck, NJ 07666</t>
         </is>
       </c>
-      <c r="I88" s="30" t="inlineStr">
+      <c r="I89" s="30" t="inlineStr">
         <is>
           <t>The Shops at Riverside</t>
         </is>
       </c>
-      <c r="J88" s="30" t="n">
+      <c r="J89" s="30" t="n">
         <v>1.96</v>
       </c>
-      <c r="K88" s="31" t="inlineStr">
+      <c r="K89" s="31" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/nokings/event/906951/</t>
         </is>
       </c>
-      <c r="L88" s="32" t="inlineStr">
+      <c r="L89" s="32" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="33" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="33" t="inlineStr">
         <is>
           <t>mobilize:905416:1774713600</t>
         </is>
       </c>
-      <c r="B89" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="C89" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="D89" s="34" t="inlineStr">
+      <c r="B90" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="C90" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="D90" s="34" t="inlineStr">
         <is>
           <t>2026-03-08T07:16:44</t>
         </is>
       </c>
-      <c r="E89" s="35" t="inlineStr">
+      <c r="E90" s="35" t="inlineStr">
         <is>
           <t>NO KINGS Defend Our Democracy Marana</t>
         </is>
       </c>
-      <c r="F89" s="35" t="inlineStr">
+      <c r="F90" s="35" t="inlineStr">
         <is>
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="G89" s="35" t="inlineStr">
+      <c r="G90" s="35" t="inlineStr">
         <is>
           <t>9:00 AM</t>
         </is>
       </c>
-      <c r="H89" s="34" t="inlineStr">
+      <c r="H90" s="34" t="inlineStr">
         <is>
           <t>North Silverbell Road &amp; North Cortaro Road | Marana, AZ 85743</t>
         </is>
       </c>
-      <c r="I89" s="35" t="inlineStr">
+      <c r="I90" s="35" t="inlineStr">
         <is>
           <t>Tucson Premium Outlets</t>
         </is>
       </c>
-      <c r="J89" s="35" t="n">
+      <c r="J90" s="35" t="n">
         <v>1.97</v>
       </c>
-      <c r="K89" s="36" t="inlineStr">
+      <c r="K90" s="36" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/nokings/event/905416/</t>
         </is>
       </c>
-      <c r="L89" s="37" t="inlineStr">
+      <c r="L90" s="37" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="38" t="inlineStr">
-        <is>
-          <t>mobilize:901723:1774702800</t>
-        </is>
-      </c>
-      <c r="B90" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="C90" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="D90" s="39" t="inlineStr">
-        <is>
-          <t>2026-03-08T07:16:44</t>
-        </is>
-      </c>
-      <c r="E90" s="40" t="inlineStr">
-        <is>
-          <t>NO KINGS CORAL SPRINGS</t>
-        </is>
-      </c>
-      <c r="F90" s="40" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="38" t="inlineStr">
+        <is>
+          <t>mobilize:918765:1774704600</t>
+        </is>
+      </c>
+      <c r="B91" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="C91" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="D91" s="39" t="inlineStr">
+        <is>
+          <t>2026-03-12T05:20:25</t>
+        </is>
+      </c>
+      <c r="E91" s="40" t="inlineStr">
+        <is>
+          <t>Coral Springs NO KINGS with Oliver Larkin Team</t>
+        </is>
+      </c>
+      <c r="F91" s="40" t="inlineStr">
         <is>
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="G90" s="40" t="inlineStr">
-        <is>
-          <t>9:00 AM</t>
-        </is>
-      </c>
-      <c r="H90" s="39" t="inlineStr">
-        <is>
-          <t>University Dr. and Sample Rd. | 3151 N University Dr | Coral Springs, FL 33065</t>
-        </is>
-      </c>
-      <c r="I90" s="40" t="inlineStr">
+      <c r="G91" s="40" t="inlineStr">
+        <is>
+          <t>9:30 AM</t>
+        </is>
+      </c>
+      <c r="H91" s="39" t="inlineStr">
+        <is>
+          <t>3151 N University Dr | Coral Springs, FL 33065</t>
+        </is>
+      </c>
+      <c r="I91" s="40" t="inlineStr">
         <is>
           <t>Coral Square</t>
         </is>
       </c>
-      <c r="J90" s="40" t="n">
+      <c r="J91" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="K90" s="41" t="inlineStr">
-        <is>
-          <t>https://www.mobilize.us/nokings/event/901723/</t>
-        </is>
-      </c>
-      <c r="L90" s="42" t="inlineStr">
-        <is>
-          <t>RALLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="43" t="inlineStr">
-        <is>
-          <t>mobilize:918765:1774704600</t>
-        </is>
-      </c>
-      <c r="B91" s="44" t="b">
-        <v>0</v>
-      </c>
-      <c r="C91" s="44" t="b">
-        <v>0</v>
-      </c>
-      <c r="D91" s="44" t="inlineStr">
-        <is>
-          <t>2026-03-12T05:20:25</t>
-        </is>
-      </c>
-      <c r="E91" s="45" t="inlineStr">
-        <is>
-          <t>Coral Springs NO KINGS with Oliver Larkin Team</t>
-        </is>
-      </c>
-      <c r="F91" s="45" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G91" s="45" t="inlineStr">
-        <is>
-          <t>9:30 AM</t>
-        </is>
-      </c>
-      <c r="H91" s="44" t="inlineStr">
-        <is>
-          <t>3151 N University Dr | Coral Springs, FL 33065</t>
-        </is>
-      </c>
-      <c r="I91" s="45" t="inlineStr">
-        <is>
-          <t>Coral Square</t>
-        </is>
-      </c>
-      <c r="J91" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="K91" s="46" t="inlineStr">
+      <c r="K91" s="41" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/oliverforcongress/event/918765/</t>
         </is>
       </c>
-      <c r="L91" s="47" t="inlineStr">
+      <c r="L91" s="42" t="inlineStr">
         <is>
           <t>RALLY</t>
         </is>
@@ -14298,7 +14179,7 @@
     <row r="92">
       <c r="A92" s="43" t="inlineStr">
         <is>
-          <t>mobilize:919136:1773619200</t>
+          <t>mobilize:901723:1774702800</t>
         </is>
       </c>
       <c r="B92" s="44" t="b">
@@ -14309,52 +14190,52 @@
       </c>
       <c r="D92" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E92" s="45" t="inlineStr">
         <is>
-          <t>Channel No Kings Day into Real Impact</t>
+          <t>NO KINGS CORAL SPRINGS</t>
         </is>
       </c>
       <c r="F92" s="45" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G92" s="45" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="H92" s="44" t="inlineStr">
         <is>
-          <t>Wilshire Boulevard &amp; South La Brea Avenue | Los Angeles, CA 90036</t>
+          <t>University Dr. and Sample Rd. | 3151 N University Dr | Coral Springs, FL 33065</t>
         </is>
       </c>
       <c r="I92" s="45" t="inlineStr">
         <is>
-          <t>Beverly Center</t>
+          <t>Coral Square</t>
         </is>
       </c>
       <c r="J92" s="45" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="K92" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/refusefascismorg/event/919136/</t>
+          <t>https://www.mobilize.us/nokings/event/901723/</t>
         </is>
       </c>
       <c r="L92" s="47" t="inlineStr">
         <is>
-          <t>MEETING</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="43" t="inlineStr">
         <is>
-          <t>mobilize:911204:1774706400</t>
+          <t>mobilize:919136:1773619200</t>
         </is>
       </c>
       <c r="B93" s="44" t="b">
@@ -14365,52 +14246,52 @@
       </c>
       <c r="D93" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E93" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Salem, NH</t>
+          <t>Channel No Kings Day into Real Impact</t>
         </is>
       </c>
       <c r="F93" s="45" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G93" s="45" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="H93" s="44" t="inlineStr">
         <is>
-          <t>Salem Commons (corner of Main &amp; Bridge) | 308 Main St | Salem, NH 03079</t>
+          <t>Wilshire Boulevard &amp; South La Brea Avenue | Los Angeles, CA 90036</t>
         </is>
       </c>
       <c r="I93" s="45" t="inlineStr">
         <is>
-          <t>Mall at Rockingham Park</t>
+          <t>Beverly Center</t>
         </is>
       </c>
       <c r="J93" s="45" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="K93" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/911204/</t>
+          <t>https://www.mobilize.us/refusefascismorg/event/919136/</t>
         </is>
       </c>
       <c r="L93" s="47" t="inlineStr">
         <is>
-          <t>VISIBILITY_EVENT</t>
+          <t>MEETING</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="43" t="inlineStr">
         <is>
-          <t>mobilize:901819:1774724400</t>
+          <t>mobilize:911204:1774706400</t>
         </is>
       </c>
       <c r="B94" s="44" t="b">
@@ -14426,7 +14307,7 @@
       </c>
       <c r="E94" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS GILROY</t>
+          <t>NO KINGS Salem, NH</t>
         </is>
       </c>
       <c r="F94" s="45" t="inlineStr">
@@ -14436,37 +14317,37 @@
       </c>
       <c r="G94" s="45" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="H94" s="44" t="inlineStr">
         <is>
-          <t>1st Street &amp; Santa Teresa Boulevard | Gilroy, CA 95020</t>
+          <t>Salem Commons (corner of Main &amp; Bridge) | 308 Main St | Salem, NH 03079</t>
         </is>
       </c>
       <c r="I94" s="45" t="inlineStr">
         <is>
-          <t>Gilroy Premium Outlets</t>
+          <t>Mall at Rockingham Park</t>
         </is>
       </c>
       <c r="J94" s="45" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="K94" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/901819/</t>
+          <t>https://www.mobilize.us/nokings/event/911204/</t>
         </is>
       </c>
       <c r="L94" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="43" t="inlineStr">
         <is>
-          <t>mobilize:905593:1774717200</t>
+          <t>mobilize:901819:1774724400</t>
         </is>
       </c>
       <c r="B95" s="44" t="b">
@@ -14482,7 +14363,7 @@
       </c>
       <c r="E95" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Bloomington, Indiana</t>
+          <t>NO KINGS GILROY</t>
         </is>
       </c>
       <c r="F95" s="45" t="inlineStr">
@@ -14492,25 +14373,25 @@
       </c>
       <c r="G95" s="45" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="H95" s="44" t="inlineStr">
         <is>
-          <t>Monroe County Courthouse | 100 W Kirkwood Ave | Bloomington, IN 47404</t>
+          <t>1st Street &amp; Santa Teresa Boulevard | Gilroy, CA 95020</t>
         </is>
       </c>
       <c r="I95" s="45" t="inlineStr">
         <is>
-          <t>College Mall</t>
+          <t>Gilroy Premium Outlets</t>
         </is>
       </c>
       <c r="J95" s="45" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="K95" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/905593/</t>
+          <t>https://www.mobilize.us/nokings/event/901819/</t>
         </is>
       </c>
       <c r="L95" s="47" t="inlineStr">
@@ -14522,7 +14403,7 @@
     <row r="96">
       <c r="A96" s="43" t="inlineStr">
         <is>
-          <t>mobilize:900939:1774729800</t>
+          <t>mobilize:905593:1774717200</t>
         </is>
       </c>
       <c r="B96" s="44" t="b">
@@ -14533,12 +14414,12 @@
       </c>
       <c r="D96" s="44" t="inlineStr">
         <is>
-          <t>2026-03-11T19:33:16</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E96" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS De Pere</t>
+          <t>NO KINGS Bloomington, Indiana</t>
         </is>
       </c>
       <c r="F96" s="45" t="inlineStr">
@@ -14548,25 +14429,25 @@
       </c>
       <c r="G96" s="45" t="inlineStr">
         <is>
-          <t>3:30 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="H96" s="44" t="inlineStr">
         <is>
-          <t>Voyager Park | 100 William St | De Pere, WI 54115</t>
+          <t>Monroe County Courthouse | 100 W Kirkwood Ave | Bloomington, IN 47404</t>
         </is>
       </c>
       <c r="I96" s="45" t="inlineStr">
         <is>
-          <t>Bay Park Square</t>
+          <t>College Mall</t>
         </is>
       </c>
       <c r="J96" s="45" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="K96" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/900939/</t>
+          <t>https://www.mobilize.us/nokings/event/905593/</t>
         </is>
       </c>
       <c r="L96" s="47" t="inlineStr">
@@ -14578,7 +14459,7 @@
     <row r="97">
       <c r="A97" s="43" t="inlineStr">
         <is>
-          <t>mobilize:916646:1774717200</t>
+          <t>mobilize:900939:1774729800</t>
         </is>
       </c>
       <c r="B97" s="44" t="b">
@@ -14589,12 +14470,12 @@
       </c>
       <c r="D97" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-11T19:33:16</t>
         </is>
       </c>
       <c r="E97" s="45" t="inlineStr">
         <is>
-          <t>Brookline Rally for No Kings Day</t>
+          <t>NO KINGS De Pere</t>
         </is>
       </c>
       <c r="F97" s="45" t="inlineStr">
@@ -14604,25 +14485,25 @@
       </c>
       <c r="G97" s="45" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>3:30 PM</t>
         </is>
       </c>
       <c r="H97" s="44" t="inlineStr">
         <is>
-          <t>Coolidge Corner | Brookline, MA 02446</t>
+          <t>Voyager Park | 100 William St | De Pere, WI 54115</t>
         </is>
       </c>
       <c r="I97" s="45" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Bay Park Square</t>
         </is>
       </c>
       <c r="J97" s="45" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="K97" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/speakoutseniors/event/916646/</t>
+          <t>https://www.mobilize.us/nokings/event/900939/</t>
         </is>
       </c>
       <c r="L97" s="47" t="inlineStr">
@@ -14634,7 +14515,7 @@
     <row r="98">
       <c r="A98" s="43" t="inlineStr">
         <is>
-          <t>mobilize:901742:1774717200</t>
+          <t>mobilize:916646:1774717200</t>
         </is>
       </c>
       <c r="B98" s="44" t="b">
@@ -14645,12 +14526,12 @@
       </c>
       <c r="D98" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E98" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Vacaville</t>
+          <t>Brookline Rally for No Kings Day</t>
         </is>
       </c>
       <c r="F98" s="45" t="inlineStr">
@@ -14660,25 +14541,25 @@
       </c>
       <c r="G98" s="45" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="H98" s="44" t="inlineStr">
         <is>
-          <t>Vacaville City Hall | 650 Merchant St | Vacaville, CA 95688</t>
+          <t>Coolidge Corner | Brookline, MA 02446</t>
         </is>
       </c>
       <c r="I98" s="45" t="inlineStr">
         <is>
-          <t>Vacaville Premium Outlets</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="J98" s="45" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="K98" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/901742/</t>
+          <t>https://www.mobilize.us/speakoutseniors/event/916646/</t>
         </is>
       </c>
       <c r="L98" s="47" t="inlineStr">
@@ -14690,7 +14571,7 @@
     <row r="99">
       <c r="A99" s="43" t="inlineStr">
         <is>
-          <t>mobilize:914833:1774565100</t>
+          <t>mobilize:901742:1774717200</t>
         </is>
       </c>
       <c r="B99" s="44" t="b">
@@ -14701,52 +14582,52 @@
       </c>
       <c r="D99" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E99" s="45" t="inlineStr">
         <is>
-          <t>No Kings: Sign-making!!</t>
+          <t>NO KINGS Vacaville</t>
         </is>
       </c>
       <c r="F99" s="45" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G99" s="45" t="inlineStr">
         <is>
-          <t>6:45 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="H99" s="44" t="inlineStr">
         <is>
-          <t>United Parish in Brookline | 15 Marion St | Brookline, MA 02446</t>
+          <t>Vacaville City Hall | 650 Merchant St | Vacaville, CA 95688</t>
         </is>
       </c>
       <c r="I99" s="45" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Vacaville Premium Outlets</t>
         </is>
       </c>
       <c r="J99" s="45" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="K99" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/activisteveningsbrookline/event/914833/</t>
+          <t>https://www.mobilize.us/nokings/event/901742/</t>
         </is>
       </c>
       <c r="L99" s="47" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="43" t="inlineStr">
         <is>
-          <t>mobilize:903863:1774720800</t>
+          <t>mobilize:914833:1774565100</t>
         </is>
       </c>
       <c r="B100" s="44" t="b">
@@ -14757,32 +14638,32 @@
       </c>
       <c r="D100" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E100" s="45" t="inlineStr">
         <is>
-          <t>❌👑 NO KINGS 3 – DENVER 👑❌</t>
+          <t>No Kings: Sign-making!!</t>
         </is>
       </c>
       <c r="F100" s="45" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G100" s="45" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>6:45 PM</t>
         </is>
       </c>
       <c r="H100" s="44" t="inlineStr">
         <is>
-          <t>Colorado State Capitol | 200 E Colfax Ave | Denver, CO 80203</t>
+          <t>United Parish in Brookline | 15 Marion St | Brookline, MA 02446</t>
         </is>
       </c>
       <c r="I100" s="45" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="J100" s="45" t="n">
@@ -14790,19 +14671,19 @@
       </c>
       <c r="K100" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/903863/</t>
+          <t>https://www.mobilize.us/activisteveningsbrookline/event/914833/</t>
         </is>
       </c>
       <c r="L100" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="43" t="inlineStr">
         <is>
-          <t>mobilize:902012:1774710000</t>
+          <t>mobilize:903863:1774720800</t>
         </is>
       </c>
       <c r="B101" s="44" t="b">
@@ -14818,7 +14699,7 @@
       </c>
       <c r="E101" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Wrentham</t>
+          <t>❌👑 NO KINGS 3 – DENVER 👑❌</t>
         </is>
       </c>
       <c r="F101" s="45" t="inlineStr">
@@ -14828,37 +14709,37 @@
       </c>
       <c r="G101" s="45" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="H101" s="44" t="inlineStr">
         <is>
-          <t>Corners of RTS 1A and 140 | 5 Dedham St | Wrentham, MA 02093</t>
+          <t>Colorado State Capitol | 200 E Colfax Ave | Denver, CO 80203</t>
         </is>
       </c>
       <c r="I101" s="45" t="inlineStr">
         <is>
-          <t>Wrentham Village Premium Outlets</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="J101" s="45" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="K101" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/902012/</t>
+          <t>https://www.mobilize.us/nokings/event/903863/</t>
         </is>
       </c>
       <c r="L101" s="47" t="inlineStr">
         <is>
-          <t>VISIBILITY_EVENT</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="43" t="inlineStr">
         <is>
-          <t>mobilize:917428:1774711800</t>
+          <t>mobilize:902012:1774710000</t>
         </is>
       </c>
       <c r="B102" s="44" t="b">
@@ -14869,12 +14750,12 @@
       </c>
       <c r="D102" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E102" s="45" t="inlineStr">
         <is>
-          <t>Volunteer for No Kings 3 Tyler TX</t>
+          <t>NO KINGS Wrentham</t>
         </is>
       </c>
       <c r="F102" s="45" t="inlineStr">
@@ -14884,37 +14765,37 @@
       </c>
       <c r="G102" s="45" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="H102" s="44" t="inlineStr">
         <is>
-          <t>1510 S College Ave | Tyler, TX 75702</t>
+          <t>Corners of RTS 1A and 140 | 5 Dedham St | Wrentham, MA 02093</t>
         </is>
       </c>
       <c r="I102" s="45" t="inlineStr">
         <is>
-          <t>Broadway Square</t>
+          <t>Wrentham Village Premium Outlets</t>
         </is>
       </c>
       <c r="J102" s="45" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="K102" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisiblesmithcounty/event/917428/</t>
+          <t>https://www.mobilize.us/nokings/event/902012/</t>
         </is>
       </c>
       <c r="L102" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="43" t="inlineStr">
         <is>
-          <t>mobilize:901792:1774713600</t>
+          <t>mobilize:917428:1774711800</t>
         </is>
       </c>
       <c r="B103" s="44" t="b">
@@ -14925,12 +14806,12 @@
       </c>
       <c r="D103" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E103" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS TYLER</t>
+          <t>Volunteer for No Kings 3 Tyler TX</t>
         </is>
       </c>
       <c r="F103" s="45" t="inlineStr">
@@ -14940,12 +14821,12 @@
       </c>
       <c r="G103" s="45" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>10:30 AM</t>
         </is>
       </c>
       <c r="H103" s="44" t="inlineStr">
         <is>
-          <t>Bergfeld Park | 1510 S College Ave, Corner of Broadway &amp; 4th - drop off zone | Tyler, TX 75702</t>
+          <t>1510 S College Ave | Tyler, TX 75702</t>
         </is>
       </c>
       <c r="I103" s="45" t="inlineStr">
@@ -14954,11 +14835,11 @@
         </is>
       </c>
       <c r="J103" s="45" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="K103" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/901792/</t>
+          <t>https://www.mobilize.us/indivisiblesmithcounty/event/917428/</t>
         </is>
       </c>
       <c r="L103" s="47" t="inlineStr">
@@ -14970,7 +14851,7 @@
     <row r="104">
       <c r="A104" s="43" t="inlineStr">
         <is>
-          <t>mobilize:908380:1774724400</t>
+          <t>mobilize:901792:1774713600</t>
         </is>
       </c>
       <c r="B104" s="44" t="b">
@@ -14986,7 +14867,7 @@
       </c>
       <c r="E104" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Seattle Wedgwood Neighborhood</t>
+          <t>NO KINGS TYLER</t>
         </is>
       </c>
       <c r="F104" s="45" t="inlineStr">
@@ -14996,37 +14877,37 @@
       </c>
       <c r="G104" s="45" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="H104" s="44" t="inlineStr">
         <is>
-          <t>7500 35th Ave NE | Seattle, WA 98115</t>
+          <t>Bergfeld Park | 1510 S College Ave, Corner of Broadway &amp; 4th - drop off zone | Tyler, TX 75702</t>
         </is>
       </c>
       <c r="I104" s="45" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Broadway Square</t>
         </is>
       </c>
       <c r="J104" s="45" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="K104" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/908380/</t>
+          <t>https://www.mobilize.us/nokings/event/901792/</t>
         </is>
       </c>
       <c r="L104" s="47" t="inlineStr">
         <is>
-          <t>VISIBILITY_EVENT</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="43" t="inlineStr">
         <is>
-          <t>mobilize:913046:1774706400</t>
+          <t>mobilize:908380:1774724400</t>
         </is>
       </c>
       <c r="B105" s="44" t="b">
@@ -15037,12 +14918,12 @@
       </c>
       <c r="D105" s="44" t="inlineStr">
         <is>
-          <t>2026-03-10T15:14:09</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E105" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS [Lexington]</t>
+          <t>NO KINGS Seattle Wedgwood Neighborhood</t>
         </is>
       </c>
       <c r="F105" s="45" t="inlineStr">
@@ -15052,37 +14933,37 @@
       </c>
       <c r="G105" s="45" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="H105" s="44" t="inlineStr">
         <is>
-          <t>Captain John Parker Statue | Bedford St | Lexington, MA 02421</t>
+          <t>7500 35th Ave NE | Seattle, WA 98115</t>
         </is>
       </c>
       <c r="I105" s="45" t="inlineStr">
         <is>
-          <t>Burlington Mall</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="J105" s="45" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="K105" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/913046/</t>
+          <t>https://www.mobilize.us/nokings/event/908380/</t>
         </is>
       </c>
       <c r="L105" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="43" t="inlineStr">
         <is>
-          <t>mobilize:901123:1774710000</t>
+          <t>mobilize:913046:1774706400</t>
         </is>
       </c>
       <c r="B106" s="44" t="b">
@@ -15093,12 +14974,12 @@
       </c>
       <c r="D106" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-10T15:14:09</t>
         </is>
       </c>
       <c r="E106" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Woodbridge United</t>
+          <t>NO KINGS [Lexington]</t>
         </is>
       </c>
       <c r="F106" s="45" t="inlineStr">
@@ -15108,25 +14989,25 @@
       </c>
       <c r="G106" s="45" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="H106" s="44" t="inlineStr">
         <is>
-          <t>Lake Ridge Commuter Lot | Old Bridge Rd &amp; Minnieville Rd, 12745 Minnieville Rd | Woodbridge, VA 22192</t>
+          <t>Captain John Parker Statue | Bedford St | Lexington, MA 02421</t>
         </is>
       </c>
       <c r="I106" s="45" t="inlineStr">
         <is>
-          <t>Potomac Mills</t>
+          <t>Burlington Mall</t>
         </is>
       </c>
       <c r="J106" s="45" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="K106" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/901123/</t>
+          <t>https://www.mobilize.us/nokings/event/913046/</t>
         </is>
       </c>
       <c r="L106" s="47" t="inlineStr">
@@ -15138,7 +15019,7 @@
     <row r="107">
       <c r="A107" s="43" t="inlineStr">
         <is>
-          <t>mobilize:900805:1774724400</t>
+          <t>mobilize:901123:1774710000</t>
         </is>
       </c>
       <c r="B107" s="44" t="b">
@@ -15154,7 +15035,7 @@
       </c>
       <c r="E107" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Fort Worth</t>
+          <t>NO KINGS Woodbridge United</t>
         </is>
       </c>
       <c r="F107" s="45" t="inlineStr">
@@ -15164,25 +15045,25 @@
       </c>
       <c r="G107" s="45" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="H107" s="44" t="inlineStr">
         <is>
-          <t>General Worth Square | 900 Main St | Fort Worth, TX 76102</t>
+          <t>Lake Ridge Commuter Lot | Old Bridge Rd &amp; Minnieville Rd, 12745 Minnieville Rd | Woodbridge, VA 22192</t>
         </is>
       </c>
       <c r="I107" s="45" t="inlineStr">
         <is>
-          <t>University Park Village</t>
+          <t>Potomac Mills</t>
         </is>
       </c>
       <c r="J107" s="45" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="K107" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/900805/</t>
+          <t>https://www.mobilize.us/nokings/event/901123/</t>
         </is>
       </c>
       <c r="L107" s="47" t="inlineStr">
@@ -15194,7 +15075,7 @@
     <row r="108">
       <c r="A108" s="43" t="inlineStr">
         <is>
-          <t>mobilize:903527:1774710000</t>
+          <t>mobilize:900805:1774724400</t>
         </is>
       </c>
       <c r="B108" s="44" t="b">
@@ -15205,12 +15086,12 @@
       </c>
       <c r="D108" s="44" t="inlineStr">
         <is>
-          <t>2026-03-09T15:27:00</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E108" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS ALEXANDRIA</t>
+          <t>NO KINGS Fort Worth</t>
         </is>
       </c>
       <c r="F108" s="45" t="inlineStr">
@@ -15220,25 +15101,25 @@
       </c>
       <c r="G108" s="45" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="H108" s="44" t="inlineStr">
         <is>
-          <t>Neighborhood Park | 2401 Main Line Blvd | Alexandria, VA 22301</t>
+          <t>General Worth Square | 900 Main St | Fort Worth, TX 76102</t>
         </is>
       </c>
       <c r="I108" s="45" t="inlineStr">
         <is>
-          <t>Fashion Center at Pentagon City</t>
+          <t>University Park Village</t>
         </is>
       </c>
       <c r="J108" s="45" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="K108" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/903527/</t>
+          <t>https://www.mobilize.us/nokings/event/900805/</t>
         </is>
       </c>
       <c r="L108" s="47" t="inlineStr">
@@ -15250,7 +15131,7 @@
     <row r="109">
       <c r="A109" s="43" t="inlineStr">
         <is>
-          <t>mobilize:904509:1774717200</t>
+          <t>mobilize:903527:1774710000</t>
         </is>
       </c>
       <c r="B109" s="44" t="b">
@@ -15261,12 +15142,12 @@
       </c>
       <c r="D109" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-09T15:27:00</t>
         </is>
       </c>
       <c r="E109" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS: Downtown Tacoma!</t>
+          <t>NO KINGS ALEXANDRIA</t>
         </is>
       </c>
       <c r="F109" s="45" t="inlineStr">
@@ -15276,37 +15157,37 @@
       </c>
       <c r="G109" s="45" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="H109" s="44" t="inlineStr">
         <is>
-          <t>Tacoma Union Station | 1745 Pacific Ave | Tacoma, WA 98402</t>
+          <t>Neighborhood Park | 2401 Main Line Blvd | Alexandria, VA 22301</t>
         </is>
       </c>
       <c r="I109" s="45" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>Fashion Center at Pentagon City</t>
         </is>
       </c>
       <c r="J109" s="45" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="K109" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/904509/</t>
+          <t>https://www.mobilize.us/nokings/event/903527/</t>
         </is>
       </c>
       <c r="L109" s="47" t="inlineStr">
         <is>
-          <t>VISIBILITY_EVENT</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="43" t="inlineStr">
         <is>
-          <t>mobilize:893361:1774710000</t>
+          <t>mobilize:904509:1774717200</t>
         </is>
       </c>
       <c r="B110" s="44" t="b">
@@ -15317,12 +15198,12 @@
       </c>
       <c r="D110" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E110" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS</t>
+          <t>NO KINGS: Downtown Tacoma!</t>
         </is>
       </c>
       <c r="F110" s="45" t="inlineStr">
@@ -15337,32 +15218,32 @@
       </c>
       <c r="H110" s="44" t="inlineStr">
         <is>
-          <t>Schaumburg Road &amp; Roselle Road | Schaumburg, IL 60193</t>
+          <t>Tacoma Union Station | 1745 Pacific Ave | Tacoma, WA 98402</t>
         </is>
       </c>
       <c r="I110" s="45" t="inlineStr">
         <is>
-          <t>Woodfield Mall</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="J110" s="45" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="K110" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisible/event/893361/</t>
+          <t>https://www.mobilize.us/nokings/event/904509/</t>
         </is>
       </c>
       <c r="L110" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="43" t="inlineStr">
         <is>
-          <t>mobilize:907132:1774710000</t>
+          <t>mobilize:893361:1774710000</t>
         </is>
       </c>
       <c r="B111" s="44" t="b">
@@ -15373,12 +15254,12 @@
       </c>
       <c r="D111" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E111" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS SCHAUMBURG, IL</t>
+          <t>NO KINGS</t>
         </is>
       </c>
       <c r="F111" s="45" t="inlineStr">
@@ -15393,7 +15274,7 @@
       </c>
       <c r="H111" s="44" t="inlineStr">
         <is>
-          <t>CLOCK TOWER | ROSELLE AND SCHAUMBURG ROAD | Schaumburg, IL 60193</t>
+          <t>Schaumburg Road &amp; Roselle Road | Schaumburg, IL 60193</t>
         </is>
       </c>
       <c r="I111" s="45" t="inlineStr">
@@ -15406,7 +15287,7 @@
       </c>
       <c r="K111" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/907132/</t>
+          <t>https://www.mobilize.us/indivisible/event/893361/</t>
         </is>
       </c>
       <c r="L111" s="47" t="inlineStr">
@@ -15418,7 +15299,7 @@
     <row r="112">
       <c r="A112" s="43" t="inlineStr">
         <is>
-          <t>mobilize:900828:1774713600</t>
+          <t>mobilize:907132:1774710000</t>
         </is>
       </c>
       <c r="B112" s="44" t="b">
@@ -15434,7 +15315,7 @@
       </c>
       <c r="E112" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Miami</t>
+          <t>NO KINGS SCHAUMBURG, IL</t>
         </is>
       </c>
       <c r="F112" s="45" t="inlineStr">
@@ -15444,25 +15325,25 @@
       </c>
       <c r="G112" s="45" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="H112" s="44" t="inlineStr">
         <is>
-          <t>Tropical Park | 7900 SW 40th St | Miami, FL 33155</t>
+          <t>CLOCK TOWER | ROSELLE AND SCHAUMBURG ROAD | Schaumburg, IL 60193</t>
         </is>
       </c>
       <c r="I112" s="45" t="inlineStr">
         <is>
-          <t>Dadeland Mall</t>
+          <t>Woodfield Mall</t>
         </is>
       </c>
       <c r="J112" s="45" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="K112" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/900828/</t>
+          <t>https://www.mobilize.us/nokings/event/907132/</t>
         </is>
       </c>
       <c r="L112" s="47" t="inlineStr">
@@ -15474,7 +15355,7 @@
     <row r="113">
       <c r="A113" s="43" t="inlineStr">
         <is>
-          <t>mobilize:917329:1774724400</t>
+          <t>mobilize:900828:1774713600</t>
         </is>
       </c>
       <c r="B113" s="44" t="b">
@@ -15485,12 +15366,12 @@
       </c>
       <c r="D113" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E113" s="45" t="inlineStr">
         <is>
-          <t>Volunteer for No Kings Tri-Valley 3</t>
+          <t>NO KINGS Miami</t>
         </is>
       </c>
       <c r="F113" s="45" t="inlineStr">
@@ -15505,32 +15386,32 @@
       </c>
       <c r="H113" s="44" t="inlineStr">
         <is>
-          <t>Amador Valley Community Park | 4301 Black Ave | Pleasanton, CA 94566</t>
+          <t>Tropical Park | 7900 SW 40th St | Miami, FL 33155</t>
         </is>
       </c>
       <c r="I113" s="45" t="inlineStr">
         <is>
-          <t>San Francisco Premium Outlets</t>
+          <t>Dadeland Mall</t>
         </is>
       </c>
       <c r="J113" s="45" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="K113" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisibletrivalley/event/917329/</t>
+          <t>https://www.mobilize.us/nokings/event/900828/</t>
         </is>
       </c>
       <c r="L113" s="47" t="inlineStr">
         <is>
-          <t>COMMUNITY</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="43" t="inlineStr">
         <is>
-          <t>mobilize:906022:1774729800</t>
+          <t>mobilize:917329:1774724400</t>
         </is>
       </c>
       <c r="B114" s="44" t="b">
@@ -15541,12 +15422,12 @@
       </c>
       <c r="D114" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E114" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Tri-Valley</t>
+          <t>Volunteer for No Kings Tri-Valley 3</t>
         </is>
       </c>
       <c r="F114" s="45" t="inlineStr">
@@ -15556,7 +15437,7 @@
       </c>
       <c r="G114" s="45" t="inlineStr">
         <is>
-          <t>1:30 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="H114" s="44" t="inlineStr">
@@ -15574,19 +15455,19 @@
       </c>
       <c r="K114" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/906022/</t>
+          <t>https://www.mobilize.us/indivisibletrivalley/event/917329/</t>
         </is>
       </c>
       <c r="L114" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>COMMUNITY</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="43" t="inlineStr">
         <is>
-          <t>mobilize:795854:1773507600</t>
+          <t>mobilize:906022:1774729800</t>
         </is>
       </c>
       <c r="B115" s="44" t="b">
@@ -15602,47 +15483,47 @@
       </c>
       <c r="E115" s="45" t="inlineStr">
         <is>
-          <t>NO WAR. NO KINGS: Tacoma</t>
+          <t>NO KINGS Tri-Valley</t>
         </is>
       </c>
       <c r="F115" s="45" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G115" s="45" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>1:30 PM</t>
         </is>
       </c>
       <c r="H115" s="44" t="inlineStr">
         <is>
-          <t>Union Station - Federal Courthouse | 1717 Pacific Ave | Tacoma, WA 98402</t>
+          <t>Amador Valley Community Park | 4301 Black Ave | Pleasanton, CA 94566</t>
         </is>
       </c>
       <c r="I115" s="45" t="inlineStr">
         <is>
-          <t>Tacoma Mall</t>
+          <t>San Francisco Premium Outlets</t>
         </is>
       </c>
       <c r="J115" s="45" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="K115" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/seattleindivisible/event/795854/</t>
+          <t>https://www.mobilize.us/nokings/event/906022/</t>
         </is>
       </c>
       <c r="L115" s="47" t="inlineStr">
         <is>
-          <t>VISIBILITY_EVENT</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="43" t="inlineStr">
         <is>
-          <t>mobilize:912423:1774699200</t>
+          <t>mobilize:795854:1773507600</t>
         </is>
       </c>
       <c r="B116" s="44" t="b">
@@ -15658,35 +15539,35 @@
       </c>
       <c r="E116" s="45" t="inlineStr">
         <is>
-          <t>WOFA NO KINGS BRIDGE BRIGADE, Arlington, VA - N Scott St Over 66</t>
+          <t>NO WAR. NO KINGS: Tacoma</t>
         </is>
       </c>
       <c r="F116" s="45" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G116" s="45" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="H116" s="44" t="inlineStr">
         <is>
-          <t>Address for GPS. Bridge and street parking nearby. | 1821 21st St N | Arlington, VA 22209</t>
+          <t>Union Station - Federal Courthouse | 1717 Pacific Ave | Tacoma, WA 98402</t>
         </is>
       </c>
       <c r="I116" s="45" t="inlineStr">
         <is>
-          <t>Fashion Center at Pentagon City</t>
+          <t>Tacoma Mall</t>
         </is>
       </c>
       <c r="J116" s="45" t="n">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="K116" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/912423/</t>
+          <t>https://www.mobilize.us/seattleindivisible/event/795854/</t>
         </is>
       </c>
       <c r="L116" s="47" t="inlineStr">
@@ -15698,7 +15579,7 @@
     <row r="117">
       <c r="A117" s="43" t="inlineStr">
         <is>
-          <t>mobilize:901675:1774717200</t>
+          <t>mobilize:912423:1774699200</t>
         </is>
       </c>
       <c r="B117" s="44" t="b">
@@ -15714,7 +15595,7 @@
       </c>
       <c r="E117" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Eagan</t>
+          <t>WOFA NO KINGS BRIDGE BRIGADE, Arlington, VA - N Scott St Over 66</t>
         </is>
       </c>
       <c r="F117" s="45" t="inlineStr">
@@ -15724,25 +15605,25 @@
       </c>
       <c r="G117" s="45" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>8:00 AM</t>
         </is>
       </c>
       <c r="H117" s="44" t="inlineStr">
         <is>
-          <t>Pilot Knob Road &amp; Yankee Doodle Road | Eagan, MN 55121</t>
+          <t>Address for GPS. Bridge and street parking nearby. | 1821 21st St N | Arlington, VA 22209</t>
         </is>
       </c>
       <c r="I117" s="45" t="inlineStr">
         <is>
-          <t>Twin Cities Premium Outlets</t>
+          <t>Fashion Center at Pentagon City</t>
         </is>
       </c>
       <c r="J117" s="45" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="K117" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/901675/</t>
+          <t>https://www.mobilize.us/nokings/event/912423/</t>
         </is>
       </c>
       <c r="L117" s="47" t="inlineStr">
@@ -15754,7 +15635,7 @@
     <row r="118">
       <c r="A118" s="43" t="inlineStr">
         <is>
-          <t>mobilize:894909:1774720800</t>
+          <t>mobilize:901675:1774717200</t>
         </is>
       </c>
       <c r="B118" s="44" t="b">
@@ -15765,12 +15646,12 @@
       </c>
       <c r="D118" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E118" s="45" t="inlineStr">
         <is>
-          <t>No Kings 3 - Ann Arbor Indivisible</t>
+          <t>NO KINGS Eagan</t>
         </is>
       </c>
       <c r="F118" s="45" t="inlineStr">
@@ -15780,37 +15661,37 @@
       </c>
       <c r="G118" s="45" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="H118" s="44" t="inlineStr">
         <is>
-          <t>Liberty Street Post Office | 200 E Liberty St | Ann Arbor, MI 48104</t>
+          <t>Pilot Knob Road &amp; Yankee Doodle Road | Eagan, MN 55121</t>
         </is>
       </c>
       <c r="I118" s="45" t="inlineStr">
         <is>
-          <t>Briarwood Mall</t>
+          <t>Twin Cities Premium Outlets</t>
         </is>
       </c>
       <c r="J118" s="45" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="K118" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/annarborindivisible/event/894909/</t>
+          <t>https://www.mobilize.us/nokings/event/901675/</t>
         </is>
       </c>
       <c r="L118" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="43" t="inlineStr">
         <is>
-          <t>mobilize:905229:1774720800</t>
+          <t>mobilize:894909:1774720800</t>
         </is>
       </c>
       <c r="B119" s="44" t="b">
@@ -15821,12 +15702,12 @@
       </c>
       <c r="D119" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E119" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS - ANN ARBOR INDIVISIBLE</t>
+          <t>No Kings 3 - Ann Arbor Indivisible</t>
         </is>
       </c>
       <c r="F119" s="45" t="inlineStr">
@@ -15854,7 +15735,7 @@
       </c>
       <c r="K119" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/905229/</t>
+          <t>https://www.mobilize.us/annarborindivisible/event/894909/</t>
         </is>
       </c>
       <c r="L119" s="47" t="inlineStr">
@@ -15866,7 +15747,7 @@
     <row r="120">
       <c r="A120" s="43" t="inlineStr">
         <is>
-          <t>mobilize:918887:1774720800</t>
+          <t>mobilize:905229:1774720800</t>
         </is>
       </c>
       <c r="B120" s="44" t="b">
@@ -15877,12 +15758,12 @@
       </c>
       <c r="D120" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E120" s="45" t="inlineStr">
         <is>
-          <t>MMOP Signature Collection @ No Kings - Ann Arbor</t>
+          <t>NO KINGS - ANN ARBOR INDIVISIBLE</t>
         </is>
       </c>
       <c r="F120" s="45" t="inlineStr">
@@ -15910,19 +15791,19 @@
       </c>
       <c r="K120" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/mmop/event/918887/</t>
+          <t>https://www.mobilize.us/nokings/event/905229/</t>
         </is>
       </c>
       <c r="L120" s="47" t="inlineStr">
         <is>
-          <t>SIGNATURE_GATHERING</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="43" t="inlineStr">
         <is>
-          <t>mobilize:914532:1774720800</t>
+          <t>mobilize:918887:1774720800</t>
         </is>
       </c>
       <c r="B121" s="44" t="b">
@@ -15938,7 +15819,7 @@
       </c>
       <c r="E121" s="45" t="inlineStr">
         <is>
-          <t>Ann Arbor Liberty St No Kings Rally Signature Gathering</t>
+          <t>MMOP Signature Collection @ No Kings - Ann Arbor</t>
         </is>
       </c>
       <c r="F121" s="45" t="inlineStr">
@@ -15953,7 +15834,7 @@
       </c>
       <c r="H121" s="44" t="inlineStr">
         <is>
-          <t>United States Postal Service | 200 E Liberty St Lbby | Ann Arbor, MI 48104</t>
+          <t>Liberty Street Post Office | 200 E Liberty St | Ann Arbor, MI 48104</t>
         </is>
       </c>
       <c r="I121" s="45" t="inlineStr">
@@ -15962,11 +15843,11 @@
         </is>
       </c>
       <c r="J121" s="45" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="K121" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/mcmorrowformichigan/event/914532/</t>
+          <t>https://www.mobilize.us/mmop/event/918887/</t>
         </is>
       </c>
       <c r="L121" s="47" t="inlineStr">
@@ -15978,7 +15859,7 @@
     <row r="122">
       <c r="A122" s="43" t="inlineStr">
         <is>
-          <t>mobilize:910369:1774706400</t>
+          <t>mobilize:914532:1774720800</t>
         </is>
       </c>
       <c r="B122" s="44" t="b">
@@ -15994,7 +15875,7 @@
       </c>
       <c r="E122" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS [X/Twitter]</t>
+          <t>Ann Arbor Liberty St No Kings Rally Signature Gathering</t>
         </is>
       </c>
       <c r="F122" s="45" t="inlineStr">
@@ -16004,37 +15885,37 @@
       </c>
       <c r="G122" s="45" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="H122" s="44" t="inlineStr">
         <is>
-          <t>10001 | New York, NY 10001</t>
+          <t>United States Postal Service | 200 E Liberty St Lbby | Ann Arbor, MI 48104</t>
         </is>
       </c>
       <c r="I122" s="45" t="inlineStr">
         <is>
-          <t>Newport Centre</t>
+          <t>Briarwood Mall</t>
         </is>
       </c>
       <c r="J122" s="45" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="K122" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/910369/</t>
+          <t>https://www.mobilize.us/mcmorrowformichigan/event/914532/</t>
         </is>
       </c>
       <c r="L122" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>SIGNATURE_GATHERING</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="43" t="inlineStr">
         <is>
-          <t>mobilize:918752:1774704600</t>
+          <t>mobilize:910369:1774706400</t>
         </is>
       </c>
       <c r="B123" s="44" t="b">
@@ -16050,7 +15931,7 @@
       </c>
       <c r="E123" s="45" t="inlineStr">
         <is>
-          <t>Boca Raton NO KINGS with Oliver Larkin Campaign</t>
+          <t>NO KINGS [X/Twitter]</t>
         </is>
       </c>
       <c r="F123" s="45" t="inlineStr">
@@ -16060,25 +15941,25 @@
       </c>
       <c r="G123" s="45" t="inlineStr">
         <is>
-          <t>9:30 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="H123" s="44" t="inlineStr">
         <is>
-          <t>Boca Raton City Hall | 201 W Palmetto Park Rd | Boca Raton, FL 33432</t>
+          <t>10001 | New York, NY 10001</t>
         </is>
       </c>
       <c r="I123" s="45" t="inlineStr">
         <is>
-          <t>Town Center at Boca Raton</t>
+          <t>Newport Centre</t>
         </is>
       </c>
       <c r="J123" s="45" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="K123" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/oliverforcongress/event/918752/</t>
+          <t>https://www.mobilize.us/nokings/event/910369/</t>
         </is>
       </c>
       <c r="L123" s="47" t="inlineStr">
@@ -16090,7 +15971,7 @@
     <row r="124">
       <c r="A124" s="43" t="inlineStr">
         <is>
-          <t>mobilize:901027:1774715400</t>
+          <t>mobilize:918752:1774704600</t>
         </is>
       </c>
       <c r="B124" s="44" t="b">
@@ -16101,12 +15982,12 @@
       </c>
       <c r="D124" s="44" t="inlineStr">
         <is>
-          <t>2026-03-11T03:29:59</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E124" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS III - Green Bay</t>
+          <t>Boca Raton NO KINGS with Oliver Larkin Campaign</t>
         </is>
       </c>
       <c r="F124" s="45" t="inlineStr">
@@ -16116,17 +15997,17 @@
       </c>
       <c r="G124" s="45" t="inlineStr">
         <is>
-          <t>11:30 AM</t>
+          <t>9:30 AM</t>
         </is>
       </c>
       <c r="H124" s="44" t="inlineStr">
         <is>
-          <t>St. James Park | 801 S Madison St | Green Bay, WI 54301</t>
+          <t>Boca Raton City Hall | 201 W Palmetto Park Rd | Boca Raton, FL 33432</t>
         </is>
       </c>
       <c r="I124" s="45" t="inlineStr">
         <is>
-          <t>Bay Park Square</t>
+          <t>Town Center at Boca Raton</t>
         </is>
       </c>
       <c r="J124" s="45" t="n">
@@ -16134,7 +16015,7 @@
       </c>
       <c r="K124" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/901027/</t>
+          <t>https://www.mobilize.us/oliverforcongress/event/918752/</t>
         </is>
       </c>
       <c r="L124" s="47" t="inlineStr">
@@ -16146,7 +16027,7 @@
     <row r="125">
       <c r="A125" s="43" t="inlineStr">
         <is>
-          <t>mobilize:901775:1774706400</t>
+          <t>mobilize:901027:1774715400</t>
         </is>
       </c>
       <c r="B125" s="44" t="b">
@@ -16157,12 +16038,12 @@
       </c>
       <c r="D125" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-11T03:29:59</t>
         </is>
       </c>
       <c r="E125" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Indivisible Boca Raton</t>
+          <t>NO KINGS III - Green Bay</t>
         </is>
       </c>
       <c r="F125" s="45" t="inlineStr">
@@ -16172,17 +16053,17 @@
       </c>
       <c r="G125" s="45" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>11:30 AM</t>
         </is>
       </c>
       <c r="H125" s="44" t="inlineStr">
         <is>
-          <t>Boca Raton City Hall | 201 W Palmetto Park Rd | Boca Raton, FL 33432</t>
+          <t>St. James Park | 801 S Madison St | Green Bay, WI 54301</t>
         </is>
       </c>
       <c r="I125" s="45" t="inlineStr">
         <is>
-          <t>Town Center at Boca Raton</t>
+          <t>Bay Park Square</t>
         </is>
       </c>
       <c r="J125" s="45" t="n">
@@ -16190,7 +16071,7 @@
       </c>
       <c r="K125" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/901775/</t>
+          <t>https://www.mobilize.us/nokings/event/901027/</t>
         </is>
       </c>
       <c r="L125" s="47" t="inlineStr">
@@ -16258,7 +16139,7 @@
     <row r="127">
       <c r="A127" s="43" t="inlineStr">
         <is>
-          <t>mobilize:899252:1774713600</t>
+          <t>mobilize:901775:1774706400</t>
         </is>
       </c>
       <c r="B127" s="44" t="b">
@@ -16269,12 +16150,12 @@
       </c>
       <c r="D127" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E127" s="45" t="inlineStr">
         <is>
-          <t>No Kings! Folsom</t>
+          <t>NO KINGS Indivisible Boca Raton</t>
         </is>
       </c>
       <c r="F127" s="45" t="inlineStr">
@@ -16284,25 +16165,25 @@
       </c>
       <c r="G127" s="45" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="H127" s="44" t="inlineStr">
         <is>
-          <t>Folsom-Auburn Rd Bridge | Folsom-Auburn Road &amp; Greenback Lane | Folsom, CA 95630</t>
+          <t>Boca Raton City Hall | 201 W Palmetto Park Rd | Boca Raton, FL 33432</t>
         </is>
       </c>
       <c r="I127" s="45" t="inlineStr">
         <is>
-          <t>Folsom Outlet Marketplace</t>
+          <t>Town Center at Boca Raton</t>
         </is>
       </c>
       <c r="J127" s="45" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="K127" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/cadems/event/899252/</t>
+          <t>https://www.mobilize.us/nokings/event/901775/</t>
         </is>
       </c>
       <c r="L127" s="47" t="inlineStr">
@@ -16314,7 +16195,7 @@
     <row r="128">
       <c r="A128" s="43" t="inlineStr">
         <is>
-          <t>mobilize:914413:1774713600</t>
+          <t>mobilize:899252:1774713600</t>
         </is>
       </c>
       <c r="B128" s="44" t="b">
@@ -16325,12 +16206,12 @@
       </c>
       <c r="D128" s="44" t="inlineStr">
         <is>
-          <t>2026-03-10T15:14:09</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E128" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Folsom!</t>
+          <t>No Kings! Folsom</t>
         </is>
       </c>
       <c r="F128" s="45" t="inlineStr">
@@ -16358,19 +16239,19 @@
       </c>
       <c r="K128" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/914413/</t>
+          <t>https://www.mobilize.us/cadems/event/899252/</t>
         </is>
       </c>
       <c r="L128" s="47" t="inlineStr">
         <is>
-          <t>VISIBILITY_EVENT</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="43" t="inlineStr">
         <is>
-          <t>mobilize:919030:1774720800</t>
+          <t>mobilize:914413:1774713600</t>
         </is>
       </c>
       <c r="B129" s="44" t="b">
@@ -16381,12 +16262,12 @@
       </c>
       <c r="D129" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-10T15:14:09</t>
         </is>
       </c>
       <c r="E129" s="45" t="inlineStr">
         <is>
-          <t>CAT LADIES MEET UP AT NO KINGS IN RANCHO CUCAMONGA (INLAND EMPIRE)</t>
+          <t>NO KINGS Folsom!</t>
         </is>
       </c>
       <c r="F129" s="45" t="inlineStr">
@@ -16396,37 +16277,37 @@
       </c>
       <c r="G129" s="45" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="H129" s="44" t="inlineStr">
         <is>
-          <t>West Foothill Boulevard &amp; Haven Avenue | Rancho Cucamonga, CA 91730</t>
+          <t>Folsom-Auburn Rd Bridge | Folsom-Auburn Road &amp; Greenback Lane | Folsom, CA 95630</t>
         </is>
       </c>
       <c r="I129" s="45" t="inlineStr">
         <is>
-          <t>Ontario Mills</t>
+          <t>Folsom Outlet Marketplace</t>
         </is>
       </c>
       <c r="J129" s="45" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="K129" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/catladiesforamerica/event/919030/</t>
+          <t>https://www.mobilize.us/nokings/event/914413/</t>
         </is>
       </c>
       <c r="L129" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="43" t="inlineStr">
         <is>
-          <t>mobilize:914795:1773608400</t>
+          <t>mobilize:919030:1774720800</t>
         </is>
       </c>
       <c r="B130" s="44" t="b">
@@ -16442,47 +16323,47 @@
       </c>
       <c r="E130" s="45" t="inlineStr">
         <is>
-          <t>Bottoms Up - Crowns Down: A No Kings Benefit Party</t>
+          <t>CAT LADIES MEET UP AT NO KINGS IN RANCHO CUCAMONGA (INLAND EMPIRE)</t>
         </is>
       </c>
       <c r="F130" s="45" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G130" s="45" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="H130" s="44" t="inlineStr">
         <is>
-          <t>Bløm Mead + Cider | 100 S 4th Ave ste 110 | Ann Arbor, MI 48104</t>
+          <t>West Foothill Boulevard &amp; Haven Avenue | Rancho Cucamonga, CA 91730</t>
         </is>
       </c>
       <c r="I130" s="45" t="inlineStr">
         <is>
-          <t>Briarwood Mall</t>
+          <t>Ontario Mills</t>
         </is>
       </c>
       <c r="J130" s="45" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="K130" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/annarborindivisible/event/914795/</t>
+          <t>https://www.mobilize.us/catladiesforamerica/event/919030/</t>
         </is>
       </c>
       <c r="L130" s="47" t="inlineStr">
         <is>
-          <t>COMMUNITY</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="43" t="inlineStr">
         <is>
-          <t>mobilize:902971:1774720800</t>
+          <t>mobilize:914795:1773608400</t>
         </is>
       </c>
       <c r="B131" s="44" t="b">
@@ -16493,32 +16374,32 @@
       </c>
       <c r="D131" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E131" s="45" t="inlineStr">
         <is>
-          <t>Indivisible Inland Empire NO KINGS</t>
+          <t>Bottoms Up - Crowns Down: A No Kings Benefit Party</t>
         </is>
       </c>
       <c r="F131" s="45" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G131" s="45" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="H131" s="44" t="inlineStr">
         <is>
-          <t>Haven Avenue &amp; Foothill Boulevard | Rancho Cucamonga, CA 91730</t>
+          <t>Bløm Mead + Cider | 100 S 4th Ave ste 110 | Ann Arbor, MI 48104</t>
         </is>
       </c>
       <c r="I131" s="45" t="inlineStr">
         <is>
-          <t>Ontario Mills</t>
+          <t>Briarwood Mall</t>
         </is>
       </c>
       <c r="J131" s="45" t="n">
@@ -16526,19 +16407,19 @@
       </c>
       <c r="K131" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/902971/</t>
+          <t>https://www.mobilize.us/annarborindivisible/event/914795/</t>
         </is>
       </c>
       <c r="L131" s="47" t="inlineStr">
         <is>
-          <t>VISIBILITY_EVENT</t>
+          <t>COMMUNITY</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="43" t="inlineStr">
         <is>
-          <t>mobilize:911156:1774706400</t>
+          <t>mobilize:902971:1774720800</t>
         </is>
       </c>
       <c r="B132" s="44" t="b">
@@ -16554,7 +16435,7 @@
       </c>
       <c r="E132" s="45" t="inlineStr">
         <is>
-          <t>South PBC Indivisible CAR PROTEST for NO KINGS DAY 3.0, Boca Raton</t>
+          <t>Indivisible Inland Empire NO KINGS</t>
         </is>
       </c>
       <c r="F132" s="45" t="inlineStr">
@@ -16564,25 +16445,25 @@
       </c>
       <c r="G132" s="45" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="H132" s="44" t="inlineStr">
         <is>
-          <t>Circle through the intersection of | West Palmetto Park Road &amp; Northwest 2nd Avenue | Boca Raton, FL 33432</t>
+          <t>Haven Avenue &amp; Foothill Boulevard | Rancho Cucamonga, CA 91730</t>
         </is>
       </c>
       <c r="I132" s="45" t="inlineStr">
         <is>
-          <t>Town Center at Boca Raton</t>
+          <t>Ontario Mills</t>
         </is>
       </c>
       <c r="J132" s="45" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="K132" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/911156/</t>
+          <t>https://www.mobilize.us/nokings/event/902971/</t>
         </is>
       </c>
       <c r="L132" s="47" t="inlineStr">
@@ -16594,7 +16475,7 @@
     <row r="133">
       <c r="A133" s="43" t="inlineStr">
         <is>
-          <t>mobilize:914065:1774710000</t>
+          <t>mobilize:911156:1774706400</t>
         </is>
       </c>
       <c r="B133" s="44" t="b">
@@ -16610,7 +16491,7 @@
       </c>
       <c r="E133" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Rally- Midland Texas</t>
+          <t>South PBC Indivisible CAR PROTEST for NO KINGS DAY 3.0, Boca Raton</t>
         </is>
       </c>
       <c r="F133" s="45" t="inlineStr">
@@ -16625,32 +16506,32 @@
       </c>
       <c r="H133" s="44" t="inlineStr">
         <is>
-          <t>Wadley &amp; Big Spring | Midland, TX 79705</t>
+          <t>Circle through the intersection of | West Palmetto Park Road &amp; Northwest 2nd Avenue | Boca Raton, FL 33432</t>
         </is>
       </c>
       <c r="I133" s="45" t="inlineStr">
         <is>
-          <t>Midland Park Mall</t>
+          <t>Town Center at Boca Raton</t>
         </is>
       </c>
       <c r="J133" s="45" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="K133" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/914065/</t>
+          <t>https://www.mobilize.us/nokings/event/911156/</t>
         </is>
       </c>
       <c r="L133" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="43" t="inlineStr">
         <is>
-          <t>mobilize:902973:1774717200</t>
+          <t>mobilize:914065:1774710000</t>
         </is>
       </c>
       <c r="B134" s="44" t="b">
@@ -16666,7 +16547,7 @@
       </c>
       <c r="E134" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Loudoun - Rt 7 overpass at Belmont Ridge Rd</t>
+          <t>NO KINGS Rally- Midland Texas</t>
         </is>
       </c>
       <c r="F134" s="45" t="inlineStr">
@@ -16676,17 +16557,17 @@
       </c>
       <c r="G134" s="45" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="H134" s="44" t="inlineStr">
         <is>
-          <t>Rt 7 overpass at Belmont Ridge Rd | 19313 Front St | Leesburg, VA 20176</t>
+          <t>Wadley &amp; Big Spring | Midland, TX 79705</t>
         </is>
       </c>
       <c r="I134" s="45" t="inlineStr">
         <is>
-          <t>Leesburg Premium Outlets</t>
+          <t>Midland Park Mall</t>
         </is>
       </c>
       <c r="J134" s="45" t="n">
@@ -16694,19 +16575,19 @@
       </c>
       <c r="K134" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/902973/</t>
+          <t>https://www.mobilize.us/nokings/event/914065/</t>
         </is>
       </c>
       <c r="L134" s="47" t="inlineStr">
         <is>
-          <t>VISIBILITY_EVENT</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="43" t="inlineStr">
         <is>
-          <t>mobilize:903339:1774710000</t>
+          <t>mobilize:902973:1774717200</t>
         </is>
       </c>
       <c r="B135" s="44" t="b">
@@ -16717,12 +16598,12 @@
       </c>
       <c r="D135" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E135" s="45" t="inlineStr">
         <is>
-          <t>No Kings</t>
+          <t>NO KINGS Loudoun - Rt 7 overpass at Belmont Ridge Rd</t>
         </is>
       </c>
       <c r="F135" s="45" t="inlineStr">
@@ -16732,37 +16613,37 @@
       </c>
       <c r="G135" s="45" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="H135" s="44" t="inlineStr">
         <is>
-          <t>Odell Veterans Memorial Park | 56-98 Broadway | Beverly, MA 01915</t>
+          <t>Rt 7 overpass at Belmont Ridge Rd | 19313 Front St | Leesburg, VA 20176</t>
         </is>
       </c>
       <c r="I135" s="45" t="inlineStr">
         <is>
-          <t>Liberty Tree Mall</t>
+          <t>Leesburg Premium Outlets</t>
         </is>
       </c>
       <c r="J135" s="45" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="K135" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/handsoffbeverly/event/903339/</t>
+          <t>https://www.mobilize.us/nokings/event/902973/</t>
         </is>
       </c>
       <c r="L135" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="43" t="inlineStr">
         <is>
-          <t>mobilize:905824:1774710000</t>
+          <t>mobilize:903339:1774710000</t>
         </is>
       </c>
       <c r="B136" s="44" t="b">
@@ -16773,12 +16654,12 @@
       </c>
       <c r="D136" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E136" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Dover Delaware</t>
+          <t>No Kings</t>
         </is>
       </c>
       <c r="F136" s="45" t="inlineStr">
@@ -16793,12 +16674,12 @@
       </c>
       <c r="H136" s="44" t="inlineStr">
         <is>
-          <t>Legislative Mall | 410 Legislative Ave | Dover, DE 19901</t>
+          <t>Odell Veterans Memorial Park | 56-98 Broadway | Beverly, MA 01915</t>
         </is>
       </c>
       <c r="I136" s="45" t="inlineStr">
         <is>
-          <t>Dover Mall</t>
+          <t>Liberty Tree Mall</t>
         </is>
       </c>
       <c r="J136" s="45" t="n">
@@ -16806,7 +16687,7 @@
       </c>
       <c r="K136" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/905824/</t>
+          <t>https://www.mobilize.us/handsoffbeverly/event/903339/</t>
         </is>
       </c>
       <c r="L136" s="47" t="inlineStr">
@@ -16818,7 +16699,7 @@
     <row r="137">
       <c r="A137" s="43" t="inlineStr">
         <is>
-          <t>mobilize:914596:1773700200</t>
+          <t>mobilize:905824:1774710000</t>
         </is>
       </c>
       <c r="B137" s="44" t="b">
@@ -16829,52 +16710,52 @@
       </c>
       <c r="D137" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E137" s="45" t="inlineStr">
         <is>
-          <t>Common Good Community Gathering - No Kings Information Meeting</t>
+          <t>NO KINGS Dover Delaware</t>
         </is>
       </c>
       <c r="F137" s="45" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G137" s="45" t="inlineStr">
         <is>
-          <t>5:30 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="H137" s="44" t="inlineStr">
         <is>
-          <t>The Library Center | 4653 S Campbell Ave, Hatch Auditorium | Springfield, MO 65810</t>
+          <t>Legislative Mall | 410 Legislative Ave | Dover, DE 19901</t>
         </is>
       </c>
       <c r="I137" s="45" t="inlineStr">
         <is>
-          <t>Battlefield Mall</t>
+          <t>Dover Mall</t>
         </is>
       </c>
       <c r="J137" s="45" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K137" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/communitytogether417/event/914596/</t>
+          <t>https://www.mobilize.us/nokings/event/905824/</t>
         </is>
       </c>
       <c r="L137" s="47" t="inlineStr">
         <is>
-          <t>COMMUNITY</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="43" t="inlineStr">
         <is>
-          <t>mobilize:911747:1774708200</t>
+          <t>mobilize:914596:1773700200</t>
         </is>
       </c>
       <c r="B138" s="44" t="b">
@@ -16885,52 +16766,52 @@
       </c>
       <c r="D138" s="44" t="inlineStr">
         <is>
-          <t>2026-03-11T03:29:59</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E138" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Audubon, PA</t>
+          <t>Common Good Community Gathering - No Kings Information Meeting</t>
         </is>
       </c>
       <c r="F138" s="45" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G138" s="45" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>5:30 PM</t>
         </is>
       </c>
       <c r="H138" s="44" t="inlineStr">
         <is>
-          <t>Sidewalk in front of Giant Supermarket | 2670 Egypt Rd | Norristown, PA 19403</t>
+          <t>The Library Center | 4653 S Campbell Ave, Hatch Auditorium | Springfield, MO 65810</t>
         </is>
       </c>
       <c r="I138" s="45" t="inlineStr">
         <is>
-          <t>King of Prussia</t>
+          <t>Battlefield Mall</t>
         </is>
       </c>
       <c r="J138" s="45" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K138" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/911747/</t>
+          <t>https://www.mobilize.us/communitytogether417/event/914596/</t>
         </is>
       </c>
       <c r="L138" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>COMMUNITY</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="43" t="inlineStr">
         <is>
-          <t>mobilize:901953:1774713600</t>
+          <t>mobilize:911747:1774708200</t>
         </is>
       </c>
       <c r="B139" s="44" t="b">
@@ -16941,12 +16822,12 @@
       </c>
       <c r="D139" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-11T03:29:59</t>
         </is>
       </c>
       <c r="E139" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Salem, MA</t>
+          <t>NO KINGS Audubon, PA</t>
         </is>
       </c>
       <c r="F139" s="45" t="inlineStr">
@@ -16956,25 +16837,25 @@
       </c>
       <c r="G139" s="45" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>10:30 AM</t>
         </is>
       </c>
       <c r="H139" s="44" t="inlineStr">
         <is>
-          <t>Riley Plaza | 1-21 Margin St | Salem, MA 01970</t>
+          <t>Sidewalk in front of Giant Supermarket | 2670 Egypt Rd | Norristown, PA 19403</t>
         </is>
       </c>
       <c r="I139" s="45" t="inlineStr">
         <is>
-          <t>Northshore Mall</t>
+          <t>King of Prussia</t>
         </is>
       </c>
       <c r="J139" s="45" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="K139" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/901953/</t>
+          <t>https://www.mobilize.us/nokings/event/911747/</t>
         </is>
       </c>
       <c r="L139" s="47" t="inlineStr">
@@ -16986,7 +16867,7 @@
     <row r="140">
       <c r="A140" s="43" t="inlineStr">
         <is>
-          <t>mobilize:911119:1774112400</t>
+          <t>mobilize:901953:1774713600</t>
         </is>
       </c>
       <c r="B140" s="44" t="b">
@@ -16997,52 +16878,52 @@
       </c>
       <c r="D140" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E140" s="45" t="inlineStr">
         <is>
-          <t>No Kings - Clayton - Sign Making Party</t>
+          <t>NO KINGS Salem, MA</t>
         </is>
       </c>
       <c r="F140" s="45" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G140" s="45" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="H140" s="44" t="inlineStr">
         <is>
-          <t>1302 W Market St | Smithfield, NC 27577</t>
+          <t>Riley Plaza | 1-21 Margin St | Salem, MA 01970</t>
         </is>
       </c>
       <c r="I140" s="45" t="inlineStr">
         <is>
-          <t>Carolina Premium Outlets</t>
+          <t>Northshore Mall</t>
         </is>
       </c>
       <c r="J140" s="45" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="K140" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisiblejoco/event/911119/</t>
+          <t>https://www.mobilize.us/nokings/event/901953/</t>
         </is>
       </c>
       <c r="L140" s="47" t="inlineStr">
         <is>
-          <t>MEETING</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="43" t="inlineStr">
         <is>
-          <t>mobilize:911460:1774724400</t>
+          <t>mobilize:911119:1774112400</t>
         </is>
       </c>
       <c r="B141" s="44" t="b">
@@ -17053,163 +16934,219 @@
       </c>
       <c r="D141" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E141" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Duluth - "Elections - Free. Fair. Forever!"</t>
+          <t>No Kings - Clayton - Sign Making Party</t>
         </is>
       </c>
       <c r="F141" s="45" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G141" s="45" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="H141" s="44" t="inlineStr">
         <is>
-          <t>Duluth City Hall | 411 W 1st St | Duluth, MN 55802</t>
+          <t>1302 W Market St | Smithfield, NC 27577</t>
         </is>
       </c>
       <c r="I141" s="45" t="inlineStr">
         <is>
-          <t>Miller Hill Mall</t>
+          <t>Carolina Premium Outlets</t>
         </is>
       </c>
       <c r="J141" s="45" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="K141" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/911460/</t>
+          <t>https://www.mobilize.us/indivisiblejoco/event/911119/</t>
         </is>
       </c>
       <c r="L141" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>MEETING</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="43" t="inlineStr">
         <is>
+          <t>mobilize:911460:1774724400</t>
+        </is>
+      </c>
+      <c r="B142" s="44" t="b">
+        <v>0</v>
+      </c>
+      <c r="C142" s="44" t="b">
+        <v>0</v>
+      </c>
+      <c r="D142" s="44" t="inlineStr">
+        <is>
+          <t>2026-03-08T07:16:44</t>
+        </is>
+      </c>
+      <c r="E142" s="45" t="inlineStr">
+        <is>
+          <t>NO KINGS Duluth - "Elections - Free. Fair. Forever!"</t>
+        </is>
+      </c>
+      <c r="F142" s="45" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G142" s="45" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="H142" s="44" t="inlineStr">
+        <is>
+          <t>Duluth City Hall | 411 W 1st St | Duluth, MN 55802</t>
+        </is>
+      </c>
+      <c r="I142" s="45" t="inlineStr">
+        <is>
+          <t>Miller Hill Mall</t>
+        </is>
+      </c>
+      <c r="J142" s="45" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K142" s="46" t="inlineStr">
+        <is>
+          <t>https://www.mobilize.us/nokings/event/911460/</t>
+        </is>
+      </c>
+      <c r="L142" s="47" t="inlineStr">
+        <is>
+          <t>RALLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="43" t="inlineStr">
+        <is>
           <t>mobilize:791329:1773759600</t>
         </is>
       </c>
-      <c r="B142" s="44" t="b">
-        <v>0</v>
-      </c>
-      <c r="C142" s="44" t="b">
-        <v>0</v>
-      </c>
-      <c r="D142" s="44" t="inlineStr">
+      <c r="B143" s="44" t="b">
+        <v>0</v>
+      </c>
+      <c r="C143" s="44" t="b">
+        <v>0</v>
+      </c>
+      <c r="D143" s="44" t="inlineStr">
         <is>
           <t>2026-03-12T05:20:25</t>
         </is>
       </c>
-      <c r="E142" s="45" t="inlineStr">
+      <c r="E143" s="45" t="inlineStr">
         <is>
           <t>NO KINGS. NO OLIGARCHS: Seattle 50th St Overpass!</t>
         </is>
       </c>
-      <c r="F142" s="45" t="inlineStr">
+      <c r="F143" s="45" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="G142" s="45" t="inlineStr">
+      <c r="G143" s="45" t="inlineStr">
         <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="H142" s="44" t="inlineStr">
+      <c r="H143" s="44" t="inlineStr">
         <is>
           <t>50th St I-5 Overpass | 5th Avenue Northeast &amp; Northeast 50th Street | Seattle, WA 98105</t>
         </is>
       </c>
-      <c r="I142" s="45" t="inlineStr">
+      <c r="I143" s="45" t="inlineStr">
         <is>
           <t>Northgate Station</t>
         </is>
       </c>
-      <c r="J142" s="45" t="n">
+      <c r="J143" s="45" t="n">
         <v>2.98</v>
       </c>
-      <c r="K142" s="46" t="inlineStr">
+      <c r="K143" s="46" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/seattleindivisible/event/791329/</t>
         </is>
       </c>
-      <c r="L142" s="47" t="inlineStr">
+      <c r="L143" s="47" t="inlineStr">
         <is>
           <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="48" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="48" t="inlineStr">
         <is>
           <t>mobilize:916494:1774305000</t>
         </is>
       </c>
-      <c r="B143" s="49" t="b">
-        <v>0</v>
-      </c>
-      <c r="C143" s="49" t="b">
-        <v>0</v>
-      </c>
-      <c r="D143" s="49" t="inlineStr">
+      <c r="B144" s="49" t="b">
+        <v>0</v>
+      </c>
+      <c r="C144" s="49" t="b">
+        <v>0</v>
+      </c>
+      <c r="D144" s="49" t="inlineStr">
         <is>
           <t>2026-03-12T05:20:25</t>
         </is>
       </c>
-      <c r="E143" s="50" t="inlineStr">
+      <c r="E144" s="50" t="inlineStr">
         <is>
           <t>No Kings 3.0 Poster Party</t>
         </is>
       </c>
-      <c r="F143" s="50" t="inlineStr">
+      <c r="F144" s="50" t="inlineStr">
         <is>
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="G143" s="50" t="inlineStr">
+      <c r="G144" s="50" t="inlineStr">
         <is>
           <t>6:30 PM</t>
         </is>
       </c>
-      <c r="H143" s="49" t="inlineStr">
+      <c r="H144" s="49" t="inlineStr">
         <is>
           <t>Tufts Library | 46 Broad St, Room 232 (upstairs) | Weymouth, MA 02188</t>
         </is>
       </c>
-      <c r="I143" s="50" t="inlineStr">
+      <c r="I144" s="50" t="inlineStr">
         <is>
           <t>South Shore Plaza</t>
         </is>
       </c>
-      <c r="J143" s="50" t="n">
+      <c r="J144" s="50" t="n">
         <v>2.98</v>
       </c>
-      <c r="K143" s="51" t="inlineStr">
+      <c r="K144" s="51" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/massdems/event/916494/</t>
         </is>
       </c>
-      <c r="L143" s="52" t="inlineStr">
+      <c r="L144" s="52" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L143"/>
-  <conditionalFormatting sqref="A2:L143">
+  <autoFilter ref="A1:L144"/>
+  <conditionalFormatting sqref="A2:L144">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$B2=TRUE</formula>
     </cfRule>
@@ -17357,6 +17294,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId143"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/latest.xlsx
+++ b/docs/latest.xlsx
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="B6" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="14" t="b">
         <v>0</v>
@@ -2412,7 +2412,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>mobilize:801600:1773590400</t>
+          <t>mobilize:899401:1773504000</t>
         </is>
       </c>
       <c r="B8" s="14" t="b">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>2026-03-09T15:27:00</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>Say No To Ken Calvert Weekly Visibility Sign Waving- Formerly Empty Chair Town Hall!</t>
+          <t>NO WARS!! NO KINGS Protest Airport Rotary Saturday, March 14th 12-1pm</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>Intersection of Monterrey and 111- park at Panera | 73075 CA-111 | Palm Desert, CA 92260</t>
+          <t>Airport Rotary | hyannnis, MA 02601</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
-          <t>The Gardens on El Paseo</t>
+          <t>Cape Cod Mall</t>
         </is>
       </c>
       <c r="J8" s="15" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="K8" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisible/event/801600/</t>
+          <t>https://www.mobilize.us/indivisible/event/899401/</t>
         </is>
       </c>
       <c r="L8" s="17" t="inlineStr">
@@ -2468,7 +2468,7 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>mobilize:899401:1773504000</t>
+          <t>mobilize:801600:1773590400</t>
         </is>
       </c>
       <c r="B9" s="14" t="b">
@@ -2479,32 +2479,32 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-09T15:27:00</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>NO WARS!! NO KINGS Protest Airport Rotary Saturday, March 14th 12-1pm</t>
+          <t>Say No To Ken Calvert Weekly Visibility Sign Waving- Formerly Empty Chair Town Hall!</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>Airport Rotary | hyannnis, MA 02601</t>
+          <t>Intersection of Monterrey and 111- park at Panera | 73075 CA-111 | Palm Desert, CA 92260</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
         <is>
-          <t>Cape Cod Mall</t>
+          <t>The Gardens on El Paseo</t>
         </is>
       </c>
       <c r="J9" s="15" t="n">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="K9" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisible/event/899401/</t>
+          <t>https://www.mobilize.us/indivisible/event/801600/</t>
         </is>
       </c>
       <c r="L9" s="17" t="inlineStr">
@@ -2748,7 +2748,7 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>mobilize:909535:1773865800</t>
+          <t>mobilize:791569:1773595800</t>
         </is>
       </c>
       <c r="B14" s="14" t="b">
@@ -2759,32 +2759,32 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-09T15:27:00</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>Bridge Brigade over Storrow Drive promoting NO KINGS -March 28</t>
+          <t>Menlo Park Speaks Out</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>4:30 PM</t>
+          <t>10:30 AM</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Appleton Bridge over Storrow Drive to the Esplanade. (Easy access from Red line Charles St station.) | Frances Appleton Brg | Boston, MA 02114</t>
+          <t>Fremont Park | University Drive &amp; Santa Cruz Avenue | Menlo Park, CA 94025</t>
         </is>
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Stanford Shopping Center</t>
         </is>
       </c>
       <c r="J14" s="15" t="n">
@@ -2792,19 +2792,19 @@
       </c>
       <c r="K14" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/bostonindivisible/event/909535/</t>
+          <t>https://www.mobilize.us/menloparkspeaksout/event/791569/</t>
         </is>
       </c>
       <c r="L14" s="17" t="inlineStr">
         <is>
-          <t>VISIBILITY_EVENT</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>mobilize:791569:1773595800</t>
+          <t>mobilize:909535:1773865800</t>
         </is>
       </c>
       <c r="B15" s="14" t="b">
@@ -2815,32 +2815,32 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>2026-03-09T15:27:00</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>Menlo Park Speaks Out</t>
+          <t>Bridge Brigade over Storrow Drive promoting NO KINGS -March 28</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>4:30 PM</t>
         </is>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>Fremont Park | University Drive &amp; Santa Cruz Avenue | Menlo Park, CA 94025</t>
+          <t>Appleton Bridge over Storrow Drive to the Esplanade. (Easy access from Red line Charles St station.) | Frances Appleton Brg | Boston, MA 02114</t>
         </is>
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
-          <t>Stanford Shopping Center</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="J15" s="15" t="n">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="K15" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/menloparkspeaksout/event/791569/</t>
+          <t>https://www.mobilize.us/bostonindivisible/event/909535/</t>
         </is>
       </c>
       <c r="L15" s="17" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
@@ -3028,43 +3028,43 @@
     <row r="19">
       <c r="A19" s="28" t="inlineStr">
         <is>
-          <t>mobilize:774947:1774051200</t>
+          <t>mobilize:892572:1773504000</t>
         </is>
       </c>
       <c r="B19" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" s="29" t="b">
         <v>0</v>
       </c>
       <c r="D19" s="29" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E19" s="30" t="inlineStr">
         <is>
-          <t>Weekly Napa Rally to Resist the Trump/Musk/GOP Regime!</t>
+          <t>Saturday RESIST Standout</t>
         </is>
       </c>
       <c r="F19" s="30" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G19" s="30" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="H19" s="29" t="inlineStr">
         <is>
-          <t>Soscol Avenue &amp; 3rd Street | Napa, CA 94559</t>
+          <t>Newton Center | Beacon Street &amp; Centre Street | Newton, MA 02459</t>
         </is>
       </c>
       <c r="I19" s="30" t="inlineStr">
         <is>
-          <t>Napa Premium Outlets</t>
+          <t>The Shops at Chestnut Hill</t>
         </is>
       </c>
       <c r="J19" s="30" t="n">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="K19" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisible/event/774947/</t>
+          <t>https://www.mobilize.us/newtonindivisible/event/892572/</t>
         </is>
       </c>
       <c r="L19" s="32" t="inlineStr">
@@ -3084,7 +3084,7 @@
     <row r="20">
       <c r="A20" s="28" t="inlineStr">
         <is>
-          <t>mobilize:892572:1773504000</t>
+          <t>mobilize:774947:1774051200</t>
         </is>
       </c>
       <c r="B20" s="29" t="b">
@@ -3095,32 +3095,32 @@
       </c>
       <c r="D20" s="29" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-14T09:08:59</t>
         </is>
       </c>
       <c r="E20" s="30" t="inlineStr">
         <is>
-          <t>Saturday RESIST Standout</t>
+          <t>Weekly Napa Rally to Resist the Trump/Musk/GOP Regime!</t>
         </is>
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G20" s="30" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="H20" s="29" t="inlineStr">
         <is>
-          <t>Newton Center | Beacon Street &amp; Centre Street | Newton, MA 02459</t>
+          <t>Soscol Avenue &amp; 3rd Street | Napa, CA 94559</t>
         </is>
       </c>
       <c r="I20" s="30" t="inlineStr">
         <is>
-          <t>The Shops at Chestnut Hill</t>
+          <t>Napa Premium Outlets</t>
         </is>
       </c>
       <c r="J20" s="30" t="n">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="K20" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/newtonindivisible/event/892572/</t>
+          <t>https://www.mobilize.us/indivisible/event/774947/</t>
         </is>
       </c>
       <c r="L20" s="32" t="inlineStr">
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="B33" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" s="29" t="b">
         <v>0</v>
@@ -4264,7 +4264,7 @@
         </is>
       </c>
       <c r="B41" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" s="44" t="b">
         <v>0</v>
@@ -4316,7 +4316,7 @@
     <row r="42">
       <c r="A42" s="43" t="inlineStr">
         <is>
-          <t>mobilize:860202:1773964800</t>
+          <t>mobilize:824060:1773964800</t>
         </is>
       </c>
       <c r="B42" s="44" t="b">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="E42" s="45" t="inlineStr">
         <is>
-          <t>Weekly Meade Ave Bridge Bannering Over I-805 | Thursday Afternoons</t>
+          <t>Visibility Brigade - North Park</t>
         </is>
       </c>
       <c r="F42" s="45" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="H42" s="44" t="inlineStr">
         <is>
-          <t>Meade Ave Bridge Over I-805 | 4371 Boundary St | San Diego, CA 92116</t>
+          <t>Meade Ave bridge over I-805 in North Park | 4371 Boundary St | San Diego, CA 92116</t>
         </is>
       </c>
       <c r="I42" s="45" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="K42" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/visibilitybrigadesandiego/event/860202/</t>
+          <t>https://www.mobilize.us/indivisible/event/824060/</t>
         </is>
       </c>
       <c r="L42" s="47" t="inlineStr">
@@ -4372,7 +4372,7 @@
     <row r="43">
       <c r="A43" s="43" t="inlineStr">
         <is>
-          <t>mobilize:824060:1773964800</t>
+          <t>mobilize:860202:1773964800</t>
         </is>
       </c>
       <c r="B43" s="44" t="b">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="E43" s="45" t="inlineStr">
         <is>
-          <t>Visibility Brigade - North Park</t>
+          <t>Weekly Meade Ave Bridge Bannering Over I-805 | Thursday Afternoons</t>
         </is>
       </c>
       <c r="F43" s="45" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="H43" s="44" t="inlineStr">
         <is>
-          <t>Meade Ave bridge over I-805 in North Park | 4371 Boundary St | San Diego, CA 92116</t>
+          <t>Meade Ave Bridge Over I-805 | 4371 Boundary St | San Diego, CA 92116</t>
         </is>
       </c>
       <c r="I43" s="45" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="K43" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisible/event/824060/</t>
+          <t>https://www.mobilize.us/visibilitybrigadesandiego/event/860202/</t>
         </is>
       </c>
       <c r="L43" s="47" t="inlineStr">
@@ -4652,7 +4652,7 @@
     <row r="48">
       <c r="A48" s="43" t="inlineStr">
         <is>
-          <t>mobilize:897984:1773919800</t>
+          <t>mobilize:870158:1773600300</t>
         </is>
       </c>
       <c r="B48" s="44" t="b">
@@ -4663,27 +4663,27 @@
       </c>
       <c r="D48" s="44" t="inlineStr">
         <is>
-          <t>2026-03-13T18:05:07</t>
+          <t>2026-03-09T15:27:00</t>
         </is>
       </c>
       <c r="E48" s="45" t="inlineStr">
         <is>
-          <t>Newton Bridge Brigade—Kendrick St Overpass</t>
+          <t>Needham Resists Visibility Brigade</t>
         </is>
       </c>
       <c r="F48" s="45" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G48" s="45" t="inlineStr">
         <is>
-          <t>7:30 AM</t>
+          <t>2:45 PM</t>
         </is>
       </c>
       <c r="H48" s="44" t="inlineStr">
         <is>
-          <t>Kendrick Street Overpass | Kendrick St, (Bridge over 128/95) | Needham, MA 02494</t>
+          <t>Kendrick Street Bridge over 95/128 (park at Cutler Park, 84 Kendrick St) | Kendrick Street | Needham, MA 02494</t>
         </is>
       </c>
       <c r="I48" s="45" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="K48" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/newtonindivisible/event/897984/</t>
+          <t>https://www.mobilize.us/needhamresistsvisibilitybrigade/event/870158/</t>
         </is>
       </c>
       <c r="L48" s="47" t="inlineStr">
@@ -4708,7 +4708,7 @@
     <row r="49">
       <c r="A49" s="43" t="inlineStr">
         <is>
-          <t>mobilize:870158:1773600300</t>
+          <t>mobilize:897984:1773919800</t>
         </is>
       </c>
       <c r="B49" s="44" t="b">
@@ -4719,27 +4719,27 @@
       </c>
       <c r="D49" s="44" t="inlineStr">
         <is>
-          <t>2026-03-09T15:27:00</t>
+          <t>2026-03-13T18:05:07</t>
         </is>
       </c>
       <c r="E49" s="45" t="inlineStr">
         <is>
-          <t>Needham Resists Visibility Brigade</t>
+          <t>Newton Bridge Brigade—Kendrick St Overpass</t>
         </is>
       </c>
       <c r="F49" s="45" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G49" s="45" t="inlineStr">
         <is>
-          <t>2:45 PM</t>
+          <t>7:30 AM</t>
         </is>
       </c>
       <c r="H49" s="44" t="inlineStr">
         <is>
-          <t>Kendrick Street Bridge over 95/128 (park at Cutler Park, 84 Kendrick St) | Kendrick Street | Needham, MA 02494</t>
+          <t>Kendrick Street Overpass | Kendrick St, (Bridge over 128/95) | Needham, MA 02494</t>
         </is>
       </c>
       <c r="I49" s="45" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="K49" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/needhamresistsvisibilitybrigade/event/870158/</t>
+          <t>https://www.mobilize.us/newtonindivisible/event/897984/</t>
         </is>
       </c>
       <c r="L49" s="47" t="inlineStr">
@@ -4932,43 +4932,43 @@
     <row r="53">
       <c r="A53" s="43" t="inlineStr">
         <is>
-          <t>mobilize:893656:1774045800</t>
+          <t>mobilize:807188:1773788400</t>
         </is>
       </c>
       <c r="B53" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53" s="44" t="b">
         <v>0</v>
       </c>
       <c r="D53" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-11T03:29:59</t>
         </is>
       </c>
       <c r="E53" s="45" t="inlineStr">
         <is>
-          <t>Fight Fascism Fridays - Every Friday in Rancho Cucamonga</t>
+          <t>Tesla Takedown Tuesday: Woodland Park Overpass!</t>
         </is>
       </c>
       <c r="F53" s="45" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G53" s="45" t="inlineStr">
         <is>
-          <t>3:30 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="H53" s="44" t="inlineStr">
         <is>
-          <t>Haven Avenue &amp; Foothill Boulevard | Rancho Cucamonga, CA 91730</t>
+          <t>Woodland Park N Pedestrian Bridge | 5192 Aurora Ave N | Seattle, WA 98103</t>
         </is>
       </c>
       <c r="I53" s="45" t="inlineStr">
         <is>
-          <t>Ontario Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="J53" s="45" t="n">
@@ -4976,19 +4976,19 @@
       </c>
       <c r="K53" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/catladiesforamerica/event/893656/</t>
+          <t>https://www.mobilize.us/seattleindivisible/event/807188/</t>
         </is>
       </c>
       <c r="L53" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="43" t="inlineStr">
         <is>
-          <t>mobilize:807188:1773788400</t>
+          <t>mobilize:893656:1774045800</t>
         </is>
       </c>
       <c r="B54" s="44" t="b">
@@ -4999,32 +4999,32 @@
       </c>
       <c r="D54" s="44" t="inlineStr">
         <is>
-          <t>2026-03-11T03:29:59</t>
+          <t>2026-03-14T09:08:59</t>
         </is>
       </c>
       <c r="E54" s="45" t="inlineStr">
         <is>
-          <t>Tesla Takedown Tuesday: Woodland Park Overpass!</t>
+          <t>Fight Fascism Fridays - Every Friday in Rancho Cucamonga</t>
         </is>
       </c>
       <c r="F54" s="45" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G54" s="45" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>3:30 PM</t>
         </is>
       </c>
       <c r="H54" s="44" t="inlineStr">
         <is>
-          <t>Woodland Park N Pedestrian Bridge | 5192 Aurora Ave N | Seattle, WA 98103</t>
+          <t>Haven Avenue &amp; Foothill Boulevard | Rancho Cucamonga, CA 91730</t>
         </is>
       </c>
       <c r="I54" s="45" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Ontario Mills</t>
         </is>
       </c>
       <c r="J54" s="45" t="n">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="K54" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/seattleindivisible/event/807188/</t>
+          <t>https://www.mobilize.us/catladiesforamerica/event/893656/</t>
         </is>
       </c>
       <c r="L54" s="47" t="inlineStr">
         <is>
-          <t>VISIBILITY_EVENT</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="B56" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" s="44" t="b">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="B60" s="49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" s="49" t="b">
         <v>0</v>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F2" s="10" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F3" s="15" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F4" s="15" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr">
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="B6" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="14" t="b">
         <v>0</v>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F6" s="15" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F7" s="15" t="inlineStr">
@@ -5909,7 +5909,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>mobilize:899401:1773504000</t>
+          <t>mobilize:801600:1773590400</t>
         </is>
       </c>
       <c r="B8" s="14" t="b">
@@ -5920,37 +5920,37 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-09T15:27:00</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>NO WARS!! NO KINGS Protest Airport Rotary Saturday, March 14th 12-1pm</t>
+          <t>Say No To Ken Calvert Weekly Visibility Sign Waving- Formerly Empty Chair Town Hall!</t>
         </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="H8" s="15" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>Airport Rotary | hyannnis, MA 02601</t>
+          <t>Intersection of Monterrey and 111- park at Panera | 73075 CA-111 | Palm Desert, CA 92260</t>
         </is>
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
-          <t>Cape Cod Mall</t>
+          <t>The Gardens on El Paseo</t>
         </is>
       </c>
       <c r="K8" s="15" t="n">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="L8" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisible/event/899401/</t>
+          <t>https://www.mobilize.us/indivisible/event/801600/</t>
         </is>
       </c>
       <c r="M8" s="17" t="inlineStr">
@@ -5970,7 +5970,7 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>mobilize:801600:1773590400</t>
+          <t>mobilize:899401:1773504000</t>
         </is>
       </c>
       <c r="B9" s="14" t="b">
@@ -5981,37 +5981,37 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>2026-03-09T15:27:00</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>Say No To Ken Calvert Weekly Visibility Sign Waving- Formerly Empty Chair Town Hall!</t>
+          <t>NO WARS!! NO KINGS Protest Airport Rotary Saturday, March 14th 12-1pm</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>Intersection of Monterrey and 111- park at Panera | 73075 CA-111 | Palm Desert, CA 92260</t>
+          <t>Airport Rotary | hyannnis, MA 02601</t>
         </is>
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
-          <t>The Gardens on El Paseo</t>
+          <t>Cape Cod Mall</t>
         </is>
       </c>
       <c r="K9" s="15" t="n">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="L9" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisible/event/801600/</t>
+          <t>https://www.mobilize.us/indivisible/event/899401/</t>
         </is>
       </c>
       <c r="M9" s="17" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
@@ -6275,7 +6275,7 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>mobilize:909535:1773865800</t>
+          <t>mobilize:791569:1773595800</t>
         </is>
       </c>
       <c r="B14" s="14" t="b">
@@ -6286,37 +6286,37 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-09T15:27:00</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>Bridge Brigade over Storrow Drive promoting NO KINGS -March 28</t>
+          <t>Menlo Park Speaks Out</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>4:30 PM</t>
+          <t>10:30 AM</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>Appleton Bridge over Storrow Drive to the Esplanade. (Easy access from Red line Charles St station.) | Frances Appleton Brg | Boston, MA 02114</t>
+          <t>Fremont Park | University Drive &amp; Santa Cruz Avenue | Menlo Park, CA 94025</t>
         </is>
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Stanford Shopping Center</t>
         </is>
       </c>
       <c r="K14" s="15" t="n">
@@ -6324,19 +6324,19 @@
       </c>
       <c r="L14" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/bostonindivisible/event/909535/</t>
+          <t>https://www.mobilize.us/menloparkspeaksout/event/791569/</t>
         </is>
       </c>
       <c r="M14" s="17" t="inlineStr">
         <is>
-          <t>VISIBILITY_EVENT</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>mobilize:791569:1773595800</t>
+          <t>mobilize:909535:1773865800</t>
         </is>
       </c>
       <c r="B15" s="14" t="b">
@@ -6347,37 +6347,37 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>2026-03-09T15:27:00</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>Menlo Park Speaks Out</t>
+          <t>Bridge Brigade over Storrow Drive promoting NO KINGS -March 28</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>4:30 PM</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>Fremont Park | University Drive &amp; Santa Cruz Avenue | Menlo Park, CA 94025</t>
+          <t>Appleton Bridge over Storrow Drive to the Esplanade. (Easy access from Red line Charles St station.) | Frances Appleton Brg | Boston, MA 02114</t>
         </is>
       </c>
       <c r="J15" s="15" t="inlineStr">
         <is>
-          <t>Stanford Shopping Center</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="K15" s="15" t="n">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="L15" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/menloparkspeaksout/event/791569/</t>
+          <t>https://www.mobilize.us/bostonindivisible/event/909535/</t>
         </is>
       </c>
       <c r="M15" s="17" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F17" s="25" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="E18" s="29" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F18" s="30" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="E19" s="29" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F19" s="30" t="inlineStr">
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="B20" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" s="29" t="b">
         <v>0</v>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="E20" s="29" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F20" s="30" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="E21" s="29" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F21" s="30" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="E22" s="29" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F22" s="30" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="E23" s="29" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F23" s="30" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F24" s="30" t="inlineStr">
@@ -6946,7 +6946,7 @@
     <row r="25">
       <c r="A25" s="28" t="inlineStr">
         <is>
-          <t>mobilize:875118:1773702000</t>
+          <t>mobilize:871084:1773702000</t>
         </is>
       </c>
       <c r="B25" s="29" t="b">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="E25" s="29" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F25" s="30" t="inlineStr">
         <is>
-          <t>Weekly Taylor St Bridge Bannering Over I-8 | Monday Afternoons - Visibility Brigade</t>
+          <t>Weekly Taylor St Bridge Bannering Over I-8 | Monday Afternoons</t>
         </is>
       </c>
       <c r="G25" s="30" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="L25" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisible/event/875118/</t>
+          <t>https://www.mobilize.us/visibilitybrigadesandiego/event/871084/</t>
         </is>
       </c>
       <c r="M25" s="32" t="inlineStr">
@@ -7007,7 +7007,7 @@
     <row r="26">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>mobilize:871084:1773702000</t>
+          <t>mobilize:875118:1773702000</t>
         </is>
       </c>
       <c r="B26" s="29" t="b">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="E26" s="29" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>Weekly Taylor St Bridge Bannering Over I-8 | Monday Afternoons</t>
+          <t>Weekly Taylor St Bridge Bannering Over I-8 | Monday Afternoons - Visibility Brigade</t>
         </is>
       </c>
       <c r="G26" s="30" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="L26" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/visibilitybrigadesandiego/event/871084/</t>
+          <t>https://www.mobilize.us/indivisible/event/875118/</t>
         </is>
       </c>
       <c r="M26" s="32" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="E27" s="29" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F27" s="30" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="E28" s="29" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F28" s="30" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="E29" s="29" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F29" s="30" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="E30" s="29" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F30" s="30" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="E31" s="29" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F31" s="30" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="E32" s="29" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F32" s="30" t="inlineStr">
@@ -7438,7 +7438,7 @@
         </is>
       </c>
       <c r="B33" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" s="29" t="b">
         <v>0</v>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="E33" s="29" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F33" s="30" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="E34" s="34" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F34" s="35" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="E35" s="39" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F35" s="40" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="E36" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F36" s="45" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="E37" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F37" s="45" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="E38" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F38" s="45" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="E39" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F39" s="45" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="E40" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F40" s="45" t="inlineStr">
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="B41" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" s="44" t="b">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="E41" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F41" s="45" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="E42" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F42" s="45" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="E43" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F43" s="45" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="E44" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F44" s="45" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="E45" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F45" s="45" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="E46" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F46" s="45" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="E47" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F47" s="45" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="E48" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F48" s="45" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="E49" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F49" s="45" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="E50" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F50" s="45" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="E51" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F51" s="45" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="E52" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F52" s="45" t="inlineStr">
@@ -8654,48 +8654,48 @@
     <row r="53">
       <c r="A53" s="43" t="inlineStr">
         <is>
-          <t>mobilize:893656:1774045800</t>
+          <t>mobilize:807188:1773788400</t>
         </is>
       </c>
       <c r="B53" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53" s="44" t="b">
         <v>0</v>
       </c>
       <c r="D53" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-11T03:29:59</t>
         </is>
       </c>
       <c r="E53" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F53" s="45" t="inlineStr">
         <is>
-          <t>Fight Fascism Fridays - Every Friday in Rancho Cucamonga</t>
+          <t>Tesla Takedown Tuesday: Woodland Park Overpass!</t>
         </is>
       </c>
       <c r="G53" s="45" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H53" s="45" t="inlineStr">
         <is>
-          <t>3:30 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="I53" s="44" t="inlineStr">
         <is>
-          <t>Haven Avenue &amp; Foothill Boulevard | Rancho Cucamonga, CA 91730</t>
+          <t>Woodland Park N Pedestrian Bridge | 5192 Aurora Ave N | Seattle, WA 98103</t>
         </is>
       </c>
       <c r="J53" s="45" t="inlineStr">
         <is>
-          <t>Ontario Mills</t>
+          <t>Northgate Station</t>
         </is>
       </c>
       <c r="K53" s="45" t="n">
@@ -8703,19 +8703,19 @@
       </c>
       <c r="L53" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/catladiesforamerica/event/893656/</t>
+          <t>https://www.mobilize.us/seattleindivisible/event/807188/</t>
         </is>
       </c>
       <c r="M53" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="43" t="inlineStr">
         <is>
-          <t>mobilize:807188:1773788400</t>
+          <t>mobilize:893656:1774045800</t>
         </is>
       </c>
       <c r="B54" s="44" t="b">
@@ -8726,37 +8726,37 @@
       </c>
       <c r="D54" s="44" t="inlineStr">
         <is>
-          <t>2026-03-11T03:29:59</t>
+          <t>2026-03-14T09:08:59</t>
         </is>
       </c>
       <c r="E54" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F54" s="45" t="inlineStr">
         <is>
-          <t>Tesla Takedown Tuesday: Woodland Park Overpass!</t>
+          <t>Fight Fascism Fridays - Every Friday in Rancho Cucamonga</t>
         </is>
       </c>
       <c r="G54" s="45" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H54" s="45" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>3:30 PM</t>
         </is>
       </c>
       <c r="I54" s="44" t="inlineStr">
         <is>
-          <t>Woodland Park N Pedestrian Bridge | 5192 Aurora Ave N | Seattle, WA 98103</t>
+          <t>Haven Avenue &amp; Foothill Boulevard | Rancho Cucamonga, CA 91730</t>
         </is>
       </c>
       <c r="J54" s="45" t="inlineStr">
         <is>
-          <t>Northgate Station</t>
+          <t>Ontario Mills</t>
         </is>
       </c>
       <c r="K54" s="45" t="n">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="L54" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/seattleindivisible/event/807188/</t>
+          <t>https://www.mobilize.us/catladiesforamerica/event/893656/</t>
         </is>
       </c>
       <c r="M54" s="47" t="inlineStr">
         <is>
-          <t>VISIBILITY_EVENT</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="E55" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F55" s="45" t="inlineStr">
@@ -8841,7 +8841,7 @@
         </is>
       </c>
       <c r="B56" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" s="44" t="b">
         <v>0</v>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="E56" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F56" s="45" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="E57" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F57" s="45" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="E58" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F58" s="45" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="E59" s="44" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F59" s="45" t="inlineStr">
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="B60" s="49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" s="49" t="b">
         <v>0</v>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="E60" s="49" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-14T10:05:09</t>
         </is>
       </c>
       <c r="F60" s="50" t="inlineStr">
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="B6" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="14" t="b">
         <v>0</v>
@@ -9635,7 +9635,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>mobilize:900830:1774735200</t>
+          <t>mobilize:894448:1774735200</t>
         </is>
       </c>
       <c r="B8" s="14" t="b">
@@ -9646,12 +9646,12 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>NO KINGS Santa Rosa, CA</t>
+          <t>No Kings III - SANTA ROSA (mirror)</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>Old Courthouse Square | 3rd Street &amp; Santa Rosa Avenue | Santa Rosa, CA 95404</t>
+          <t>Old Courthouse Square | 3rd Street &amp; Santa Rosa Avenue | Santa Rosa, CA 95401</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="K8" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/900830/</t>
+          <t>https://www.mobilize.us/indivisiblesonomacounty/event/894448/</t>
         </is>
       </c>
       <c r="L8" s="17" t="inlineStr">
@@ -9691,7 +9691,7 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>mobilize:894448:1774735200</t>
+          <t>mobilize:900830:1774735200</t>
         </is>
       </c>
       <c r="B9" s="14" t="b">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>No Kings III - SANTA ROSA (mirror)</t>
+          <t>NO KINGS Santa Rosa, CA</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>Old Courthouse Square | 3rd Street &amp; Santa Rosa Avenue | Santa Rosa, CA 95401</t>
+          <t>Old Courthouse Square | 3rd Street &amp; Santa Rosa Avenue | Santa Rosa, CA 95404</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="K9" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisiblesonomacounty/event/894448/</t>
+          <t>https://www.mobilize.us/nokings/event/900830/</t>
         </is>
       </c>
       <c r="L9" s="17" t="inlineStr">
@@ -9859,7 +9859,7 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>mobilize:910199:1774720800</t>
+          <t>mobilize:909736:1774717200</t>
         </is>
       </c>
       <c r="B12" s="14" t="b">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>NO KINGS WESLEY CHAPEL, FL</t>
+          <t>NO KINGS SPRINGFIELD MISSOURI</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
@@ -9885,17 +9885,17 @@
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Florida 56 &amp; Grand Cypress Drive | Wesley Chapel, FL 33559</t>
+          <t>East Battlefield Road &amp; Glenstone Avenue | Springfield, MO 65804</t>
         </is>
       </c>
       <c r="I12" s="15" t="inlineStr">
         <is>
-          <t>Tampa Premium Outlets</t>
+          <t>Battlefield Mall</t>
         </is>
       </c>
       <c r="J12" s="15" t="n">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="K12" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/910199/</t>
+          <t>https://www.mobilize.us/nokings/event/909736/</t>
         </is>
       </c>
       <c r="L12" s="17" t="inlineStr">
@@ -9915,7 +9915,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>mobilize:909736:1774717200</t>
+          <t>mobilize:910199:1774720800</t>
         </is>
       </c>
       <c r="B13" s="14" t="b">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>NO KINGS SPRINGFIELD MISSOURI</t>
+          <t>NO KINGS WESLEY CHAPEL, FL</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
@@ -9941,17 +9941,17 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>East Battlefield Road &amp; Glenstone Avenue | Springfield, MO 65804</t>
+          <t>Florida 56 &amp; Grand Cypress Drive | Wesley Chapel, FL 33559</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
-          <t>Battlefield Mall</t>
+          <t>Tampa Premium Outlets</t>
         </is>
       </c>
       <c r="J13" s="15" t="n">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="K13" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/909736/</t>
+          <t>https://www.mobilize.us/nokings/event/910199/</t>
         </is>
       </c>
       <c r="L13" s="17" t="inlineStr">
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="B14" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" s="14" t="b">
         <v>0</v>
@@ -10419,7 +10419,7 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>mobilize:899414:1775318400</t>
+          <t>mobilize:899401:1773504000</t>
         </is>
       </c>
       <c r="B22" s="14" t="b">
@@ -10430,17 +10430,17 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>NO KINGS! Protest Airport Rotary Saturday, April 4th 12-1pm</t>
+          <t>NO WARS!! NO KINGS Protest Airport Rotary Saturday, March 14th 12-1pm</t>
         </is>
       </c>
       <c r="F22" s="15" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G22" s="15" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Airport Rotary | Hyannis, MA 02601</t>
+          <t>Airport Rotary | hyannnis, MA 02601</t>
         </is>
       </c>
       <c r="I22" s="15" t="inlineStr">
@@ -10463,7 +10463,7 @@
       </c>
       <c r="K22" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisible/event/899414/</t>
+          <t>https://www.mobilize.us/indivisible/event/899401/</t>
         </is>
       </c>
       <c r="L22" s="17" t="inlineStr">
@@ -10475,7 +10475,7 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>mobilize:906121:1774713600</t>
+          <t>mobilize:903789:1774710000</t>
         </is>
       </c>
       <c r="B23" s="14" t="b">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>NO KINGS Hyannis Airport Rotary - Cape Cod</t>
+          <t>Volunteer for Safety Marshal for March 28 No Kings</t>
         </is>
       </c>
       <c r="F23" s="15" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="G23" s="15" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>Hyannis Airport Rotary | Airport Rotary | Hyannis, MA 02601</t>
+          <t>Airport Rotary | Hyannis Airport Rotary, Hyannis, MA | Hyannis, MA 02601</t>
         </is>
       </c>
       <c r="I23" s="15" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="K23" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/906121/</t>
+          <t>https://www.mobilize.us/indivisible/event/903789/</t>
         </is>
       </c>
       <c r="L23" s="17" t="inlineStr">
@@ -10587,7 +10587,7 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>mobilize:899401:1773504000</t>
+          <t>mobilize:906121:1774713600</t>
         </is>
       </c>
       <c r="B25" s="14" t="b">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>NO WARS!! NO KINGS Protest Airport Rotary Saturday, March 14th 12-1pm</t>
+          <t>NO KINGS Hyannis Airport Rotary - Cape Cod</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Airport Rotary | hyannnis, MA 02601</t>
+          <t>Hyannis Airport Rotary | Airport Rotary | Hyannis, MA 02601</t>
         </is>
       </c>
       <c r="I25" s="15" t="inlineStr">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="K25" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisible/event/899401/</t>
+          <t>https://www.mobilize.us/nokings/event/906121/</t>
         </is>
       </c>
       <c r="L25" s="17" t="inlineStr">
@@ -10643,7 +10643,7 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>mobilize:903789:1774710000</t>
+          <t>mobilize:899414:1775318400</t>
         </is>
       </c>
       <c r="B26" s="14" t="b">
@@ -10659,22 +10659,22 @@
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>Volunteer for Safety Marshal for March 28 No Kings</t>
+          <t>NO KINGS! Protest Airport Rotary Saturday, April 4th 12-1pm</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Airport Rotary | Hyannis Airport Rotary, Hyannis, MA | Hyannis, MA 02601</t>
+          <t>Airport Rotary | Hyannis, MA 02601</t>
         </is>
       </c>
       <c r="I26" s="15" t="inlineStr">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="K26" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisible/event/903789/</t>
+          <t>https://www.mobilize.us/indivisible/event/899414/</t>
         </is>
       </c>
       <c r="L26" s="17" t="inlineStr">
@@ -10921,114 +10921,114 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="53" t="inlineStr">
+        <is>
+          <t>mobilize:905953:1774720800</t>
+        </is>
+      </c>
+      <c r="B31" s="54" t="b">
+        <v>0</v>
+      </c>
+      <c r="C31" s="54" t="b">
+        <v>1</v>
+      </c>
+      <c r="D31" s="54" t="inlineStr">
+        <is>
+          <t>2026-03-10T15:14:09</t>
+        </is>
+      </c>
+      <c r="E31" s="55" t="inlineStr">
+        <is>
+          <t>NO KINGS WEST HOLLYWOOD</t>
+        </is>
+      </c>
+      <c r="F31" s="55" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G31" s="55" t="inlineStr">
+        <is>
+          <t>11:00 AM</t>
+        </is>
+      </c>
+      <c r="H31" s="54" t="inlineStr">
+        <is>
+          <t>West Hollywood Park | 647 N San Vicente Blvd | West Hollywood, CA 90069</t>
+        </is>
+      </c>
+      <c r="I31" s="55" t="inlineStr">
+        <is>
+          <t>Beverly Center</t>
+        </is>
+      </c>
+      <c r="J31" s="55" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K31" s="54" t="inlineStr">
+        <is>
+          <t>https://www.mobilize.us/nokings/event/905953/</t>
+        </is>
+      </c>
+      <c r="L31" s="56" t="inlineStr">
+        <is>
+          <t>RALLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>mobilize:918389:1774720800</t>
         </is>
       </c>
-      <c r="B31" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="C31" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="C32" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>2026-03-12T05:20:25</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>No Kings in West Hollywood Park with Dayenu</t>
         </is>
       </c>
-      <c r="F31" s="15" t="inlineStr">
+      <c r="F32" s="15" t="inlineStr">
         <is>
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="G31" s="15" t="inlineStr">
+      <c r="G32" s="15" t="inlineStr">
         <is>
           <t>11:00 AM</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="H32" s="14" t="inlineStr">
         <is>
           <t>West Hollywood Park | 647 N San Vicente Blvd | West Hollywood, CA 90069</t>
         </is>
       </c>
-      <c r="I31" s="15" t="inlineStr">
+      <c r="I32" s="15" t="inlineStr">
         <is>
           <t>Beverly Center</t>
         </is>
       </c>
-      <c r="J31" s="15" t="n">
+      <c r="J32" s="15" t="n">
         <v>0.65</v>
       </c>
-      <c r="K31" s="16" t="inlineStr">
+      <c r="K32" s="16" t="inlineStr">
         <is>
           <t>https://www.mobilize.us/dayenu/event/918389/</t>
         </is>
       </c>
-      <c r="L31" s="17" t="inlineStr">
+      <c r="L32" s="17" t="inlineStr">
         <is>
           <t>ADVOCACY</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="53" t="inlineStr">
-        <is>
-          <t>mobilize:905953:1774720800</t>
-        </is>
-      </c>
-      <c r="B32" s="54" t="b">
-        <v>0</v>
-      </c>
-      <c r="C32" s="54" t="b">
-        <v>1</v>
-      </c>
-      <c r="D32" s="54" t="inlineStr">
-        <is>
-          <t>2026-03-10T15:14:09</t>
-        </is>
-      </c>
-      <c r="E32" s="55" t="inlineStr">
-        <is>
-          <t>NO KINGS WEST HOLLYWOOD</t>
-        </is>
-      </c>
-      <c r="F32" s="55" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G32" s="55" t="inlineStr">
-        <is>
-          <t>11:00 AM</t>
-        </is>
-      </c>
-      <c r="H32" s="54" t="inlineStr">
-        <is>
-          <t>West Hollywood Park | 647 N San Vicente Blvd | West Hollywood, CA 90069</t>
-        </is>
-      </c>
-      <c r="I32" s="55" t="inlineStr">
-        <is>
-          <t>Beverly Center</t>
-        </is>
-      </c>
-      <c r="J32" s="55" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="K32" s="54" t="inlineStr">
-        <is>
-          <t>https://www.mobilize.us/nokings/event/905953/</t>
-        </is>
-      </c>
-      <c r="L32" s="56" t="inlineStr">
-        <is>
-          <t>RALLY</t>
         </is>
       </c>
     </row>
@@ -11651,23 +11651,23 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>mobilize:901078:1774731600</t>
+          <t>mobilize:905855:1774720800</t>
         </is>
       </c>
       <c r="B44" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44" s="14" t="b">
         <v>0</v>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>2026-03-14T09:08:59</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>NO KINGS Santa Rosa, CA - SRJC March to Old Courthouse Square</t>
+          <t>NO Kings Richfield-66th St Sidewalk Rally</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
@@ -11677,17 +11677,17 @@
       </c>
       <c r="G44" s="15" t="inlineStr">
         <is>
-          <t>2:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>SRJC (March begins at 3pm; please assemble 1:30-2 pm) | Mendocino Ave &amp; Carr Street | Santa Rosa, CA 95401</t>
+          <t>Penn Avenue South &amp; West 66th Street, West 66th Street and Lyndale Ave | Richfield, MN 55423</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
-          <t>Santa Rosa Plaza</t>
+          <t>Southdale Center</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="K44" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/901078/</t>
+          <t>https://www.mobilize.us/nokings/event/905855/</t>
         </is>
       </c>
       <c r="L44" s="17" t="inlineStr">
@@ -11707,7 +11707,7 @@
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>mobilize:905855:1774720800</t>
+          <t>mobilize:913357:1774720800</t>
         </is>
       </c>
       <c r="B45" s="14" t="b">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>NO Kings Richfield-66th St Sidewalk Rally</t>
+          <t>Richfield 66th St.  Rally for No Kings Day 3.0</t>
         </is>
       </c>
       <c r="F45" s="15" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>Penn Avenue South &amp; West 66th Street, West 66th Street and Lyndale Ave | Richfield, MN 55423</t>
+          <t>West 66th Street &amp; Penn Avenue South | Richfield, MN 55423</t>
         </is>
       </c>
       <c r="I45" s="15" t="inlineStr">
@@ -11751,19 +11751,19 @@
       </c>
       <c r="K45" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/905855/</t>
+          <t>https://www.mobilize.us/nokings/event/913357/</t>
         </is>
       </c>
       <c r="L45" s="17" t="inlineStr">
         <is>
-          <t>VISIBILITY_EVENT</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>mobilize:913357:1774720800</t>
+          <t>mobilize:901078:1774731600</t>
         </is>
       </c>
       <c r="B46" s="14" t="b">
@@ -11774,12 +11774,12 @@
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-14T09:08:59</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Richfield 66th St.  Rally for No Kings Day 3.0</t>
+          <t>NO KINGS Santa Rosa, CA - SRJC March to Old Courthouse Square</t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
@@ -11789,17 +11789,17 @@
       </c>
       <c r="G46" s="15" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>2:00 PM</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>West 66th Street &amp; Penn Avenue South | Richfield, MN 55423</t>
+          <t>SRJC (March begins at 3pm; please assemble 1:30-2 pm) | Mendocino Ave &amp; Carr Street | Santa Rosa, CA 95401</t>
         </is>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
-          <t>Southdale Center</t>
+          <t>Santa Rosa Plaza</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="K46" s="16" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/913357/</t>
+          <t>https://www.mobilize.us/nokings/event/901078/</t>
         </is>
       </c>
       <c r="L46" s="17" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
@@ -12603,7 +12603,7 @@
     <row r="61">
       <c r="A61" s="28" t="inlineStr">
         <is>
-          <t>mobilize:909677:1774728000</t>
+          <t>mobilize:912299:1774717200</t>
         </is>
       </c>
       <c r="B61" s="29" t="b">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="E61" s="30" t="inlineStr">
         <is>
-          <t>NO KINGS Napa</t>
+          <t>NO KINGS Tulalip/Marysville</t>
         </is>
       </c>
       <c r="F61" s="30" t="inlineStr">
@@ -12629,17 +12629,17 @@
       </c>
       <c r="G61" s="30" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="H61" s="29" t="inlineStr">
         <is>
-          <t>Oxbow Commons | 1268 McKinstry St | Napa, CA 94559</t>
+          <t>I-5 and 88th St Overpass | 88th St NE | Tulalip/Marysville, WA 98271</t>
         </is>
       </c>
       <c r="I61" s="30" t="inlineStr">
         <is>
-          <t>Napa Premium Outlets</t>
+          <t>Seattle Premium Outlets</t>
         </is>
       </c>
       <c r="J61" s="30" t="n">
@@ -12647,124 +12647,124 @@
       </c>
       <c r="K61" s="31" t="inlineStr">
         <is>
+          <t>https://www.mobilize.us/nokings/event/912299/</t>
+        </is>
+      </c>
+      <c r="L61" s="32" t="inlineStr">
+        <is>
+          <t>VISIBILITY_EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="28" t="inlineStr">
+        <is>
+          <t>mobilize:901623:1774728000</t>
+        </is>
+      </c>
+      <c r="B62" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="C62" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D62" s="29" t="inlineStr">
+        <is>
+          <t>2026-03-08T07:16:44</t>
+        </is>
+      </c>
+      <c r="E62" s="30" t="inlineStr">
+        <is>
+          <t>NO KINGS Napa</t>
+        </is>
+      </c>
+      <c r="F62" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G62" s="30" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="H62" s="29" t="inlineStr">
+        <is>
+          <t>Oxbow Commons | 1268 McKinstry St | Napa, CA 94559</t>
+        </is>
+      </c>
+      <c r="I62" s="30" t="inlineStr">
+        <is>
+          <t>Napa Premium Outlets</t>
+        </is>
+      </c>
+      <c r="J62" s="30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="K62" s="31" t="inlineStr">
+        <is>
+          <t>https://www.mobilize.us/nokings/event/901623/</t>
+        </is>
+      </c>
+      <c r="L62" s="32" t="inlineStr">
+        <is>
+          <t>RALLY</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="57" t="inlineStr">
+        <is>
+          <t>mobilize:909677:1774728000</t>
+        </is>
+      </c>
+      <c r="B63" s="58" t="b">
+        <v>0</v>
+      </c>
+      <c r="C63" s="58" t="b">
+        <v>1</v>
+      </c>
+      <c r="D63" s="58" t="inlineStr">
+        <is>
+          <t>2026-03-08T07:16:44</t>
+        </is>
+      </c>
+      <c r="E63" s="59" t="inlineStr">
+        <is>
+          <t>NO KINGS Napa</t>
+        </is>
+      </c>
+      <c r="F63" s="59" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G63" s="59" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="H63" s="58" t="inlineStr">
+        <is>
+          <t>Oxbow Commons | 1268 McKinstry St | Napa, CA 94559</t>
+        </is>
+      </c>
+      <c r="I63" s="59" t="inlineStr">
+        <is>
+          <t>Napa Premium Outlets</t>
+        </is>
+      </c>
+      <c r="J63" s="59" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="K63" s="58" t="inlineStr">
+        <is>
           <t>https://www.mobilize.us/nokings/event/909677/</t>
         </is>
       </c>
-      <c r="L61" s="32" t="inlineStr">
+      <c r="L63" s="60" t="inlineStr">
         <is>
           <t>RALLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="57" t="inlineStr">
-        <is>
-          <t>mobilize:901623:1774728000</t>
-        </is>
-      </c>
-      <c r="B62" s="58" t="b">
-        <v>0</v>
-      </c>
-      <c r="C62" s="58" t="b">
-        <v>1</v>
-      </c>
-      <c r="D62" s="58" t="inlineStr">
-        <is>
-          <t>2026-03-08T07:16:44</t>
-        </is>
-      </c>
-      <c r="E62" s="59" t="inlineStr">
-        <is>
-          <t>NO KINGS Napa</t>
-        </is>
-      </c>
-      <c r="F62" s="59" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G62" s="59" t="inlineStr">
-        <is>
-          <t>1:00 PM</t>
-        </is>
-      </c>
-      <c r="H62" s="58" t="inlineStr">
-        <is>
-          <t>Oxbow Commons | 1268 McKinstry St | Napa, CA 94559</t>
-        </is>
-      </c>
-      <c r="I62" s="59" t="inlineStr">
-        <is>
-          <t>Napa Premium Outlets</t>
-        </is>
-      </c>
-      <c r="J62" s="59" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="K62" s="58" t="inlineStr">
-        <is>
-          <t>https://www.mobilize.us/nokings/event/901623/</t>
-        </is>
-      </c>
-      <c r="L62" s="60" t="inlineStr">
-        <is>
-          <t>RALLY</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="28" t="inlineStr">
-        <is>
-          <t>mobilize:912299:1774717200</t>
-        </is>
-      </c>
-      <c r="B63" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="C63" s="29" t="b">
-        <v>0</v>
-      </c>
-      <c r="D63" s="29" t="inlineStr">
-        <is>
-          <t>2026-03-08T07:16:44</t>
-        </is>
-      </c>
-      <c r="E63" s="30" t="inlineStr">
-        <is>
-          <t>NO KINGS Tulalip/Marysville</t>
-        </is>
-      </c>
-      <c r="F63" s="30" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G63" s="30" t="inlineStr">
-        <is>
-          <t>10:00 AM</t>
-        </is>
-      </c>
-      <c r="H63" s="29" t="inlineStr">
-        <is>
-          <t>I-5 and 88th St Overpass | 88th St NE | Tulalip/Marysville, WA 98271</t>
-        </is>
-      </c>
-      <c r="I63" s="30" t="inlineStr">
-        <is>
-          <t>Seattle Premium Outlets</t>
-        </is>
-      </c>
-      <c r="J63" s="30" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="K63" s="31" t="inlineStr">
-        <is>
-          <t>https://www.mobilize.us/nokings/event/912299/</t>
-        </is>
-      </c>
-      <c r="L63" s="32" t="inlineStr">
-        <is>
-          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
@@ -13275,7 +13275,7 @@
     <row r="73">
       <c r="A73" s="28" t="inlineStr">
         <is>
-          <t>mobilize:918680:1774737000</t>
+          <t>mobilize:900775:1774737000</t>
         </is>
       </c>
       <c r="B73" s="29" t="b">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="D73" s="29" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E73" s="30" t="inlineStr">
         <is>
-          <t>No Kings in Pico-Robertson with Dayenu</t>
+          <t>NO KINGS Pico-Robertson Neighborhood (At Pico and LaCienega)</t>
         </is>
       </c>
       <c r="F73" s="30" t="inlineStr">
@@ -13319,19 +13319,19 @@
       </c>
       <c r="K73" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/dayenu/event/918680/</t>
+          <t>https://www.mobilize.us/nokings/event/900775/</t>
         </is>
       </c>
       <c r="L73" s="32" t="inlineStr">
         <is>
-          <t>ADVOCACY</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="28" t="inlineStr">
         <is>
-          <t>mobilize:900775:1774737000</t>
+          <t>mobilize:918680:1774737000</t>
         </is>
       </c>
       <c r="B74" s="29" t="b">
@@ -13342,12 +13342,12 @@
       </c>
       <c r="D74" s="29" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E74" s="30" t="inlineStr">
         <is>
-          <t>NO KINGS Pico-Robertson Neighborhood (At Pico and LaCienega)</t>
+          <t>No Kings in Pico-Robertson with Dayenu</t>
         </is>
       </c>
       <c r="F74" s="30" t="inlineStr">
@@ -13375,19 +13375,19 @@
       </c>
       <c r="K74" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/900775/</t>
+          <t>https://www.mobilize.us/dayenu/event/918680/</t>
         </is>
       </c>
       <c r="L74" s="32" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>ADVOCACY</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="28" t="inlineStr">
         <is>
-          <t>mobilize:906200:1774713600</t>
+          <t>mobilize:902986:1774717200</t>
         </is>
       </c>
       <c r="B75" s="29" t="b">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="E75" s="30" t="inlineStr">
         <is>
-          <t>NO KINGS Danvers</t>
+          <t>NO KINGS Loudoun - Rt 7 overpass at Crosstrail Blvd</t>
         </is>
       </c>
       <c r="F75" s="30" t="inlineStr">
@@ -13413,17 +13413,17 @@
       </c>
       <c r="G75" s="30" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="H75" s="29" t="inlineStr">
         <is>
-          <t>Route 114 Bridge on Andover St. Danvers Ma | 100 Brooksby Village Dr Peabody MA, Intersects with Garden St. Danvers Ma | Peabody, MA 01960</t>
+          <t>Rt 7 overpass at Crosstrail Blvd | 101 Crosstrail Blvd | Leesburg, VA 20175</t>
         </is>
       </c>
       <c r="I75" s="30" t="inlineStr">
         <is>
-          <t>Northshore Mall</t>
+          <t>Leesburg Premium Outlets</t>
         </is>
       </c>
       <c r="J75" s="30" t="n">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="K75" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/906200/</t>
+          <t>https://www.mobilize.us/nokings/event/902986/</t>
         </is>
       </c>
       <c r="L75" s="32" t="inlineStr">
@@ -13443,7 +13443,7 @@
     <row r="76">
       <c r="A76" s="28" t="inlineStr">
         <is>
-          <t>mobilize:902986:1774717200</t>
+          <t>mobilize:906200:1774713600</t>
         </is>
       </c>
       <c r="B76" s="29" t="b">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="E76" s="30" t="inlineStr">
         <is>
-          <t>NO KINGS Loudoun - Rt 7 overpass at Crosstrail Blvd</t>
+          <t>NO KINGS Danvers</t>
         </is>
       </c>
       <c r="F76" s="30" t="inlineStr">
@@ -13469,17 +13469,17 @@
       </c>
       <c r="G76" s="30" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="H76" s="29" t="inlineStr">
         <is>
-          <t>Rt 7 overpass at Crosstrail Blvd | 101 Crosstrail Blvd | Leesburg, VA 20175</t>
+          <t>Route 114 Bridge on Andover St. Danvers Ma | 100 Brooksby Village Dr Peabody MA, Intersects with Garden St. Danvers Ma | Peabody, MA 01960</t>
         </is>
       </c>
       <c r="I76" s="30" t="inlineStr">
         <is>
-          <t>Leesburg Premium Outlets</t>
+          <t>Northshore Mall</t>
         </is>
       </c>
       <c r="J76" s="30" t="n">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="K76" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/902986/</t>
+          <t>https://www.mobilize.us/nokings/event/906200/</t>
         </is>
       </c>
       <c r="L76" s="32" t="inlineStr">
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="B84" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C84" s="29" t="b">
         <v>0</v>
@@ -14231,7 +14231,7 @@
         </is>
       </c>
       <c r="B90" s="29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C90" s="29" t="b">
         <v>0</v>
@@ -14395,7 +14395,7 @@
     <row r="93">
       <c r="A93" s="28" t="inlineStr">
         <is>
-          <t>mobilize:916537:1774706400</t>
+          <t>mobilize:901796:1774717200</t>
         </is>
       </c>
       <c r="B93" s="29" t="b">
@@ -14406,12 +14406,12 @@
       </c>
       <c r="D93" s="29" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E93" s="30" t="inlineStr">
         <is>
-          <t>NO KINGS: Greenburgh, NY</t>
+          <t>No Kings- WOFA HANDS ACROSS ARLINGTON</t>
         </is>
       </c>
       <c r="F93" s="30" t="inlineStr">
@@ -14421,17 +14421,17 @@
       </c>
       <c r="G93" s="30" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="H93" s="29" t="inlineStr">
         <is>
-          <t>Town of Greenburgh Town Hall | 177 Hillside Ave | White Plains, NY 10607</t>
+          <t>125 S Old Glebe Rd | Arlington, VA 22204</t>
         </is>
       </c>
       <c r="I93" s="30" t="inlineStr">
         <is>
-          <t>The Westchester</t>
+          <t>Fashion Center at Pentagon City</t>
         </is>
       </c>
       <c r="J93" s="30" t="n">
@@ -14439,19 +14439,19 @@
       </c>
       <c r="K93" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/916537/</t>
+          <t>https://www.mobilize.us/nokings/event/901796/</t>
         </is>
       </c>
       <c r="L93" s="32" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="28" t="inlineStr">
         <is>
-          <t>mobilize:901796:1774717200</t>
+          <t>mobilize:916537:1774706400</t>
         </is>
       </c>
       <c r="B94" s="29" t="b">
@@ -14462,12 +14462,12 @@
       </c>
       <c r="D94" s="29" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E94" s="30" t="inlineStr">
         <is>
-          <t>No Kings- WOFA HANDS ACROSS ARLINGTON</t>
+          <t>NO KINGS: Greenburgh, NY</t>
         </is>
       </c>
       <c r="F94" s="30" t="inlineStr">
@@ -14477,17 +14477,17 @@
       </c>
       <c r="G94" s="30" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="H94" s="29" t="inlineStr">
         <is>
-          <t>125 S Old Glebe Rd | Arlington, VA 22204</t>
+          <t>Town of Greenburgh Town Hall | 177 Hillside Ave | White Plains, NY 10607</t>
         </is>
       </c>
       <c r="I94" s="30" t="inlineStr">
         <is>
-          <t>Fashion Center at Pentagon City</t>
+          <t>The Westchester</t>
         </is>
       </c>
       <c r="J94" s="30" t="n">
@@ -14495,12 +14495,12 @@
       </c>
       <c r="K94" s="31" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/901796/</t>
+          <t>https://www.mobilize.us/nokings/event/916537/</t>
         </is>
       </c>
       <c r="L94" s="32" t="inlineStr">
         <is>
-          <t>VISIBILITY_EVENT</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
@@ -15179,7 +15179,7 @@
     <row r="107">
       <c r="A107" s="43" t="inlineStr">
         <is>
-          <t>mobilize:903863:1774720800</t>
+          <t>mobilize:914833:1774565100</t>
         </is>
       </c>
       <c r="B107" s="44" t="b">
@@ -15190,32 +15190,32 @@
       </c>
       <c r="D107" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E107" s="45" t="inlineStr">
         <is>
-          <t>❌👑 NO KINGS 3 – DENVER 👑❌</t>
+          <t>No Kings: Sign-making!!</t>
         </is>
       </c>
       <c r="F107" s="45" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G107" s="45" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>6:45 PM</t>
         </is>
       </c>
       <c r="H107" s="44" t="inlineStr">
         <is>
-          <t>Colorado State Capitol | 200 E Colfax Ave | Denver, CO 80203</t>
+          <t>United Parish in Brookline | 15 Marion St | Brookline, MA 02446</t>
         </is>
       </c>
       <c r="I107" s="45" t="inlineStr">
         <is>
-          <t>Cherry Creek Shopping Center</t>
+          <t>Copley Place</t>
         </is>
       </c>
       <c r="J107" s="45" t="n">
@@ -15223,19 +15223,19 @@
       </c>
       <c r="K107" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/903863/</t>
+          <t>https://www.mobilize.us/activisteveningsbrookline/event/914833/</t>
         </is>
       </c>
       <c r="L107" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="43" t="inlineStr">
         <is>
-          <t>mobilize:914833:1774565100</t>
+          <t>mobilize:903863:1774720800</t>
         </is>
       </c>
       <c r="B108" s="44" t="b">
@@ -15246,32 +15246,32 @@
       </c>
       <c r="D108" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E108" s="45" t="inlineStr">
         <is>
-          <t>No Kings: Sign-making!!</t>
+          <t>❌👑 NO KINGS 3 – DENVER 👑❌</t>
         </is>
       </c>
       <c r="F108" s="45" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G108" s="45" t="inlineStr">
         <is>
-          <t>6:45 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="H108" s="44" t="inlineStr">
         <is>
-          <t>United Parish in Brookline | 15 Marion St | Brookline, MA 02446</t>
+          <t>Colorado State Capitol | 200 E Colfax Ave | Denver, CO 80203</t>
         </is>
       </c>
       <c r="I108" s="45" t="inlineStr">
         <is>
-          <t>Copley Place</t>
+          <t>Cherry Creek Shopping Center</t>
         </is>
       </c>
       <c r="J108" s="45" t="n">
@@ -15279,12 +15279,12 @@
       </c>
       <c r="K108" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/activisteveningsbrookline/event/914833/</t>
+          <t>https://www.mobilize.us/nokings/event/903863/</t>
         </is>
       </c>
       <c r="L108" s="47" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="B115" s="44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C115" s="44" t="b">
         <v>0</v>
@@ -15963,7 +15963,7 @@
     <row r="121">
       <c r="A121" s="43" t="inlineStr">
         <is>
-          <t>mobilize:900828:1774713600</t>
+          <t>mobilize:920352:1774386900</t>
         </is>
       </c>
       <c r="B121" s="44" t="b">
@@ -15974,32 +15974,32 @@
       </c>
       <c r="D121" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-13T18:05:07</t>
         </is>
       </c>
       <c r="E121" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Miami</t>
+          <t>No Kings Twin Cities Sips and Signs-Washburn Library</t>
         </is>
       </c>
       <c r="F121" s="45" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G121" s="45" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>4:15 PM</t>
         </is>
       </c>
       <c r="H121" s="44" t="inlineStr">
         <is>
-          <t>Tropical Park | 7900 SW 40th St | Miami, FL 33155</t>
+          <t>Washburn Library | 5244 Lyndale Ave S | Minneapolis, MN 55419</t>
         </is>
       </c>
       <c r="I121" s="45" t="inlineStr">
         <is>
-          <t>Dadeland Mall</t>
+          <t>Southdale Center</t>
         </is>
       </c>
       <c r="J121" s="45" t="n">
@@ -16007,19 +16007,19 @@
       </c>
       <c r="K121" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/900828/</t>
+          <t>https://www.mobilize.us/indivisibletwincities/event/920352/</t>
         </is>
       </c>
       <c r="L121" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>COMMUNITY</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="43" t="inlineStr">
         <is>
-          <t>mobilize:920352:1774386900</t>
+          <t>mobilize:900828:1774713600</t>
         </is>
       </c>
       <c r="B122" s="44" t="b">
@@ -16030,32 +16030,32 @@
       </c>
       <c r="D122" s="44" t="inlineStr">
         <is>
-          <t>2026-03-13T18:05:07</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E122" s="45" t="inlineStr">
         <is>
-          <t>No Kings Twin Cities Sips and Signs-Washburn Library</t>
+          <t>NO KINGS Miami</t>
         </is>
       </c>
       <c r="F122" s="45" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G122" s="45" t="inlineStr">
         <is>
-          <t>4:15 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="H122" s="44" t="inlineStr">
         <is>
-          <t>Washburn Library | 5244 Lyndale Ave S | Minneapolis, MN 55419</t>
+          <t>Tropical Park | 7900 SW 40th St | Miami, FL 33155</t>
         </is>
       </c>
       <c r="I122" s="45" t="inlineStr">
         <is>
-          <t>Southdale Center</t>
+          <t>Dadeland Mall</t>
         </is>
       </c>
       <c r="J122" s="45" t="n">
@@ -16063,19 +16063,19 @@
       </c>
       <c r="K122" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisibletwincities/event/920352/</t>
+          <t>https://www.mobilize.us/nokings/event/900828/</t>
         </is>
       </c>
       <c r="L122" s="47" t="inlineStr">
         <is>
-          <t>COMMUNITY</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="43" t="inlineStr">
         <is>
-          <t>mobilize:917329:1774724400</t>
+          <t>mobilize:906022:1774729800</t>
         </is>
       </c>
       <c r="B123" s="44" t="b">
@@ -16086,12 +16086,12 @@
       </c>
       <c r="D123" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E123" s="45" t="inlineStr">
         <is>
-          <t>Volunteer for No Kings Tri-Valley 3</t>
+          <t>NO KINGS Tri-Valley</t>
         </is>
       </c>
       <c r="F123" s="45" t="inlineStr">
@@ -16101,7 +16101,7 @@
       </c>
       <c r="G123" s="45" t="inlineStr">
         <is>
-          <t>12:00 PM</t>
+          <t>1:30 PM</t>
         </is>
       </c>
       <c r="H123" s="44" t="inlineStr">
@@ -16119,19 +16119,19 @@
       </c>
       <c r="K123" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisibletrivalley/event/917329/</t>
+          <t>https://www.mobilize.us/nokings/event/906022/</t>
         </is>
       </c>
       <c r="L123" s="47" t="inlineStr">
         <is>
-          <t>COMMUNITY</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="43" t="inlineStr">
         <is>
-          <t>mobilize:906022:1774729800</t>
+          <t>mobilize:917329:1774724400</t>
         </is>
       </c>
       <c r="B124" s="44" t="b">
@@ -16142,12 +16142,12 @@
       </c>
       <c r="D124" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E124" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Tri-Valley</t>
+          <t>Volunteer for No Kings Tri-Valley 3</t>
         </is>
       </c>
       <c r="F124" s="45" t="inlineStr">
@@ -16157,7 +16157,7 @@
       </c>
       <c r="G124" s="45" t="inlineStr">
         <is>
-          <t>1:30 PM</t>
+          <t>12:00 PM</t>
         </is>
       </c>
       <c r="H124" s="44" t="inlineStr">
@@ -16175,12 +16175,12 @@
       </c>
       <c r="K124" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/906022/</t>
+          <t>https://www.mobilize.us/indivisibletrivalley/event/917329/</t>
         </is>
       </c>
       <c r="L124" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>COMMUNITY</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
     <row r="133">
       <c r="A133" s="43" t="inlineStr">
         <is>
-          <t>mobilize:901775:1774706400</t>
+          <t>mobilize:893210:1774706400</t>
         </is>
       </c>
       <c r="B133" s="44" t="b">
@@ -16646,12 +16646,12 @@
       </c>
       <c r="D133" s="44" t="inlineStr">
         <is>
-          <t>2026-03-08T07:16:44</t>
+          <t>2026-03-12T05:20:25</t>
         </is>
       </c>
       <c r="E133" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Indivisible Boca Raton</t>
+          <t>Indivisible Boca Raton No Kings 3.0</t>
         </is>
       </c>
       <c r="F133" s="45" t="inlineStr">
@@ -16679,7 +16679,7 @@
       </c>
       <c r="K133" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/901775/</t>
+          <t>https://www.mobilize.us/indivisible/event/893210/</t>
         </is>
       </c>
       <c r="L133" s="47" t="inlineStr">
@@ -16691,7 +16691,7 @@
     <row r="134">
       <c r="A134" s="43" t="inlineStr">
         <is>
-          <t>mobilize:893210:1774706400</t>
+          <t>mobilize:901775:1774706400</t>
         </is>
       </c>
       <c r="B134" s="44" t="b">
@@ -16702,12 +16702,12 @@
       </c>
       <c r="D134" s="44" t="inlineStr">
         <is>
-          <t>2026-03-12T05:20:25</t>
+          <t>2026-03-08T07:16:44</t>
         </is>
       </c>
       <c r="E134" s="45" t="inlineStr">
         <is>
-          <t>Indivisible Boca Raton No Kings 3.0</t>
+          <t>NO KINGS Indivisible Boca Raton</t>
         </is>
       </c>
       <c r="F134" s="45" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="K134" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/indivisible/event/893210/</t>
+          <t>https://www.mobilize.us/nokings/event/901775/</t>
         </is>
       </c>
       <c r="L134" s="47" t="inlineStr">
@@ -17083,7 +17083,7 @@
     <row r="141">
       <c r="A141" s="43" t="inlineStr">
         <is>
-          <t>mobilize:902973:1774717200</t>
+          <t>mobilize:914065:1774710000</t>
         </is>
       </c>
       <c r="B141" s="44" t="b">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="E141" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Loudoun - Rt 7 overpass at Belmont Ridge Rd</t>
+          <t>NO KINGS Rally- Midland Texas</t>
         </is>
       </c>
       <c r="F141" s="45" t="inlineStr">
@@ -17109,17 +17109,17 @@
       </c>
       <c r="G141" s="45" t="inlineStr">
         <is>
-          <t>1:00 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="H141" s="44" t="inlineStr">
         <is>
-          <t>Rt 7 overpass at Belmont Ridge Rd | 19313 Front St | Leesburg, VA 20176</t>
+          <t>Wadley &amp; Big Spring | Midland, TX 79705</t>
         </is>
       </c>
       <c r="I141" s="45" t="inlineStr">
         <is>
-          <t>Leesburg Premium Outlets</t>
+          <t>Midland Park Mall</t>
         </is>
       </c>
       <c r="J141" s="45" t="n">
@@ -17127,19 +17127,19 @@
       </c>
       <c r="K141" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/902973/</t>
+          <t>https://www.mobilize.us/nokings/event/914065/</t>
         </is>
       </c>
       <c r="L141" s="47" t="inlineStr">
         <is>
-          <t>VISIBILITY_EVENT</t>
+          <t>RALLY</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="43" t="inlineStr">
         <is>
-          <t>mobilize:914065:1774710000</t>
+          <t>mobilize:902973:1774717200</t>
         </is>
       </c>
       <c r="B142" s="44" t="b">
@@ -17155,7 +17155,7 @@
       </c>
       <c r="E142" s="45" t="inlineStr">
         <is>
-          <t>NO KINGS Rally- Midland Texas</t>
+          <t>NO KINGS Loudoun - Rt 7 overpass at Belmont Ridge Rd</t>
         </is>
       </c>
       <c r="F142" s="45" t="inlineStr">
@@ -17165,17 +17165,17 @@
       </c>
       <c r="G142" s="45" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>1:00 PM</t>
         </is>
       </c>
       <c r="H142" s="44" t="inlineStr">
         <is>
-          <t>Wadley &amp; Big Spring | Midland, TX 79705</t>
+          <t>Rt 7 overpass at Belmont Ridge Rd | 19313 Front St | Leesburg, VA 20176</t>
         </is>
       </c>
       <c r="I142" s="45" t="inlineStr">
         <is>
-          <t>Midland Park Mall</t>
+          <t>Leesburg Premium Outlets</t>
         </is>
       </c>
       <c r="J142" s="45" t="n">
@@ -17183,12 +17183,12 @@
       </c>
       <c r="K142" s="46" t="inlineStr">
         <is>
-          <t>https://www.mobilize.us/nokings/event/914065/</t>
+          <t>https://www.mobilize.us/nokings/event/902973/</t>
         </is>
       </c>
       <c r="L142" s="47" t="inlineStr">
         <is>
-          <t>RALLY</t>
+          <t>VISIBILITY_EVENT</t>
         </is>
       </c>
     </row>
